--- a/Experimentos/grid_experimentos_radar.xlsx
+++ b/Experimentos/grid_experimentos_radar.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="3" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="CONFIG_REFERENCIA" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="CATALOGO_EXPERIMENTOS" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="RESULTADOS_GRID" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="RUN_SUMMARY" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="RUN_ARTEFACTOS" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CONFIG_REFERENCIA" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CATALOGO_EXPERIMENTOS" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RESULTADOS_GRID" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RUN_SUMMARY" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RUN_ARTEFACTOS" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" calcMode="auto" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.001" forceFullCalc="1"/>
@@ -727,21 +727,21 @@
     <row r="13" ht="19.5" customHeight="1" s="27">
       <c r="A13" s="29" t="inlineStr">
         <is>
-          <t>• Horizonte sugerido: 1, 2, 3 y 4 semanas.</t>
+          <t>6) Cierre oficial E1 Ridge: E1_v5_clean queda como mejor Ridge limpio global y E1_v4_clean como referencia parsimoniosa.</t>
         </is>
       </c>
     </row>
     <row r="14" ht="19.5" customHeight="1" s="27">
       <c r="A14" s="29" t="inlineStr">
         <is>
-          <t>• Pesos iniciales del documento: w1=30%, w2=25%, w3=30%, w4=15%; alpha=35%, beta=25%, gamma=25%, delta=10%, eta=5%.</t>
+          <t>7) El orden operativo del plan original continua con E2 Huber antes de E3 Random Forest y E4 XGBoost / LightGBM.</t>
         </is>
       </c>
     </row>
     <row r="15" ht="19.5" customHeight="1" s="27">
       <c r="A15" s="29" t="inlineStr">
         <is>
-          <t>• Puedes cambiar los pesos en 'CONFIG_REFERENCIA' y todas las fórmulas se actualizarán.</t>
+          <t>8) No se continua automaticamente con E1_v6+; Ridge queda cerrado como baseline lineal regularizado principal.</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="G2" s="57" t="inlineStr">
         <is>
-          <t>Buen baseline para señal real e interpretabilidad</t>
+          <t>Ridge cerrado como rama principal: E1_v5_clean mejor global por L_total_Radar; E1_v4_clean referencia parsimoniosa. No continuar automaticamente con E1_v6+.</t>
         </is>
       </c>
     </row>
@@ -1261,7 +1261,7 @@
       </c>
       <c r="G3" s="57" t="inlineStr">
         <is>
-          <t>Útil si hay ruido, shocks y colas</t>
+          <t>Siguiente familia del plan original: Huber con el mismo marco de evaluacion temporal, tuning interno temporal y perdida Radar.</t>
         </is>
       </c>
     </row>

--- a/Experimentos/grid_experimentos_radar.xlsx
+++ b/Experimentos/grid_experimentos_radar.xlsx
@@ -734,18 +734,24 @@
     <row r="14" ht="19.5" customHeight="1" s="27">
       <c r="A14" s="29" t="inlineStr">
         <is>
-          <t>7) El orden operativo del plan original continua con E2 Huber antes de E3 Random Forest y E4 XGBoost / LightGBM.</t>
+          <t>7) Cierre oficial E2 Huber: E2_v3_clean gana internamente, E2_v2_clean descarta convergencia como causa principal y la familia queda cerrada.</t>
         </is>
       </c>
     </row>
     <row r="15" ht="19.5" customHeight="1" s="27">
       <c r="A15" s="29" t="inlineStr">
         <is>
-          <t>8) No se continua automaticamente con E1_v6+; Ridge queda cerrado como baseline lineal regularizado principal.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="19.5" customHeight="1" s="27"/>
+          <t>8) E2_v4_clean queda cancelada por decision metodologica explicita y no se ejecuta.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="19.5" customHeight="1" s="27">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>9) Siguiente prioridad operativa: E3 Random Forest con el mismo marco temporal limpio; E4 XGBoost y E5 CatBoost quedan como continuidad.</t>
+        </is>
+      </c>
+    </row>
     <row r="17" ht="19.5" customHeight="1" s="27">
       <c r="A17" s="30" t="inlineStr">
         <is>
@@ -1261,7 +1267,7 @@
       </c>
       <c r="G3" s="57" t="inlineStr">
         <is>
-          <t>Siguiente familia del plan original: Huber con el mismo marco de evaluacion temporal, tuning interno temporal y perdida Radar.</t>
+          <t>Familia cerrada bajo esquema limpio temporal: E2_v3_clean gana internamente, E2_v2_clean descarta convergencia como explicacion principal y E2_v4_clean se cancela por decision metodologica. No competitiva frente a E1_v5_clean.</t>
         </is>
       </c>
     </row>
@@ -1298,7 +1304,7 @@
       </c>
       <c r="G4" s="57" t="inlineStr">
         <is>
-          <t>Puede captar interacciones sin mucho tuning</t>
+          <t>Siguiente prioridad operativa: Random Forest clean con el mismo marco temporal. Referencia principal E1_v5_clean; referencias secundarias E1_v4_clean y E2_v3_clean.</t>
         </is>
       </c>
     </row>
@@ -1335,7 +1341,7 @@
       </c>
       <c r="G5" s="57" t="inlineStr">
         <is>
-          <t>Muy buen candidato para desempeño</t>
+          <t>Continuidad natural de E3: XGBoost / LightGBM con la misma arquitectura limpia por familias.</t>
         </is>
       </c>
     </row>
@@ -1372,7 +1378,7 @@
       </c>
       <c r="G6" s="57" t="inlineStr">
         <is>
-          <t>Suele funcionar bien con estructura tabular</t>
+          <t>Continuidad de boosting: CatBoost con el mismo marco temporal y comparaciones contra E1/E3.</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1580,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:AK161"/>
+  <dimension ref="A1:AK173"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.54296875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12" customWidth="1" style="26" min="1" max="1"/>
@@ -14817,6 +14823,1890 @@
       <c r="AK161" s="49" t="inlineStr">
         <is>
           <t>2026-03-21 10:54:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="162" ht="15" customHeight="1" s="27">
+      <c r="A162" s="49" t="inlineStr">
+        <is>
+          <t>2026-03-23 05:00:29</t>
+        </is>
+      </c>
+      <c r="B162" s="49" t="inlineStr">
+        <is>
+          <t>E2_v1_clean</t>
+        </is>
+      </c>
+      <c r="C162" s="50" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="D162" s="50" t="inlineStr">
+        <is>
+          <t>robusto</t>
+        </is>
+      </c>
+      <c r="E162" s="50" t="inlineStr">
+        <is>
+          <t>huber_tscv</t>
+        </is>
+      </c>
+      <c r="F162" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="G162" s="49" t="inlineStr">
+        <is>
+          <t>nivel</t>
+        </is>
+      </c>
+      <c r="H162" s="50" t="inlineStr">
+        <is>
+          <t>y_t + lags [1, 2, 3, 4, 5, 6]</t>
+        </is>
+      </c>
+      <c r="I162" s="50" t="inlineStr">
+        <is>
+          <t>sentimiento_medios, v5_agua_neto, v5_alumbrado_neto, v5_americo_neto, v5_basura_neto, v5_corrupcion_neto, v5_delitos_neto, v5_morena_neto, v5_obras_neto, v5_prevencion_neto, v5_vialidad_neto</t>
+        </is>
+      </c>
+      <c r="J162" s="50" t="inlineStr">
+        <is>
+          <t>standard_scaler</t>
+        </is>
+      </c>
+      <c r="K162" s="50" t="inlineStr">
+        <is>
+          <t>corr</t>
+        </is>
+      </c>
+      <c r="L162" s="50" t="inlineStr">
+        <is>
+          <t>walk-forward_expanding</t>
+        </is>
+      </c>
+      <c r="M162" s="49" t="inlineStr">
+        <is>
+          <t>2024-10-14 a 2026-03-02</t>
+        </is>
+      </c>
+      <c r="N162" s="49" t="inlineStr">
+        <is>
+          <t>{"feature_candidates": 83, "feature_mode": "corr", "horizon": 1, "initial_train_size": 40, "lags": [1, 2, 3, 4, 5, 6], "model": "huber_tscv", "model_params": {"inner_splits": 3, "param_grid": {"alpha": [1e-06, 9.999999999999999e-06, 0.0001, 0.001, 0.01, 0.1], "epsilon": [1.1, 1.2, 1.35, 1.5, 1.75, 2.0], "max_iter": [1000], "tol": [0.0001]}, "transform_mode": "standard", "tuning_metric": "mae", "winsor_lower_quantile": 0.05, "winsor_upper_quantile": 0.95}, "rows_eval": 26, "rows_modeling": 66, "selected_feature_count_avg": 30.0, "target_mode": "nivel", "transform_mode": "standard"}</t>
+        </is>
+      </c>
+      <c r="O162" s="51" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="P162" s="51" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="Q162" s="51" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="R162" s="51" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="S162" s="52" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="T162" s="53" t="n">
+        <v>0.184685768753275</v>
+      </c>
+      <c r="U162" s="53" t="n">
+        <v>0.2307692307692307</v>
+      </c>
+      <c r="V162" s="53" t="n">
+        <v>0.1666666666666666</v>
+      </c>
+      <c r="W162" s="53" t="n">
+        <v>0.6538461538461539</v>
+      </c>
+      <c r="X162" s="54" t="n">
+        <v>0.06881508264217079</v>
+      </c>
+      <c r="Y162" s="53" t="n">
+        <v>0.1136342110145291</v>
+      </c>
+      <c r="Z162" s="53" t="n">
+        <v>0.1492880502016995</v>
+      </c>
+      <c r="AA162" s="55" t="n">
+        <v>0.7692307692307693</v>
+      </c>
+      <c r="AB162" s="55" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="AC162" s="49" t="inlineStr">
+        <is>
+          <t>corrido</t>
+        </is>
+      </c>
+      <c r="AD162" s="49" t="inlineStr">
+        <is>
+          <t>Huber limpio con tuning temporal interno | metric=mae | inner_splits=3</t>
+        </is>
+      </c>
+      <c r="AE162" s="49" t="inlineStr">
+        <is>
+          <t>run_e2_huber_clean.py</t>
+        </is>
+      </c>
+      <c r="AF162" s="49" t="inlineStr">
+        <is>
+          <t>Scripts/Modeling/run_e2_huber_clean.py</t>
+        </is>
+      </c>
+      <c r="AG162" s="49" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E2_v1_clean_20260323_050029</t>
+        </is>
+      </c>
+      <c r="AH162" s="49" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E2_v1_clean_20260323_050029/scripts/run_e2_huber_clean.py</t>
+        </is>
+      </c>
+      <c r="AI162" s="49" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E2_v1_clean_20260323_050029/parametros_run.json</t>
+        </is>
+      </c>
+      <c r="AJ162" s="49" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E2_v1_clean_20260323_050029/metricas_horizonte.json</t>
+        </is>
+      </c>
+      <c r="AK162" s="49" t="inlineStr">
+        <is>
+          <t>2026-03-23 05:00:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="163" ht="15" customHeight="1" s="27">
+      <c r="A163" s="49" t="inlineStr">
+        <is>
+          <t>2026-03-23 05:00:29</t>
+        </is>
+      </c>
+      <c r="B163" s="49" t="inlineStr">
+        <is>
+          <t>E2_v1_clean</t>
+        </is>
+      </c>
+      <c r="C163" s="50" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="D163" s="50" t="inlineStr">
+        <is>
+          <t>robusto</t>
+        </is>
+      </c>
+      <c r="E163" s="50" t="inlineStr">
+        <is>
+          <t>huber_tscv</t>
+        </is>
+      </c>
+      <c r="F163" s="50" t="n">
+        <v>2</v>
+      </c>
+      <c r="G163" s="49" t="inlineStr">
+        <is>
+          <t>nivel</t>
+        </is>
+      </c>
+      <c r="H163" s="50" t="inlineStr">
+        <is>
+          <t>y_t + lags [1, 2, 3, 4, 5, 6]</t>
+        </is>
+      </c>
+      <c r="I163" s="50" t="inlineStr">
+        <is>
+          <t>sentimiento_medios, v5_agua_neto, v5_alumbrado_neto, v5_americo_neto, v5_basura_neto, v5_corrupcion_neto, v5_delitos_neto, v5_morena_neto, v5_obras_neto, v5_prevencion_neto, v5_vialidad_neto</t>
+        </is>
+      </c>
+      <c r="J163" s="50" t="inlineStr">
+        <is>
+          <t>standard_scaler</t>
+        </is>
+      </c>
+      <c r="K163" s="50" t="inlineStr">
+        <is>
+          <t>corr</t>
+        </is>
+      </c>
+      <c r="L163" s="50" t="inlineStr">
+        <is>
+          <t>walk-forward_expanding</t>
+        </is>
+      </c>
+      <c r="M163" s="49" t="inlineStr">
+        <is>
+          <t>2024-10-14 a 2026-03-02</t>
+        </is>
+      </c>
+      <c r="N163" s="49" t="inlineStr">
+        <is>
+          <t>{"feature_candidates": 83, "feature_mode": "corr", "horizon": 2, "initial_train_size": 40, "lags": [1, 2, 3, 4, 5, 6], "model": "huber_tscv", "model_params": {"inner_splits": 3, "param_grid": {"alpha": [1e-06, 9.999999999999999e-06, 0.0001, 0.001, 0.01, 0.1], "epsilon": [1.1, 1.2, 1.35, 1.5, 1.75, 2.0], "max_iter": [1000], "tol": [0.0001]}, "transform_mode": "standard", "tuning_metric": "mae", "winsor_lower_quantile": 0.05, "winsor_upper_quantile": 0.95}, "rows_eval": 25, "rows_modeling": 65, "selected_feature_count_avg": 30.0, "target_mode": "nivel", "transform_mode": "standard"}</t>
+        </is>
+      </c>
+      <c r="O163" s="51" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="P163" s="51" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="Q163" s="51" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="R163" s="51" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="S163" s="52" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="T163" s="53" t="n">
+        <v>0.198125454400369</v>
+      </c>
+      <c r="U163" s="53" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="V163" s="53" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="W163" s="53" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="X163" s="54" t="n">
+        <v>0.0870859772600323</v>
+      </c>
+      <c r="Y163" s="53" t="n">
+        <v>0.1219034354658784</v>
+      </c>
+      <c r="Z163" s="53" t="n">
+        <v>0.1466092520563559</v>
+      </c>
+      <c r="AA163" s="55" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="AB163" s="55" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AC163" s="49" t="inlineStr">
+        <is>
+          <t>corrido</t>
+        </is>
+      </c>
+      <c r="AD163" s="49" t="inlineStr">
+        <is>
+          <t>Huber limpio con tuning temporal interno | metric=mae | inner_splits=3</t>
+        </is>
+      </c>
+      <c r="AE163" s="49" t="inlineStr">
+        <is>
+          <t>run_e2_huber_clean.py</t>
+        </is>
+      </c>
+      <c r="AF163" s="49" t="inlineStr">
+        <is>
+          <t>Scripts/Modeling/run_e2_huber_clean.py</t>
+        </is>
+      </c>
+      <c r="AG163" s="49" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E2_v1_clean_20260323_050029</t>
+        </is>
+      </c>
+      <c r="AH163" s="49" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E2_v1_clean_20260323_050029/scripts/run_e2_huber_clean.py</t>
+        </is>
+      </c>
+      <c r="AI163" s="49" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E2_v1_clean_20260323_050029/parametros_run.json</t>
+        </is>
+      </c>
+      <c r="AJ163" s="49" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E2_v1_clean_20260323_050029/metricas_horizonte.json</t>
+        </is>
+      </c>
+      <c r="AK163" s="49" t="inlineStr">
+        <is>
+          <t>2026-03-23 05:00:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="164" ht="15" customHeight="1" s="27">
+      <c r="A164" s="49" t="inlineStr">
+        <is>
+          <t>2026-03-23 05:00:29</t>
+        </is>
+      </c>
+      <c r="B164" s="49" t="inlineStr">
+        <is>
+          <t>E2_v1_clean</t>
+        </is>
+      </c>
+      <c r="C164" s="50" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="D164" s="50" t="inlineStr">
+        <is>
+          <t>robusto</t>
+        </is>
+      </c>
+      <c r="E164" s="50" t="inlineStr">
+        <is>
+          <t>huber_tscv</t>
+        </is>
+      </c>
+      <c r="F164" s="50" t="n">
+        <v>3</v>
+      </c>
+      <c r="G164" s="49" t="inlineStr">
+        <is>
+          <t>nivel</t>
+        </is>
+      </c>
+      <c r="H164" s="50" t="inlineStr">
+        <is>
+          <t>y_t + lags [1, 2, 3, 4, 5, 6]</t>
+        </is>
+      </c>
+      <c r="I164" s="50" t="inlineStr">
+        <is>
+          <t>sentimiento_medios, v5_agua_neto, v5_alumbrado_neto, v5_americo_neto, v5_basura_neto, v5_corrupcion_neto, v5_delitos_neto, v5_morena_neto, v5_obras_neto, v5_prevencion_neto, v5_vialidad_neto</t>
+        </is>
+      </c>
+      <c r="J164" s="50" t="inlineStr">
+        <is>
+          <t>standard_scaler</t>
+        </is>
+      </c>
+      <c r="K164" s="50" t="inlineStr">
+        <is>
+          <t>corr</t>
+        </is>
+      </c>
+      <c r="L164" s="50" t="inlineStr">
+        <is>
+          <t>walk-forward_expanding</t>
+        </is>
+      </c>
+      <c r="M164" s="49" t="inlineStr">
+        <is>
+          <t>2024-10-14 a 2026-03-02</t>
+        </is>
+      </c>
+      <c r="N164" s="49" t="inlineStr">
+        <is>
+          <t>{"feature_candidates": 83, "feature_mode": "corr", "horizon": 3, "initial_train_size": 40, "lags": [1, 2, 3, 4, 5, 6], "model": "huber_tscv", "model_params": {"inner_splits": 3, "param_grid": {"alpha": [1e-06, 9.999999999999999e-06, 0.0001, 0.001, 0.01, 0.1], "epsilon": [1.1, 1.2, 1.35, 1.5, 1.75, 2.0], "max_iter": [1000], "tol": [0.0001]}, "transform_mode": "standard", "tuning_metric": "mae", "winsor_lower_quantile": 0.05, "winsor_upper_quantile": 0.95}, "rows_eval": 24, "rows_modeling": 64, "selected_feature_count_avg": 30.0, "target_mode": "nivel", "transform_mode": "standard"}</t>
+        </is>
+      </c>
+      <c r="O164" s="51" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="P164" s="51" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="Q164" s="51" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="R164" s="51" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="S164" s="52" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="T164" s="53" t="n">
+        <v>0.258896465891488</v>
+      </c>
+      <c r="U164" s="53" t="n">
+        <v>0.2916666666666666</v>
+      </c>
+      <c r="V164" s="53" t="n">
+        <v>0.1818181818181818</v>
+      </c>
+      <c r="W164" s="53" t="n">
+        <v>0.7083333333333334</v>
+      </c>
+      <c r="X164" s="54" t="n">
+        <v>0.08394549255496986</v>
+      </c>
+      <c r="Y164" s="53" t="n">
+        <v>0.1592948706044114</v>
+      </c>
+      <c r="Z164" s="53" t="n">
+        <v>0.2059121290091017</v>
+      </c>
+      <c r="AA164" s="55" t="n">
+        <v>0.7083333333333334</v>
+      </c>
+      <c r="AB164" s="55" t="n">
+        <v>0.8181818181818182</v>
+      </c>
+      <c r="AC164" s="49" t="inlineStr">
+        <is>
+          <t>corrido</t>
+        </is>
+      </c>
+      <c r="AD164" s="49" t="inlineStr">
+        <is>
+          <t>Huber limpio con tuning temporal interno | metric=mae | inner_splits=3</t>
+        </is>
+      </c>
+      <c r="AE164" s="49" t="inlineStr">
+        <is>
+          <t>run_e2_huber_clean.py</t>
+        </is>
+      </c>
+      <c r="AF164" s="49" t="inlineStr">
+        <is>
+          <t>Scripts/Modeling/run_e2_huber_clean.py</t>
+        </is>
+      </c>
+      <c r="AG164" s="49" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E2_v1_clean_20260323_050029</t>
+        </is>
+      </c>
+      <c r="AH164" s="49" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E2_v1_clean_20260323_050029/scripts/run_e2_huber_clean.py</t>
+        </is>
+      </c>
+      <c r="AI164" s="49" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E2_v1_clean_20260323_050029/parametros_run.json</t>
+        </is>
+      </c>
+      <c r="AJ164" s="49" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E2_v1_clean_20260323_050029/metricas_horizonte.json</t>
+        </is>
+      </c>
+      <c r="AK164" s="49" t="inlineStr">
+        <is>
+          <t>2026-03-23 05:00:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="165" ht="15" customHeight="1" s="27">
+      <c r="A165" s="49" t="inlineStr">
+        <is>
+          <t>2026-03-23 05:00:29</t>
+        </is>
+      </c>
+      <c r="B165" s="49" t="inlineStr">
+        <is>
+          <t>E2_v1_clean</t>
+        </is>
+      </c>
+      <c r="C165" s="50" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="D165" s="50" t="inlineStr">
+        <is>
+          <t>robusto</t>
+        </is>
+      </c>
+      <c r="E165" s="50" t="inlineStr">
+        <is>
+          <t>huber_tscv</t>
+        </is>
+      </c>
+      <c r="F165" s="50" t="n">
+        <v>4</v>
+      </c>
+      <c r="G165" s="49" t="inlineStr">
+        <is>
+          <t>nivel</t>
+        </is>
+      </c>
+      <c r="H165" s="50" t="inlineStr">
+        <is>
+          <t>y_t + lags [1, 2, 3, 4, 5, 6]</t>
+        </is>
+      </c>
+      <c r="I165" s="50" t="inlineStr">
+        <is>
+          <t>sentimiento_medios, v5_agua_neto, v5_alumbrado_neto, v5_americo_neto, v5_basura_neto, v5_corrupcion_neto, v5_delitos_neto, v5_morena_neto, v5_obras_neto, v5_prevencion_neto, v5_vialidad_neto</t>
+        </is>
+      </c>
+      <c r="J165" s="50" t="inlineStr">
+        <is>
+          <t>standard_scaler</t>
+        </is>
+      </c>
+      <c r="K165" s="50" t="inlineStr">
+        <is>
+          <t>corr</t>
+        </is>
+      </c>
+      <c r="L165" s="50" t="inlineStr">
+        <is>
+          <t>walk-forward_expanding</t>
+        </is>
+      </c>
+      <c r="M165" s="49" t="inlineStr">
+        <is>
+          <t>2024-10-14 a 2026-03-02</t>
+        </is>
+      </c>
+      <c r="N165" s="49" t="inlineStr">
+        <is>
+          <t>{"feature_candidates": 83, "feature_mode": "corr", "horizon": 4, "initial_train_size": 40, "lags": [1, 2, 3, 4, 5, 6], "model": "huber_tscv", "model_params": {"inner_splits": 3, "param_grid": {"alpha": [1e-06, 9.999999999999999e-06, 0.0001, 0.001, 0.01, 0.1], "epsilon": [1.1, 1.2, 1.35, 1.5, 1.75, 2.0], "max_iter": [1000], "tol": [0.0001]}, "transform_mode": "standard", "tuning_metric": "mae", "winsor_lower_quantile": 0.05, "winsor_upper_quantile": 0.95}, "rows_eval": 23, "rows_modeling": 63, "selected_feature_count_avg": 30.0, "target_mode": "nivel", "transform_mode": "standard"}</t>
+        </is>
+      </c>
+      <c r="O165" s="51" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="P165" s="51" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="Q165" s="51" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="R165" s="51" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="S165" s="52" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="T165" s="53" t="n">
+        <v>0.3118545795245171</v>
+      </c>
+      <c r="U165" s="53" t="n">
+        <v>0.4782608695652174</v>
+      </c>
+      <c r="V165" s="53" t="n">
+        <v>0.4444444444444444</v>
+      </c>
+      <c r="W165" s="53" t="n">
+        <v>0.7391304347826086</v>
+      </c>
+      <c r="X165" s="54" t="n">
+        <v>0.06206077122213859</v>
+      </c>
+      <c r="Y165" s="53" t="n">
+        <v>0.1918791541695755</v>
+      </c>
+      <c r="Z165" s="53" t="n">
+        <v>0.2633428327259931</v>
+      </c>
+      <c r="AA165" s="55" t="n">
+        <v>0.5217391304347826</v>
+      </c>
+      <c r="AB165" s="55" t="n">
+        <v>0.5555555555555556</v>
+      </c>
+      <c r="AC165" s="49" t="inlineStr">
+        <is>
+          <t>corrido</t>
+        </is>
+      </c>
+      <c r="AD165" s="49" t="inlineStr">
+        <is>
+          <t>Huber limpio con tuning temporal interno | metric=mae | inner_splits=3</t>
+        </is>
+      </c>
+      <c r="AE165" s="49" t="inlineStr">
+        <is>
+          <t>run_e2_huber_clean.py</t>
+        </is>
+      </c>
+      <c r="AF165" s="49" t="inlineStr">
+        <is>
+          <t>Scripts/Modeling/run_e2_huber_clean.py</t>
+        </is>
+      </c>
+      <c r="AG165" s="49" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E2_v1_clean_20260323_050029</t>
+        </is>
+      </c>
+      <c r="AH165" s="49" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E2_v1_clean_20260323_050029/scripts/run_e2_huber_clean.py</t>
+        </is>
+      </c>
+      <c r="AI165" s="49" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E2_v1_clean_20260323_050029/parametros_run.json</t>
+        </is>
+      </c>
+      <c r="AJ165" s="49" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E2_v1_clean_20260323_050029/metricas_horizonte.json</t>
+        </is>
+      </c>
+      <c r="AK165" s="49" t="inlineStr">
+        <is>
+          <t>2026-03-23 05:00:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="166" ht="15" customHeight="1" s="27">
+      <c r="A166" s="49" t="inlineStr">
+        <is>
+          <t>2026-03-23 05:41:01</t>
+        </is>
+      </c>
+      <c r="B166" s="49" t="inlineStr">
+        <is>
+          <t>E2_v2_clean</t>
+        </is>
+      </c>
+      <c r="C166" s="50" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="D166" s="50" t="inlineStr">
+        <is>
+          <t>robusto</t>
+        </is>
+      </c>
+      <c r="E166" s="50" t="inlineStr">
+        <is>
+          <t>huber_tscv</t>
+        </is>
+      </c>
+      <c r="F166" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="G166" s="49" t="inlineStr">
+        <is>
+          <t>nivel</t>
+        </is>
+      </c>
+      <c r="H166" s="50" t="inlineStr">
+        <is>
+          <t>y_t + lags [1, 2, 3, 4, 5, 6]</t>
+        </is>
+      </c>
+      <c r="I166" s="50" t="inlineStr">
+        <is>
+          <t>sentimiento_medios, v5_agua_neto, v5_alumbrado_neto, v5_americo_neto, v5_basura_neto, v5_corrupcion_neto, v5_delitos_neto, v5_morena_neto, v5_obras_neto, v5_prevencion_neto, v5_vialidad_neto</t>
+        </is>
+      </c>
+      <c r="J166" s="50" t="inlineStr">
+        <is>
+          <t>standard_scaler</t>
+        </is>
+      </c>
+      <c r="K166" s="50" t="inlineStr">
+        <is>
+          <t>corr</t>
+        </is>
+      </c>
+      <c r="L166" s="50" t="inlineStr">
+        <is>
+          <t>walk-forward_expanding</t>
+        </is>
+      </c>
+      <c r="M166" s="49" t="inlineStr">
+        <is>
+          <t>2024-10-14 a 2026-03-02</t>
+        </is>
+      </c>
+      <c r="N166" s="49" t="inlineStr">
+        <is>
+          <t>{"feature_candidates": 83, "feature_mode": "corr", "horizon": 1, "initial_train_size": 40, "lags": [1, 2, 3, 4, 5, 6], "model": "huber_tscv", "model_params": {"hypothesis_note": "control_de_convergencia", "inner_splits": 3, "param_grid": {"alpha": [1e-06, 9.999999999999999e-06, 0.0001, 0.001, 0.01, 0.1], "epsilon": [1.1, 1.2, 1.35, 1.5, 1.75, 2.0], "max_iter": [5000], "tol": [0.0001, 0.001]}, "transform_mode": "standard", "tuning_metric": "mae", "winsor_lower_quantile": 0.05, "winsor_upper_quantile": 0.95}, "rows_eval": 26, "rows_modeling": 66, "selected_feature_count_avg": 30.0, "target_mode": "nivel", "transform_mode": "standard"}</t>
+        </is>
+      </c>
+      <c r="O166" s="51" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="P166" s="51" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="Q166" s="51" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="R166" s="51" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="S166" s="52" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="T166" s="53" t="n">
+        <v>0.1848095621248963</v>
+      </c>
+      <c r="U166" s="53" t="n">
+        <v>0.2307692307692307</v>
+      </c>
+      <c r="V166" s="53" t="n">
+        <v>0.1666666666666666</v>
+      </c>
+      <c r="W166" s="53" t="n">
+        <v>0.6538461538461539</v>
+      </c>
+      <c r="X166" s="54" t="n">
+        <v>0.06882808094619103</v>
+      </c>
+      <c r="Y166" s="53" t="n">
+        <v>0.1137103791037543</v>
+      </c>
+      <c r="Z166" s="53" t="n">
+        <v>0.1491199728508273</v>
+      </c>
+      <c r="AA166" s="55" t="n">
+        <v>0.7692307692307693</v>
+      </c>
+      <c r="AB166" s="55" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="AC166" s="49" t="inlineStr">
+        <is>
+          <t>corrido</t>
+        </is>
+      </c>
+      <c r="AD166" s="49" t="inlineStr">
+        <is>
+          <t>Huber limpio con tuning temporal interno | hipotesis=control_de_convergencia | metric=mae | inner_splits=3</t>
+        </is>
+      </c>
+      <c r="AE166" s="49" t="inlineStr">
+        <is>
+          <t>run_e2_huber_clean.py</t>
+        </is>
+      </c>
+      <c r="AF166" s="49" t="inlineStr">
+        <is>
+          <t>Scripts/Modeling/run_e2_huber_clean.py</t>
+        </is>
+      </c>
+      <c r="AG166" s="49" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E2_v2_clean_20260323_054101</t>
+        </is>
+      </c>
+      <c r="AH166" s="49" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E2_v2_clean_20260323_054101/scripts/run_e2_huber_clean.py</t>
+        </is>
+      </c>
+      <c r="AI166" s="49" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E2_v2_clean_20260323_054101/parametros_run.json</t>
+        </is>
+      </c>
+      <c r="AJ166" s="49" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E2_v2_clean_20260323_054101/metricas_horizonte.json</t>
+        </is>
+      </c>
+      <c r="AK166" s="49" t="inlineStr">
+        <is>
+          <t>2026-03-23 05:41:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="167" ht="15" customHeight="1" s="27">
+      <c r="A167" s="49" t="inlineStr">
+        <is>
+          <t>2026-03-23 05:41:01</t>
+        </is>
+      </c>
+      <c r="B167" s="49" t="inlineStr">
+        <is>
+          <t>E2_v2_clean</t>
+        </is>
+      </c>
+      <c r="C167" s="50" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="D167" s="50" t="inlineStr">
+        <is>
+          <t>robusto</t>
+        </is>
+      </c>
+      <c r="E167" s="50" t="inlineStr">
+        <is>
+          <t>huber_tscv</t>
+        </is>
+      </c>
+      <c r="F167" s="50" t="n">
+        <v>2</v>
+      </c>
+      <c r="G167" s="49" t="inlineStr">
+        <is>
+          <t>nivel</t>
+        </is>
+      </c>
+      <c r="H167" s="50" t="inlineStr">
+        <is>
+          <t>y_t + lags [1, 2, 3, 4, 5, 6]</t>
+        </is>
+      </c>
+      <c r="I167" s="50" t="inlineStr">
+        <is>
+          <t>sentimiento_medios, v5_agua_neto, v5_alumbrado_neto, v5_americo_neto, v5_basura_neto, v5_corrupcion_neto, v5_delitos_neto, v5_morena_neto, v5_obras_neto, v5_prevencion_neto, v5_vialidad_neto</t>
+        </is>
+      </c>
+      <c r="J167" s="50" t="inlineStr">
+        <is>
+          <t>standard_scaler</t>
+        </is>
+      </c>
+      <c r="K167" s="50" t="inlineStr">
+        <is>
+          <t>corr</t>
+        </is>
+      </c>
+      <c r="L167" s="50" t="inlineStr">
+        <is>
+          <t>walk-forward_expanding</t>
+        </is>
+      </c>
+      <c r="M167" s="49" t="inlineStr">
+        <is>
+          <t>2024-10-14 a 2026-03-02</t>
+        </is>
+      </c>
+      <c r="N167" s="49" t="inlineStr">
+        <is>
+          <t>{"feature_candidates": 83, "feature_mode": "corr", "horizon": 2, "initial_train_size": 40, "lags": [1, 2, 3, 4, 5, 6], "model": "huber_tscv", "model_params": {"hypothesis_note": "control_de_convergencia", "inner_splits": 3, "param_grid": {"alpha": [1e-06, 9.999999999999999e-06, 0.0001, 0.001, 0.01, 0.1], "epsilon": [1.1, 1.2, 1.35, 1.5, 1.75, 2.0], "max_iter": [5000], "tol": [0.0001, 0.001]}, "transform_mode": "standard", "tuning_metric": "mae", "winsor_lower_quantile": 0.05, "winsor_upper_quantile": 0.95}, "rows_eval": 25, "rows_modeling": 65, "selected_feature_count_avg": 30.0, "target_mode": "nivel", "transform_mode": "standard"}</t>
+        </is>
+      </c>
+      <c r="O167" s="51" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="P167" s="51" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="Q167" s="51" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="R167" s="51" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="S167" s="52" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="T167" s="53" t="n">
+        <v>0.198125454400369</v>
+      </c>
+      <c r="U167" s="53" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="V167" s="53" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="W167" s="53" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="X167" s="54" t="n">
+        <v>0.0870859772600323</v>
+      </c>
+      <c r="Y167" s="53" t="n">
+        <v>0.1219034354658784</v>
+      </c>
+      <c r="Z167" s="53" t="n">
+        <v>0.1466092520563559</v>
+      </c>
+      <c r="AA167" s="55" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="AB167" s="55" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AC167" s="49" t="inlineStr">
+        <is>
+          <t>corrido</t>
+        </is>
+      </c>
+      <c r="AD167" s="49" t="inlineStr">
+        <is>
+          <t>Huber limpio con tuning temporal interno | hipotesis=control_de_convergencia | metric=mae | inner_splits=3</t>
+        </is>
+      </c>
+      <c r="AE167" s="49" t="inlineStr">
+        <is>
+          <t>run_e2_huber_clean.py</t>
+        </is>
+      </c>
+      <c r="AF167" s="49" t="inlineStr">
+        <is>
+          <t>Scripts/Modeling/run_e2_huber_clean.py</t>
+        </is>
+      </c>
+      <c r="AG167" s="49" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E2_v2_clean_20260323_054101</t>
+        </is>
+      </c>
+      <c r="AH167" s="49" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E2_v2_clean_20260323_054101/scripts/run_e2_huber_clean.py</t>
+        </is>
+      </c>
+      <c r="AI167" s="49" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E2_v2_clean_20260323_054101/parametros_run.json</t>
+        </is>
+      </c>
+      <c r="AJ167" s="49" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E2_v2_clean_20260323_054101/metricas_horizonte.json</t>
+        </is>
+      </c>
+      <c r="AK167" s="49" t="inlineStr">
+        <is>
+          <t>2026-03-23 05:41:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="168" ht="15" customHeight="1" s="27">
+      <c r="A168" s="49" t="inlineStr">
+        <is>
+          <t>2026-03-23 05:41:01</t>
+        </is>
+      </c>
+      <c r="B168" s="49" t="inlineStr">
+        <is>
+          <t>E2_v2_clean</t>
+        </is>
+      </c>
+      <c r="C168" s="50" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="D168" s="50" t="inlineStr">
+        <is>
+          <t>robusto</t>
+        </is>
+      </c>
+      <c r="E168" s="50" t="inlineStr">
+        <is>
+          <t>huber_tscv</t>
+        </is>
+      </c>
+      <c r="F168" s="50" t="n">
+        <v>3</v>
+      </c>
+      <c r="G168" s="49" t="inlineStr">
+        <is>
+          <t>nivel</t>
+        </is>
+      </c>
+      <c r="H168" s="50" t="inlineStr">
+        <is>
+          <t>y_t + lags [1, 2, 3, 4, 5, 6]</t>
+        </is>
+      </c>
+      <c r="I168" s="50" t="inlineStr">
+        <is>
+          <t>sentimiento_medios, v5_agua_neto, v5_alumbrado_neto, v5_americo_neto, v5_basura_neto, v5_corrupcion_neto, v5_delitos_neto, v5_morena_neto, v5_obras_neto, v5_prevencion_neto, v5_vialidad_neto</t>
+        </is>
+      </c>
+      <c r="J168" s="50" t="inlineStr">
+        <is>
+          <t>standard_scaler</t>
+        </is>
+      </c>
+      <c r="K168" s="50" t="inlineStr">
+        <is>
+          <t>corr</t>
+        </is>
+      </c>
+      <c r="L168" s="50" t="inlineStr">
+        <is>
+          <t>walk-forward_expanding</t>
+        </is>
+      </c>
+      <c r="M168" s="49" t="inlineStr">
+        <is>
+          <t>2024-10-14 a 2026-03-02</t>
+        </is>
+      </c>
+      <c r="N168" s="49" t="inlineStr">
+        <is>
+          <t>{"feature_candidates": 83, "feature_mode": "corr", "horizon": 3, "initial_train_size": 40, "lags": [1, 2, 3, 4, 5, 6], "model": "huber_tscv", "model_params": {"hypothesis_note": "control_de_convergencia", "inner_splits": 3, "param_grid": {"alpha": [1e-06, 9.999999999999999e-06, 0.0001, 0.001, 0.01, 0.1], "epsilon": [1.1, 1.2, 1.35, 1.5, 1.75, 2.0], "max_iter": [5000], "tol": [0.0001, 0.001]}, "transform_mode": "standard", "tuning_metric": "mae", "winsor_lower_quantile": 0.05, "winsor_upper_quantile": 0.95}, "rows_eval": 24, "rows_modeling": 64, "selected_feature_count_avg": 30.0, "target_mode": "nivel", "transform_mode": "standard"}</t>
+        </is>
+      </c>
+      <c r="O168" s="51" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="P168" s="51" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="Q168" s="51" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="R168" s="51" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="S168" s="52" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="T168" s="53" t="n">
+        <v>0.258896465891488</v>
+      </c>
+      <c r="U168" s="53" t="n">
+        <v>0.2916666666666666</v>
+      </c>
+      <c r="V168" s="53" t="n">
+        <v>0.1818181818181818</v>
+      </c>
+      <c r="W168" s="53" t="n">
+        <v>0.7083333333333334</v>
+      </c>
+      <c r="X168" s="54" t="n">
+        <v>0.08394549255496986</v>
+      </c>
+      <c r="Y168" s="53" t="n">
+        <v>0.1592948706044114</v>
+      </c>
+      <c r="Z168" s="53" t="n">
+        <v>0.2059121290091017</v>
+      </c>
+      <c r="AA168" s="55" t="n">
+        <v>0.7083333333333334</v>
+      </c>
+      <c r="AB168" s="55" t="n">
+        <v>0.8181818181818182</v>
+      </c>
+      <c r="AC168" s="49" t="inlineStr">
+        <is>
+          <t>corrido</t>
+        </is>
+      </c>
+      <c r="AD168" s="49" t="inlineStr">
+        <is>
+          <t>Huber limpio con tuning temporal interno | hipotesis=control_de_convergencia | metric=mae | inner_splits=3</t>
+        </is>
+      </c>
+      <c r="AE168" s="49" t="inlineStr">
+        <is>
+          <t>run_e2_huber_clean.py</t>
+        </is>
+      </c>
+      <c r="AF168" s="49" t="inlineStr">
+        <is>
+          <t>Scripts/Modeling/run_e2_huber_clean.py</t>
+        </is>
+      </c>
+      <c r="AG168" s="49" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E2_v2_clean_20260323_054101</t>
+        </is>
+      </c>
+      <c r="AH168" s="49" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E2_v2_clean_20260323_054101/scripts/run_e2_huber_clean.py</t>
+        </is>
+      </c>
+      <c r="AI168" s="49" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E2_v2_clean_20260323_054101/parametros_run.json</t>
+        </is>
+      </c>
+      <c r="AJ168" s="49" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E2_v2_clean_20260323_054101/metricas_horizonte.json</t>
+        </is>
+      </c>
+      <c r="AK168" s="49" t="inlineStr">
+        <is>
+          <t>2026-03-23 05:41:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="169" ht="15" customHeight="1" s="27">
+      <c r="A169" s="49" t="inlineStr">
+        <is>
+          <t>2026-03-23 05:41:01</t>
+        </is>
+      </c>
+      <c r="B169" s="49" t="inlineStr">
+        <is>
+          <t>E2_v2_clean</t>
+        </is>
+      </c>
+      <c r="C169" s="50" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="D169" s="50" t="inlineStr">
+        <is>
+          <t>robusto</t>
+        </is>
+      </c>
+      <c r="E169" s="50" t="inlineStr">
+        <is>
+          <t>huber_tscv</t>
+        </is>
+      </c>
+      <c r="F169" s="50" t="n">
+        <v>4</v>
+      </c>
+      <c r="G169" s="49" t="inlineStr">
+        <is>
+          <t>nivel</t>
+        </is>
+      </c>
+      <c r="H169" s="50" t="inlineStr">
+        <is>
+          <t>y_t + lags [1, 2, 3, 4, 5, 6]</t>
+        </is>
+      </c>
+      <c r="I169" s="50" t="inlineStr">
+        <is>
+          <t>sentimiento_medios, v5_agua_neto, v5_alumbrado_neto, v5_americo_neto, v5_basura_neto, v5_corrupcion_neto, v5_delitos_neto, v5_morena_neto, v5_obras_neto, v5_prevencion_neto, v5_vialidad_neto</t>
+        </is>
+      </c>
+      <c r="J169" s="50" t="inlineStr">
+        <is>
+          <t>standard_scaler</t>
+        </is>
+      </c>
+      <c r="K169" s="50" t="inlineStr">
+        <is>
+          <t>corr</t>
+        </is>
+      </c>
+      <c r="L169" s="50" t="inlineStr">
+        <is>
+          <t>walk-forward_expanding</t>
+        </is>
+      </c>
+      <c r="M169" s="49" t="inlineStr">
+        <is>
+          <t>2024-10-14 a 2026-03-02</t>
+        </is>
+      </c>
+      <c r="N169" s="49" t="inlineStr">
+        <is>
+          <t>{"feature_candidates": 83, "feature_mode": "corr", "horizon": 4, "initial_train_size": 40, "lags": [1, 2, 3, 4, 5, 6], "model": "huber_tscv", "model_params": {"hypothesis_note": "control_de_convergencia", "inner_splits": 3, "param_grid": {"alpha": [1e-06, 9.999999999999999e-06, 0.0001, 0.001, 0.01, 0.1], "epsilon": [1.1, 1.2, 1.35, 1.5, 1.75, 2.0], "max_iter": [5000], "tol": [0.0001, 0.001]}, "transform_mode": "standard", "tuning_metric": "mae", "winsor_lower_quantile": 0.05, "winsor_upper_quantile": 0.95}, "rows_eval": 23, "rows_modeling": 63, "selected_feature_count_avg": 30.0, "target_mode": "nivel", "transform_mode": "standard"}</t>
+        </is>
+      </c>
+      <c r="O169" s="51" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="P169" s="51" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="Q169" s="51" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="R169" s="51" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="S169" s="52" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="T169" s="53" t="n">
+        <v>0.3118545795245171</v>
+      </c>
+      <c r="U169" s="53" t="n">
+        <v>0.4782608695652174</v>
+      </c>
+      <c r="V169" s="53" t="n">
+        <v>0.4444444444444444</v>
+      </c>
+      <c r="W169" s="53" t="n">
+        <v>0.7391304347826086</v>
+      </c>
+      <c r="X169" s="54" t="n">
+        <v>0.06206077122213859</v>
+      </c>
+      <c r="Y169" s="53" t="n">
+        <v>0.1918791541695755</v>
+      </c>
+      <c r="Z169" s="53" t="n">
+        <v>0.2633428327259931</v>
+      </c>
+      <c r="AA169" s="55" t="n">
+        <v>0.5217391304347826</v>
+      </c>
+      <c r="AB169" s="55" t="n">
+        <v>0.5555555555555556</v>
+      </c>
+      <c r="AC169" s="49" t="inlineStr">
+        <is>
+          <t>corrido</t>
+        </is>
+      </c>
+      <c r="AD169" s="49" t="inlineStr">
+        <is>
+          <t>Huber limpio con tuning temporal interno | hipotesis=control_de_convergencia | metric=mae | inner_splits=3</t>
+        </is>
+      </c>
+      <c r="AE169" s="49" t="inlineStr">
+        <is>
+          <t>run_e2_huber_clean.py</t>
+        </is>
+      </c>
+      <c r="AF169" s="49" t="inlineStr">
+        <is>
+          <t>Scripts/Modeling/run_e2_huber_clean.py</t>
+        </is>
+      </c>
+      <c r="AG169" s="49" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E2_v2_clean_20260323_054101</t>
+        </is>
+      </c>
+      <c r="AH169" s="49" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E2_v2_clean_20260323_054101/scripts/run_e2_huber_clean.py</t>
+        </is>
+      </c>
+      <c r="AI169" s="49" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E2_v2_clean_20260323_054101/parametros_run.json</t>
+        </is>
+      </c>
+      <c r="AJ169" s="49" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E2_v2_clean_20260323_054101/metricas_horizonte.json</t>
+        </is>
+      </c>
+      <c r="AK169" s="49" t="inlineStr">
+        <is>
+          <t>2026-03-23 05:41:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="170" ht="15" customHeight="1" s="27">
+      <c r="A170" s="49" t="inlineStr">
+        <is>
+          <t>2026-03-23 06:12:13</t>
+        </is>
+      </c>
+      <c r="B170" s="49" t="inlineStr">
+        <is>
+          <t>E2_v3_clean</t>
+        </is>
+      </c>
+      <c r="C170" s="50" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="D170" s="50" t="inlineStr">
+        <is>
+          <t>robusto</t>
+        </is>
+      </c>
+      <c r="E170" s="50" t="inlineStr">
+        <is>
+          <t>huber_tscv</t>
+        </is>
+      </c>
+      <c r="F170" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="G170" s="49" t="inlineStr">
+        <is>
+          <t>nivel</t>
+        </is>
+      </c>
+      <c r="H170" s="50" t="inlineStr">
+        <is>
+          <t>y_t + lags [1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="I170" s="50" t="inlineStr">
+        <is>
+          <t>sentimiento_medios, v5_agua_neto, v5_alumbrado_neto, v5_americo_neto, v5_basura_neto, v5_corrupcion_neto, v5_delitos_neto, v5_morena_neto, v5_obras_neto, v5_prevencion_neto, v5_vialidad_neto</t>
+        </is>
+      </c>
+      <c r="J170" s="50" t="inlineStr">
+        <is>
+          <t>standard_scaler</t>
+        </is>
+      </c>
+      <c r="K170" s="50" t="inlineStr">
+        <is>
+          <t>corr</t>
+        </is>
+      </c>
+      <c r="L170" s="50" t="inlineStr">
+        <is>
+          <t>walk-forward_expanding</t>
+        </is>
+      </c>
+      <c r="M170" s="49" t="inlineStr">
+        <is>
+          <t>2024-10-14 a 2026-03-02</t>
+        </is>
+      </c>
+      <c r="N170" s="49" t="inlineStr">
+        <is>
+          <t>{"feature_candidates": 59, "feature_mode": "corr", "horizon": 1, "initial_train_size": 40, "lags": [1, 2, 3, 4], "model": "huber_tscv", "model_params": {"hypothesis_note": "prueba_sin_memoria_larga", "inner_splits": 3, "param_grid": {"alpha": [1e-06, 9.999999999999999e-06, 0.0001, 0.001, 0.01, 0.1], "epsilon": [1.1, 1.2, 1.35, 1.5, 1.75, 2.0], "max_iter": [1000], "tol": [0.0001]}, "transform_mode": "standard", "tuning_metric": "mae", "winsor_lower_quantile": 0.05, "winsor_upper_quantile": 0.95}, "rows_eval": 28, "rows_modeling": 68, "selected_feature_count_avg": 21.0, "target_mode": "nivel", "transform_mode": "standard"}</t>
+        </is>
+      </c>
+      <c r="O170" s="51" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="P170" s="51" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="Q170" s="51" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="R170" s="51" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="S170" s="52" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="T170" s="53" t="n">
+        <v>0.1945968068018527</v>
+      </c>
+      <c r="U170" s="53" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="V170" s="53" t="n">
+        <v>0.1538461538461539</v>
+      </c>
+      <c r="W170" s="53" t="n">
+        <v>0.6785714285714286</v>
+      </c>
+      <c r="X170" s="54" t="n">
+        <v>0.07107826910979893</v>
+      </c>
+      <c r="Y170" s="53" t="n">
+        <v>0.1197323148185621</v>
+      </c>
+      <c r="Z170" s="53" t="n">
+        <v>0.1499850473896837</v>
+      </c>
+      <c r="AA170" s="55" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AB170" s="55" t="n">
+        <v>0.8461538461538461</v>
+      </c>
+      <c r="AC170" s="49" t="inlineStr">
+        <is>
+          <t>corrido</t>
+        </is>
+      </c>
+      <c r="AD170" s="49" t="inlineStr">
+        <is>
+          <t>Huber limpio con tuning temporal interno | hipotesis=prueba_sin_memoria_larga | metric=mae | inner_splits=3</t>
+        </is>
+      </c>
+      <c r="AE170" s="49" t="inlineStr">
+        <is>
+          <t>run_e2_huber_clean.py</t>
+        </is>
+      </c>
+      <c r="AF170" s="49" t="inlineStr">
+        <is>
+          <t>Scripts/Modeling/run_e2_huber_clean.py</t>
+        </is>
+      </c>
+      <c r="AG170" s="49" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E2_v3_clean_20260323_061213</t>
+        </is>
+      </c>
+      <c r="AH170" s="49" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E2_v3_clean_20260323_061213/scripts/run_e2_huber_clean.py</t>
+        </is>
+      </c>
+      <c r="AI170" s="49" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E2_v3_clean_20260323_061213/parametros_run.json</t>
+        </is>
+      </c>
+      <c r="AJ170" s="49" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E2_v3_clean_20260323_061213/metricas_horizonte.json</t>
+        </is>
+      </c>
+      <c r="AK170" s="49" t="inlineStr">
+        <is>
+          <t>2026-03-23 06:12:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="171" ht="15" customHeight="1" s="27">
+      <c r="A171" s="49" t="inlineStr">
+        <is>
+          <t>2026-03-23 06:12:13</t>
+        </is>
+      </c>
+      <c r="B171" s="49" t="inlineStr">
+        <is>
+          <t>E2_v3_clean</t>
+        </is>
+      </c>
+      <c r="C171" s="50" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="D171" s="50" t="inlineStr">
+        <is>
+          <t>robusto</t>
+        </is>
+      </c>
+      <c r="E171" s="50" t="inlineStr">
+        <is>
+          <t>huber_tscv</t>
+        </is>
+      </c>
+      <c r="F171" s="50" t="n">
+        <v>2</v>
+      </c>
+      <c r="G171" s="49" t="inlineStr">
+        <is>
+          <t>nivel</t>
+        </is>
+      </c>
+      <c r="H171" s="50" t="inlineStr">
+        <is>
+          <t>y_t + lags [1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="I171" s="50" t="inlineStr">
+        <is>
+          <t>sentimiento_medios, v5_agua_neto, v5_alumbrado_neto, v5_americo_neto, v5_basura_neto, v5_corrupcion_neto, v5_delitos_neto, v5_morena_neto, v5_obras_neto, v5_prevencion_neto, v5_vialidad_neto</t>
+        </is>
+      </c>
+      <c r="J171" s="50" t="inlineStr">
+        <is>
+          <t>standard_scaler</t>
+        </is>
+      </c>
+      <c r="K171" s="50" t="inlineStr">
+        <is>
+          <t>corr</t>
+        </is>
+      </c>
+      <c r="L171" s="50" t="inlineStr">
+        <is>
+          <t>walk-forward_expanding</t>
+        </is>
+      </c>
+      <c r="M171" s="49" t="inlineStr">
+        <is>
+          <t>2024-10-14 a 2026-03-02</t>
+        </is>
+      </c>
+      <c r="N171" s="49" t="inlineStr">
+        <is>
+          <t>{"feature_candidates": 59, "feature_mode": "corr", "horizon": 2, "initial_train_size": 40, "lags": [1, 2, 3, 4], "model": "huber_tscv", "model_params": {"hypothesis_note": "prueba_sin_memoria_larga", "inner_splits": 3, "param_grid": {"alpha": [1e-06, 9.999999999999999e-06, 0.0001, 0.001, 0.01, 0.1], "epsilon": [1.1, 1.2, 1.35, 1.5, 1.75, 2.0], "max_iter": [1000], "tol": [0.0001]}, "transform_mode": "standard", "tuning_metric": "mae", "winsor_lower_quantile": 0.05, "winsor_upper_quantile": 0.95}, "rows_eval": 27, "rows_modeling": 67, "selected_feature_count_avg": 21.0, "target_mode": "nivel", "transform_mode": "standard"}</t>
+        </is>
+      </c>
+      <c r="O171" s="51" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="P171" s="51" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="Q171" s="51" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="R171" s="51" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="S171" s="52" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="T171" s="53" t="n">
+        <v>0.1845910273692062</v>
+      </c>
+      <c r="U171" s="53" t="n">
+        <v>0.3333333333333334</v>
+      </c>
+      <c r="V171" s="53" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="W171" s="53" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="X171" s="54" t="n">
+        <v>0.06927671489480554</v>
+      </c>
+      <c r="Y171" s="53" t="n">
+        <v>0.1135759181503753</v>
+      </c>
+      <c r="Z171" s="53" t="n">
+        <v>0.1479713958144309</v>
+      </c>
+      <c r="AA171" s="55" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="AB171" s="55" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AC171" s="49" t="inlineStr">
+        <is>
+          <t>corrido</t>
+        </is>
+      </c>
+      <c r="AD171" s="49" t="inlineStr">
+        <is>
+          <t>Huber limpio con tuning temporal interno | hipotesis=prueba_sin_memoria_larga | metric=mae | inner_splits=3</t>
+        </is>
+      </c>
+      <c r="AE171" s="49" t="inlineStr">
+        <is>
+          <t>run_e2_huber_clean.py</t>
+        </is>
+      </c>
+      <c r="AF171" s="49" t="inlineStr">
+        <is>
+          <t>Scripts/Modeling/run_e2_huber_clean.py</t>
+        </is>
+      </c>
+      <c r="AG171" s="49" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E2_v3_clean_20260323_061213</t>
+        </is>
+      </c>
+      <c r="AH171" s="49" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E2_v3_clean_20260323_061213/scripts/run_e2_huber_clean.py</t>
+        </is>
+      </c>
+      <c r="AI171" s="49" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E2_v3_clean_20260323_061213/parametros_run.json</t>
+        </is>
+      </c>
+      <c r="AJ171" s="49" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E2_v3_clean_20260323_061213/metricas_horizonte.json</t>
+        </is>
+      </c>
+      <c r="AK171" s="49" t="inlineStr">
+        <is>
+          <t>2026-03-23 06:12:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="172" ht="15" customHeight="1" s="27">
+      <c r="A172" s="49" t="inlineStr">
+        <is>
+          <t>2026-03-23 06:12:13</t>
+        </is>
+      </c>
+      <c r="B172" s="49" t="inlineStr">
+        <is>
+          <t>E2_v3_clean</t>
+        </is>
+      </c>
+      <c r="C172" s="50" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="D172" s="50" t="inlineStr">
+        <is>
+          <t>robusto</t>
+        </is>
+      </c>
+      <c r="E172" s="50" t="inlineStr">
+        <is>
+          <t>huber_tscv</t>
+        </is>
+      </c>
+      <c r="F172" s="50" t="n">
+        <v>3</v>
+      </c>
+      <c r="G172" s="49" t="inlineStr">
+        <is>
+          <t>nivel</t>
+        </is>
+      </c>
+      <c r="H172" s="50" t="inlineStr">
+        <is>
+          <t>y_t + lags [1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="I172" s="50" t="inlineStr">
+        <is>
+          <t>sentimiento_medios, v5_agua_neto, v5_alumbrado_neto, v5_americo_neto, v5_basura_neto, v5_corrupcion_neto, v5_delitos_neto, v5_morena_neto, v5_obras_neto, v5_prevencion_neto, v5_vialidad_neto</t>
+        </is>
+      </c>
+      <c r="J172" s="50" t="inlineStr">
+        <is>
+          <t>standard_scaler</t>
+        </is>
+      </c>
+      <c r="K172" s="50" t="inlineStr">
+        <is>
+          <t>corr</t>
+        </is>
+      </c>
+      <c r="L172" s="50" t="inlineStr">
+        <is>
+          <t>walk-forward_expanding</t>
+        </is>
+      </c>
+      <c r="M172" s="49" t="inlineStr">
+        <is>
+          <t>2024-10-14 a 2026-03-02</t>
+        </is>
+      </c>
+      <c r="N172" s="49" t="inlineStr">
+        <is>
+          <t>{"feature_candidates": 59, "feature_mode": "corr", "horizon": 3, "initial_train_size": 40, "lags": [1, 2, 3, 4], "model": "huber_tscv", "model_params": {"hypothesis_note": "prueba_sin_memoria_larga", "inner_splits": 3, "param_grid": {"alpha": [1e-06, 9.999999999999999e-06, 0.0001, 0.001, 0.01, 0.1], "epsilon": [1.1, 1.2, 1.35, 1.5, 1.75, 2.0], "max_iter": [1000], "tol": [0.0001]}, "transform_mode": "standard", "tuning_metric": "mae", "winsor_lower_quantile": 0.05, "winsor_upper_quantile": 0.95}, "rows_eval": 26, "rows_modeling": 66, "selected_feature_count_avg": 21.0, "target_mode": "nivel", "transform_mode": "standard"}</t>
+        </is>
+      </c>
+      <c r="O172" s="51" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="P172" s="51" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="Q172" s="51" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="R172" s="51" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="S172" s="52" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="T172" s="53" t="n">
+        <v>0.2306409358773327</v>
+      </c>
+      <c r="U172" s="53" t="n">
+        <v>0.3461538461538461</v>
+      </c>
+      <c r="V172" s="53" t="n">
+        <v>0.4166666666666666</v>
+      </c>
+      <c r="W172" s="53" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="X172" s="54" t="n">
+        <v>0.1091211444209661</v>
+      </c>
+      <c r="Y172" s="53" t="n">
+        <v>0.1419096931669162</v>
+      </c>
+      <c r="Z172" s="53" t="n">
+        <v>0.1631289658990064</v>
+      </c>
+      <c r="AA172" s="55" t="n">
+        <v>0.6538461538461539</v>
+      </c>
+      <c r="AB172" s="55" t="n">
+        <v>0.5833333333333334</v>
+      </c>
+      <c r="AC172" s="49" t="inlineStr">
+        <is>
+          <t>corrido</t>
+        </is>
+      </c>
+      <c r="AD172" s="49" t="inlineStr">
+        <is>
+          <t>Huber limpio con tuning temporal interno | hipotesis=prueba_sin_memoria_larga | metric=mae | inner_splits=3</t>
+        </is>
+      </c>
+      <c r="AE172" s="49" t="inlineStr">
+        <is>
+          <t>run_e2_huber_clean.py</t>
+        </is>
+      </c>
+      <c r="AF172" s="49" t="inlineStr">
+        <is>
+          <t>Scripts/Modeling/run_e2_huber_clean.py</t>
+        </is>
+      </c>
+      <c r="AG172" s="49" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E2_v3_clean_20260323_061213</t>
+        </is>
+      </c>
+      <c r="AH172" s="49" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E2_v3_clean_20260323_061213/scripts/run_e2_huber_clean.py</t>
+        </is>
+      </c>
+      <c r="AI172" s="49" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E2_v3_clean_20260323_061213/parametros_run.json</t>
+        </is>
+      </c>
+      <c r="AJ172" s="49" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E2_v3_clean_20260323_061213/metricas_horizonte.json</t>
+        </is>
+      </c>
+      <c r="AK172" s="49" t="inlineStr">
+        <is>
+          <t>2026-03-23 06:12:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="173" ht="15" customHeight="1" s="27">
+      <c r="A173" s="49" t="inlineStr">
+        <is>
+          <t>2026-03-23 06:12:13</t>
+        </is>
+      </c>
+      <c r="B173" s="49" t="inlineStr">
+        <is>
+          <t>E2_v3_clean</t>
+        </is>
+      </c>
+      <c r="C173" s="50" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="D173" s="50" t="inlineStr">
+        <is>
+          <t>robusto</t>
+        </is>
+      </c>
+      <c r="E173" s="50" t="inlineStr">
+        <is>
+          <t>huber_tscv</t>
+        </is>
+      </c>
+      <c r="F173" s="50" t="n">
+        <v>4</v>
+      </c>
+      <c r="G173" s="49" t="inlineStr">
+        <is>
+          <t>nivel</t>
+        </is>
+      </c>
+      <c r="H173" s="50" t="inlineStr">
+        <is>
+          <t>y_t + lags [1, 2, 3, 4]</t>
+        </is>
+      </c>
+      <c r="I173" s="50" t="inlineStr">
+        <is>
+          <t>sentimiento_medios, v5_agua_neto, v5_alumbrado_neto, v5_americo_neto, v5_basura_neto, v5_corrupcion_neto, v5_delitos_neto, v5_morena_neto, v5_obras_neto, v5_prevencion_neto, v5_vialidad_neto</t>
+        </is>
+      </c>
+      <c r="J173" s="50" t="inlineStr">
+        <is>
+          <t>standard_scaler</t>
+        </is>
+      </c>
+      <c r="K173" s="50" t="inlineStr">
+        <is>
+          <t>corr</t>
+        </is>
+      </c>
+      <c r="L173" s="50" t="inlineStr">
+        <is>
+          <t>walk-forward_expanding</t>
+        </is>
+      </c>
+      <c r="M173" s="49" t="inlineStr">
+        <is>
+          <t>2024-10-14 a 2026-03-02</t>
+        </is>
+      </c>
+      <c r="N173" s="49" t="inlineStr">
+        <is>
+          <t>{"feature_candidates": 59, "feature_mode": "corr", "horizon": 4, "initial_train_size": 40, "lags": [1, 2, 3, 4], "model": "huber_tscv", "model_params": {"hypothesis_note": "prueba_sin_memoria_larga", "inner_splits": 3, "param_grid": {"alpha": [1e-06, 9.999999999999999e-06, 0.0001, 0.001, 0.01, 0.1], "epsilon": [1.1, 1.2, 1.35, 1.5, 1.75, 2.0], "max_iter": [1000], "tol": [0.0001]}, "transform_mode": "standard", "tuning_metric": "mae", "winsor_lower_quantile": 0.05, "winsor_upper_quantile": 0.95}, "rows_eval": 25, "rows_modeling": 65, "selected_feature_count_avg": 21.0, "target_mode": "nivel", "transform_mode": "standard"}</t>
+        </is>
+      </c>
+      <c r="O173" s="51" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="P173" s="51" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="Q173" s="51" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="R173" s="51" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="S173" s="52" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="T173" s="53" t="n">
+        <v>0.2331120640375527</v>
+      </c>
+      <c r="U173" s="53" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="V173" s="53" t="n">
+        <v>0.09999999999999998</v>
+      </c>
+      <c r="W173" s="53" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="X173" s="54" t="n">
+        <v>0.03698838336197151</v>
+      </c>
+      <c r="Y173" s="53" t="n">
+        <v>0.1434301389527392</v>
+      </c>
+      <c r="Z173" s="53" t="n">
+        <v>0.167126942327339</v>
+      </c>
+      <c r="AA173" s="55" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="AB173" s="55" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AC173" s="49" t="inlineStr">
+        <is>
+          <t>corrido</t>
+        </is>
+      </c>
+      <c r="AD173" s="49" t="inlineStr">
+        <is>
+          <t>Huber limpio con tuning temporal interno | hipotesis=prueba_sin_memoria_larga | metric=mae | inner_splits=3</t>
+        </is>
+      </c>
+      <c r="AE173" s="49" t="inlineStr">
+        <is>
+          <t>run_e2_huber_clean.py</t>
+        </is>
+      </c>
+      <c r="AF173" s="49" t="inlineStr">
+        <is>
+          <t>Scripts/Modeling/run_e2_huber_clean.py</t>
+        </is>
+      </c>
+      <c r="AG173" s="49" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E2_v3_clean_20260323_061213</t>
+        </is>
+      </c>
+      <c r="AH173" s="49" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E2_v3_clean_20260323_061213/scripts/run_e2_huber_clean.py</t>
+        </is>
+      </c>
+      <c r="AI173" s="49" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E2_v3_clean_20260323_061213/parametros_run.json</t>
+        </is>
+      </c>
+      <c r="AJ173" s="49" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E2_v3_clean_20260323_061213/metricas_horizonte.json</t>
+        </is>
+      </c>
+      <c r="AK173" s="49" t="inlineStr">
+        <is>
+          <t>2026-03-23 06:12:13</t>
         </is>
       </c>
     </row>
@@ -14885,7 +16775,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:W106"/>
+  <dimension ref="A1:W109"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.54296875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="14" customWidth="1" style="26" min="1" max="1"/>
@@ -21634,6 +23524,273 @@
       <c r="W106" s="49" t="inlineStr">
         <is>
           <t>2026-03-21 10:54:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="15" customHeight="1" s="27">
+      <c r="A107" s="49" t="inlineStr">
+        <is>
+          <t>E2_v1_clean</t>
+        </is>
+      </c>
+      <c r="B107" s="57" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="C107" s="57" t="inlineStr">
+        <is>
+          <t>huber_tscv</t>
+        </is>
+      </c>
+      <c r="D107" s="57" t="inlineStr">
+        <is>
+          <t>robusto</t>
+        </is>
+      </c>
+      <c r="E107" s="57" t="n">
+        <v>4</v>
+      </c>
+      <c r="F107" s="54" t="n">
+        <v>0.3019073236793116</v>
+      </c>
+      <c r="G107" s="53" t="n"/>
+      <c r="H107" s="58" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="I107" s="54" t="n">
+        <v>0.3019073236793116</v>
+      </c>
+      <c r="J107" s="54" t="n">
+        <v>0.1466779178135986</v>
+      </c>
+      <c r="K107" s="54" t="n">
+        <v>0.1912880659982875</v>
+      </c>
+      <c r="L107" s="51" t="n">
+        <v>0.6298258082497213</v>
+      </c>
+      <c r="M107" s="51" t="n">
+        <v>0.7267676767676767</v>
+      </c>
+      <c r="N107" s="49" t="n"/>
+      <c r="O107" s="57" t="n"/>
+      <c r="P107" s="49" t="inlineStr">
+        <is>
+          <t>Huber limpio con tuning interno TimeSeriesSplit | metric=mae | L_total_Radar=0.301907</t>
+        </is>
+      </c>
+      <c r="Q107" s="49" t="inlineStr">
+        <is>
+          <t>run_e2_huber_clean.py</t>
+        </is>
+      </c>
+      <c r="R107" s="49" t="inlineStr">
+        <is>
+          <t>Scripts/Modeling/run_e2_huber_clean.py</t>
+        </is>
+      </c>
+      <c r="S107" s="49" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E2_v1_clean_20260323_050029</t>
+        </is>
+      </c>
+      <c r="T107" s="49" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E2_v1_clean_20260323_050029/scripts/run_e2_huber_clean.py</t>
+        </is>
+      </c>
+      <c r="U107" s="49" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E2_v1_clean_20260323_050029/parametros_run.json</t>
+        </is>
+      </c>
+      <c r="V107" s="49" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E2_v1_clean_20260323_050029/metricas_horizonte.json</t>
+        </is>
+      </c>
+      <c r="W107" s="49" t="inlineStr">
+        <is>
+          <t>2026-03-23 05:00:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="15" customHeight="1" s="27">
+      <c r="A108" s="49" t="inlineStr">
+        <is>
+          <t>E2_v2_clean</t>
+        </is>
+      </c>
+      <c r="B108" s="57" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="C108" s="57" t="inlineStr">
+        <is>
+          <t>huber_tscv</t>
+        </is>
+      </c>
+      <c r="D108" s="57" t="inlineStr">
+        <is>
+          <t>robusto</t>
+        </is>
+      </c>
+      <c r="E108" s="57" t="n">
+        <v>4</v>
+      </c>
+      <c r="F108" s="54" t="n">
+        <v>0.3019203219833318</v>
+      </c>
+      <c r="G108" s="53" t="n"/>
+      <c r="H108" s="58" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="I108" s="54" t="n">
+        <v>0.3019203219833318</v>
+      </c>
+      <c r="J108" s="54" t="n">
+        <v>0.1466969598359049</v>
+      </c>
+      <c r="K108" s="54" t="n">
+        <v>0.1912460466605695</v>
+      </c>
+      <c r="L108" s="51" t="n">
+        <v>0.6298258082497213</v>
+      </c>
+      <c r="M108" s="51" t="n">
+        <v>0.7267676767676767</v>
+      </c>
+      <c r="N108" s="49" t="n"/>
+      <c r="O108" s="57" t="n"/>
+      <c r="P108" s="49" t="inlineStr">
+        <is>
+          <t>Huber limpio con tuning interno TimeSeriesSplit | hipotesis=control_de_convergencia | metric=mae | L_total_Radar=0.301920</t>
+        </is>
+      </c>
+      <c r="Q108" s="49" t="inlineStr">
+        <is>
+          <t>run_e2_huber_clean.py</t>
+        </is>
+      </c>
+      <c r="R108" s="49" t="inlineStr">
+        <is>
+          <t>Scripts/Modeling/run_e2_huber_clean.py</t>
+        </is>
+      </c>
+      <c r="S108" s="49" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E2_v2_clean_20260323_054101</t>
+        </is>
+      </c>
+      <c r="T108" s="49" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E2_v2_clean_20260323_054101/scripts/run_e2_huber_clean.py</t>
+        </is>
+      </c>
+      <c r="U108" s="49" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E2_v2_clean_20260323_054101/parametros_run.json</t>
+        </is>
+      </c>
+      <c r="V108" s="49" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E2_v2_clean_20260323_054101/metricas_horizonte.json</t>
+        </is>
+      </c>
+      <c r="W108" s="49" t="inlineStr">
+        <is>
+          <t>2026-03-23 05:41:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="15" customHeight="1" s="27">
+      <c r="A109" s="49" t="inlineStr">
+        <is>
+          <t>E2_v3_clean</t>
+        </is>
+      </c>
+      <c r="B109" s="57" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="C109" s="57" t="inlineStr">
+        <is>
+          <t>huber_tscv</t>
+        </is>
+      </c>
+      <c r="D109" s="57" t="inlineStr">
+        <is>
+          <t>robusto</t>
+        </is>
+      </c>
+      <c r="E109" s="57" t="n">
+        <v>4</v>
+      </c>
+      <c r="F109" s="54" t="n">
+        <v>0.2864645117875421</v>
+      </c>
+      <c r="G109" s="53" t="n"/>
+      <c r="H109" s="58" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="I109" s="54" t="n">
+        <v>0.2864645117875421</v>
+      </c>
+      <c r="J109" s="54" t="n">
+        <v>0.1296620162721482</v>
+      </c>
+      <c r="K109" s="54" t="n">
+        <v>0.157053087857615</v>
+      </c>
+      <c r="L109" s="51" t="n">
+        <v>0.707628205128205</v>
+      </c>
+      <c r="M109" s="51" t="n">
+        <v>0.7698717948717949</v>
+      </c>
+      <c r="N109" s="49" t="n"/>
+      <c r="O109" s="57" t="n"/>
+      <c r="P109" s="49" t="inlineStr">
+        <is>
+          <t>Huber limpio con tuning interno TimeSeriesSplit | hipotesis=prueba_sin_memoria_larga | metric=mae | L_total_Radar=0.286465</t>
+        </is>
+      </c>
+      <c r="Q109" s="49" t="inlineStr">
+        <is>
+          <t>run_e2_huber_clean.py</t>
+        </is>
+      </c>
+      <c r="R109" s="49" t="inlineStr">
+        <is>
+          <t>Scripts/Modeling/run_e2_huber_clean.py</t>
+        </is>
+      </c>
+      <c r="S109" s="49" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E2_v3_clean_20260323_061213</t>
+        </is>
+      </c>
+      <c r="T109" s="49" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E2_v3_clean_20260323_061213/scripts/run_e2_huber_clean.py</t>
+        </is>
+      </c>
+      <c r="U109" s="49" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E2_v3_clean_20260323_061213/parametros_run.json</t>
+        </is>
+      </c>
+      <c r="V109" s="49" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E2_v3_clean_20260323_061213/metricas_horizonte.json</t>
+        </is>
+      </c>
+      <c r="W109" s="49" t="inlineStr">
+        <is>
+          <t>2026-03-23 06:12:13</t>
         </is>
       </c>
     </row>
@@ -21677,7 +23834,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:G72"/>
+  <dimension ref="A1:G119"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.54296875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="26" customWidth="1" style="26" min="1" max="6"/>
@@ -24320,6 +26477,1745 @@
         </is>
       </c>
     </row>
+    <row r="73" ht="15" customHeight="1" s="27">
+      <c r="A73" s="61" t="inlineStr">
+        <is>
+          <t>2026-03-23 05:15:03</t>
+        </is>
+      </c>
+      <c r="B73" s="61" t="inlineStr">
+        <is>
+          <t>E2_v1_clean</t>
+        </is>
+      </c>
+      <c r="C73" s="61" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="D73" s="61" t="inlineStr">
+        <is>
+          <t>script_snapshot</t>
+        </is>
+      </c>
+      <c r="E73" s="61" t="inlineStr">
+        <is>
+          <t>run_e2_huber_clean.py</t>
+        </is>
+      </c>
+      <c r="F73" s="61" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E2_v1_clean_20260323_050029/scripts/run_e2_huber_clean.py</t>
+        </is>
+      </c>
+      <c r="G73" s="61" t="inlineStr">
+        <is>
+          <t>Copia del script ejecutado para reproducibilidad.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="15" customHeight="1" s="27">
+      <c r="A74" s="61" t="inlineStr">
+        <is>
+          <t>2026-03-23 05:15:03</t>
+        </is>
+      </c>
+      <c r="B74" s="61" t="inlineStr">
+        <is>
+          <t>E2_v1_clean</t>
+        </is>
+      </c>
+      <c r="C74" s="61" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="D74" s="61" t="inlineStr">
+        <is>
+          <t>parametros</t>
+        </is>
+      </c>
+      <c r="E74" s="61" t="inlineStr">
+        <is>
+          <t>parametros_run.json</t>
+        </is>
+      </c>
+      <c r="F74" s="61" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E2_v1_clean_20260323_050029/parametros_run.json</t>
+        </is>
+      </c>
+      <c r="G74" s="61" t="inlineStr">
+        <is>
+          <t>Parametros del experimento.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="15" customHeight="1" s="27">
+      <c r="A75" s="61" t="inlineStr">
+        <is>
+          <t>2026-03-23 05:15:03</t>
+        </is>
+      </c>
+      <c r="B75" s="61" t="inlineStr">
+        <is>
+          <t>E2_v1_clean</t>
+        </is>
+      </c>
+      <c r="C75" s="61" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="D75" s="61" t="inlineStr">
+        <is>
+          <t>seleccion_features</t>
+        </is>
+      </c>
+      <c r="E75" s="61" t="inlineStr">
+        <is>
+          <t>features_seleccionadas_h1.csv</t>
+        </is>
+      </c>
+      <c r="F75" s="61" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E2_v1_clean_20260323_050029/features_seleccionadas_h1.csv</t>
+        </is>
+      </c>
+      <c r="G75" s="61" t="inlineStr">
+        <is>
+          <t>Resumen de combinaciones de features seleccionadas por fold externo. El filtro se calcula solo con el train de cada fold externo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="15" customHeight="1" s="27">
+      <c r="A76" s="61" t="inlineStr">
+        <is>
+          <t>2026-03-23 05:15:03</t>
+        </is>
+      </c>
+      <c r="B76" s="61" t="inlineStr">
+        <is>
+          <t>E2_v1_clean</t>
+        </is>
+      </c>
+      <c r="C76" s="61" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="D76" s="61" t="inlineStr">
+        <is>
+          <t>seleccion_features</t>
+        </is>
+      </c>
+      <c r="E76" s="61" t="inlineStr">
+        <is>
+          <t>features_seleccionadas_h2.csv</t>
+        </is>
+      </c>
+      <c r="F76" s="61" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E2_v1_clean_20260323_050029/features_seleccionadas_h2.csv</t>
+        </is>
+      </c>
+      <c r="G76" s="61" t="inlineStr">
+        <is>
+          <t>Resumen de combinaciones de features seleccionadas por fold externo. El filtro se calcula solo con el train de cada fold externo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="15" customHeight="1" s="27">
+      <c r="A77" s="61" t="inlineStr">
+        <is>
+          <t>2026-03-23 05:15:03</t>
+        </is>
+      </c>
+      <c r="B77" s="61" t="inlineStr">
+        <is>
+          <t>E2_v1_clean</t>
+        </is>
+      </c>
+      <c r="C77" s="61" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="D77" s="61" t="inlineStr">
+        <is>
+          <t>seleccion_features</t>
+        </is>
+      </c>
+      <c r="E77" s="61" t="inlineStr">
+        <is>
+          <t>features_seleccionadas_h3.csv</t>
+        </is>
+      </c>
+      <c r="F77" s="61" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E2_v1_clean_20260323_050029/features_seleccionadas_h3.csv</t>
+        </is>
+      </c>
+      <c r="G77" s="61" t="inlineStr">
+        <is>
+          <t>Resumen de combinaciones de features seleccionadas por fold externo. El filtro se calcula solo con el train de cada fold externo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="15" customHeight="1" s="27">
+      <c r="A78" s="61" t="inlineStr">
+        <is>
+          <t>2026-03-23 05:15:03</t>
+        </is>
+      </c>
+      <c r="B78" s="61" t="inlineStr">
+        <is>
+          <t>E2_v1_clean</t>
+        </is>
+      </c>
+      <c r="C78" s="61" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="D78" s="61" t="inlineStr">
+        <is>
+          <t>seleccion_features</t>
+        </is>
+      </c>
+      <c r="E78" s="61" t="inlineStr">
+        <is>
+          <t>features_seleccionadas_h4.csv</t>
+        </is>
+      </c>
+      <c r="F78" s="61" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E2_v1_clean_20260323_050029/features_seleccionadas_h4.csv</t>
+        </is>
+      </c>
+      <c r="G78" s="61" t="inlineStr">
+        <is>
+          <t>Resumen de combinaciones de features seleccionadas por fold externo. El filtro se calcula solo con el train de cada fold externo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="15" customHeight="1" s="27">
+      <c r="A79" s="61" t="inlineStr">
+        <is>
+          <t>2026-03-23 05:15:03</t>
+        </is>
+      </c>
+      <c r="B79" s="61" t="inlineStr">
+        <is>
+          <t>E2_v1_clean</t>
+        </is>
+      </c>
+      <c r="C79" s="61" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="D79" s="61" t="inlineStr">
+        <is>
+          <t>predicciones</t>
+        </is>
+      </c>
+      <c r="E79" s="61" t="inlineStr">
+        <is>
+          <t>predicciones_h1.csv</t>
+        </is>
+      </c>
+      <c r="F79" s="61" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E2_v1_clean_20260323_050029/predicciones_h1.csv</t>
+        </is>
+      </c>
+      <c r="G79" s="61" t="inlineStr">
+        <is>
+          <t>Predicciones walk-forward para horizonte 1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="15" customHeight="1" s="27">
+      <c r="A80" s="61" t="inlineStr">
+        <is>
+          <t>2026-03-23 05:15:03</t>
+        </is>
+      </c>
+      <c r="B80" s="61" t="inlineStr">
+        <is>
+          <t>E2_v1_clean</t>
+        </is>
+      </c>
+      <c r="C80" s="61" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="D80" s="61" t="inlineStr">
+        <is>
+          <t>predicciones</t>
+        </is>
+      </c>
+      <c r="E80" s="61" t="inlineStr">
+        <is>
+          <t>predicciones_h2.csv</t>
+        </is>
+      </c>
+      <c r="F80" s="61" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E2_v1_clean_20260323_050029/predicciones_h2.csv</t>
+        </is>
+      </c>
+      <c r="G80" s="61" t="inlineStr">
+        <is>
+          <t>Predicciones walk-forward para horizonte 2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="15" customHeight="1" s="27">
+      <c r="A81" s="61" t="inlineStr">
+        <is>
+          <t>2026-03-23 05:15:03</t>
+        </is>
+      </c>
+      <c r="B81" s="61" t="inlineStr">
+        <is>
+          <t>E2_v1_clean</t>
+        </is>
+      </c>
+      <c r="C81" s="61" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="D81" s="61" t="inlineStr">
+        <is>
+          <t>predicciones</t>
+        </is>
+      </c>
+      <c r="E81" s="61" t="inlineStr">
+        <is>
+          <t>predicciones_h3.csv</t>
+        </is>
+      </c>
+      <c r="F81" s="61" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E2_v1_clean_20260323_050029/predicciones_h3.csv</t>
+        </is>
+      </c>
+      <c r="G81" s="61" t="inlineStr">
+        <is>
+          <t>Predicciones walk-forward para horizonte 3.</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="15" customHeight="1" s="27">
+      <c r="A82" s="61" t="inlineStr">
+        <is>
+          <t>2026-03-23 05:15:03</t>
+        </is>
+      </c>
+      <c r="B82" s="61" t="inlineStr">
+        <is>
+          <t>E2_v1_clean</t>
+        </is>
+      </c>
+      <c r="C82" s="61" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="D82" s="61" t="inlineStr">
+        <is>
+          <t>predicciones</t>
+        </is>
+      </c>
+      <c r="E82" s="61" t="inlineStr">
+        <is>
+          <t>predicciones_h4.csv</t>
+        </is>
+      </c>
+      <c r="F82" s="61" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E2_v1_clean_20260323_050029/predicciones_h4.csv</t>
+        </is>
+      </c>
+      <c r="G82" s="61" t="inlineStr">
+        <is>
+          <t>Predicciones walk-forward para horizonte 4.</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="15" customHeight="1" s="27">
+      <c r="A83" s="61" t="inlineStr">
+        <is>
+          <t>2026-03-23 05:15:03</t>
+        </is>
+      </c>
+      <c r="B83" s="61" t="inlineStr">
+        <is>
+          <t>E2_v1_clean</t>
+        </is>
+      </c>
+      <c r="C83" s="61" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="D83" s="61" t="inlineStr">
+        <is>
+          <t>resumen</t>
+        </is>
+      </c>
+      <c r="E83" s="61" t="inlineStr">
+        <is>
+          <t>resumen_modeling_horizontes.json</t>
+        </is>
+      </c>
+      <c r="F83" s="61" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E2_v1_clean_20260323_050029/resumen_modeling_horizontes.json</t>
+        </is>
+      </c>
+      <c r="G83" s="61" t="inlineStr">
+        <is>
+          <t>Resumen de tamanos y seleccion de features por horizonte.</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="15" customHeight="1" s="27">
+      <c r="A84" s="61" t="inlineStr">
+        <is>
+          <t>2026-03-23 05:15:03</t>
+        </is>
+      </c>
+      <c r="B84" s="61" t="inlineStr">
+        <is>
+          <t>E2_v1_clean</t>
+        </is>
+      </c>
+      <c r="C84" s="61" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="D84" s="61" t="inlineStr">
+        <is>
+          <t>tuning</t>
+        </is>
+      </c>
+      <c r="E84" s="61" t="inlineStr">
+        <is>
+          <t>huber_tuning_horizontes.json</t>
+        </is>
+      </c>
+      <c r="F84" s="61" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E2_v1_clean_20260323_050029/huber_tuning_horizontes.json</t>
+        </is>
+      </c>
+      <c r="G84" s="61" t="inlineStr">
+        <is>
+          <t>Mejores hiperparametros Huber por fold externo y resumen por horizonte.</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="15" customHeight="1" s="27">
+      <c r="A85" s="61" t="inlineStr">
+        <is>
+          <t>2026-03-23 05:15:03</t>
+        </is>
+      </c>
+      <c r="B85" s="61" t="inlineStr">
+        <is>
+          <t>E2_v1_clean</t>
+        </is>
+      </c>
+      <c r="C85" s="61" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="D85" s="61" t="inlineStr">
+        <is>
+          <t>comparacion</t>
+        </is>
+      </c>
+      <c r="E85" s="61" t="inlineStr">
+        <is>
+          <t>comparacion_vs_E1_v5_clean.json</t>
+        </is>
+      </c>
+      <c r="F85" s="61" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E2_v1_clean_20260323_050029/comparacion_vs_E1_v5_clean.json</t>
+        </is>
+      </c>
+      <c r="G85" s="61" t="inlineStr">
+        <is>
+          <t>Comparacion de la corrida clean contra E1_v5_clean.</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="15" customHeight="1" s="27">
+      <c r="A86" s="61" t="inlineStr">
+        <is>
+          <t>2026-03-23 05:15:03</t>
+        </is>
+      </c>
+      <c r="B86" s="61" t="inlineStr">
+        <is>
+          <t>E2_v1_clean</t>
+        </is>
+      </c>
+      <c r="C86" s="61" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="D86" s="61" t="inlineStr">
+        <is>
+          <t>metricas</t>
+        </is>
+      </c>
+      <c r="E86" s="61" t="inlineStr">
+        <is>
+          <t>metricas_horizonte.json</t>
+        </is>
+      </c>
+      <c r="F86" s="61" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E2_v1_clean_20260323_050029/metricas_horizonte.json</t>
+        </is>
+      </c>
+      <c r="G86" s="61" t="inlineStr">
+        <is>
+          <t>Resumen estructurado por horizonte.</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="15" customHeight="1" s="27">
+      <c r="A87" s="61" t="inlineStr">
+        <is>
+          <t>2026-03-23 05:15:03</t>
+        </is>
+      </c>
+      <c r="B87" s="61" t="inlineStr">
+        <is>
+          <t>E2_v1_clean</t>
+        </is>
+      </c>
+      <c r="C87" s="61" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="D87" s="61" t="inlineStr">
+        <is>
+          <t>metadata</t>
+        </is>
+      </c>
+      <c r="E87" s="61" t="inlineStr">
+        <is>
+          <t>metadata_run.json</t>
+        </is>
+      </c>
+      <c r="F87" s="61" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E2_v1_clean_20260323_050029/metadata_run.json</t>
+        </is>
+      </c>
+      <c r="G87" s="61" t="inlineStr">
+        <is>
+          <t>Metadata base del run.</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="15" customHeight="1" s="27">
+      <c r="A88" s="61" t="inlineStr">
+        <is>
+          <t>2026-03-23 06:10:23</t>
+        </is>
+      </c>
+      <c r="B88" s="61" t="inlineStr">
+        <is>
+          <t>E2_v2_clean</t>
+        </is>
+      </c>
+      <c r="C88" s="61" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="D88" s="61" t="inlineStr">
+        <is>
+          <t>script_snapshot</t>
+        </is>
+      </c>
+      <c r="E88" s="61" t="inlineStr">
+        <is>
+          <t>run_e2_huber_clean.py</t>
+        </is>
+      </c>
+      <c r="F88" s="61" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E2_v2_clean_20260323_054101/scripts/run_e2_huber_clean.py</t>
+        </is>
+      </c>
+      <c r="G88" s="61" t="inlineStr">
+        <is>
+          <t>Copia del script ejecutado para reproducibilidad.</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="15" customHeight="1" s="27">
+      <c r="A89" s="61" t="inlineStr">
+        <is>
+          <t>2026-03-23 06:10:23</t>
+        </is>
+      </c>
+      <c r="B89" s="61" t="inlineStr">
+        <is>
+          <t>E2_v2_clean</t>
+        </is>
+      </c>
+      <c r="C89" s="61" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="D89" s="61" t="inlineStr">
+        <is>
+          <t>parametros</t>
+        </is>
+      </c>
+      <c r="E89" s="61" t="inlineStr">
+        <is>
+          <t>parametros_run.json</t>
+        </is>
+      </c>
+      <c r="F89" s="61" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E2_v2_clean_20260323_054101/parametros_run.json</t>
+        </is>
+      </c>
+      <c r="G89" s="61" t="inlineStr">
+        <is>
+          <t>Parametros del experimento.</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="15" customHeight="1" s="27">
+      <c r="A90" s="61" t="inlineStr">
+        <is>
+          <t>2026-03-23 06:10:23</t>
+        </is>
+      </c>
+      <c r="B90" s="61" t="inlineStr">
+        <is>
+          <t>E2_v2_clean</t>
+        </is>
+      </c>
+      <c r="C90" s="61" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="D90" s="61" t="inlineStr">
+        <is>
+          <t>seleccion_features</t>
+        </is>
+      </c>
+      <c r="E90" s="61" t="inlineStr">
+        <is>
+          <t>features_seleccionadas_h1.csv</t>
+        </is>
+      </c>
+      <c r="F90" s="61" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E2_v2_clean_20260323_054101/features_seleccionadas_h1.csv</t>
+        </is>
+      </c>
+      <c r="G90" s="61" t="inlineStr">
+        <is>
+          <t>Resumen de combinaciones de features seleccionadas por fold externo. El filtro se calcula solo con el train de cada fold externo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="15" customHeight="1" s="27">
+      <c r="A91" s="61" t="inlineStr">
+        <is>
+          <t>2026-03-23 06:10:23</t>
+        </is>
+      </c>
+      <c r="B91" s="61" t="inlineStr">
+        <is>
+          <t>E2_v2_clean</t>
+        </is>
+      </c>
+      <c r="C91" s="61" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="D91" s="61" t="inlineStr">
+        <is>
+          <t>seleccion_features</t>
+        </is>
+      </c>
+      <c r="E91" s="61" t="inlineStr">
+        <is>
+          <t>features_seleccionadas_h2.csv</t>
+        </is>
+      </c>
+      <c r="F91" s="61" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E2_v2_clean_20260323_054101/features_seleccionadas_h2.csv</t>
+        </is>
+      </c>
+      <c r="G91" s="61" t="inlineStr">
+        <is>
+          <t>Resumen de combinaciones de features seleccionadas por fold externo. El filtro se calcula solo con el train de cada fold externo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="15" customHeight="1" s="27">
+      <c r="A92" s="61" t="inlineStr">
+        <is>
+          <t>2026-03-23 06:10:23</t>
+        </is>
+      </c>
+      <c r="B92" s="61" t="inlineStr">
+        <is>
+          <t>E2_v2_clean</t>
+        </is>
+      </c>
+      <c r="C92" s="61" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="D92" s="61" t="inlineStr">
+        <is>
+          <t>seleccion_features</t>
+        </is>
+      </c>
+      <c r="E92" s="61" t="inlineStr">
+        <is>
+          <t>features_seleccionadas_h3.csv</t>
+        </is>
+      </c>
+      <c r="F92" s="61" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E2_v2_clean_20260323_054101/features_seleccionadas_h3.csv</t>
+        </is>
+      </c>
+      <c r="G92" s="61" t="inlineStr">
+        <is>
+          <t>Resumen de combinaciones de features seleccionadas por fold externo. El filtro se calcula solo con el train de cada fold externo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="15" customHeight="1" s="27">
+      <c r="A93" s="61" t="inlineStr">
+        <is>
+          <t>2026-03-23 06:10:23</t>
+        </is>
+      </c>
+      <c r="B93" s="61" t="inlineStr">
+        <is>
+          <t>E2_v2_clean</t>
+        </is>
+      </c>
+      <c r="C93" s="61" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="D93" s="61" t="inlineStr">
+        <is>
+          <t>seleccion_features</t>
+        </is>
+      </c>
+      <c r="E93" s="61" t="inlineStr">
+        <is>
+          <t>features_seleccionadas_h4.csv</t>
+        </is>
+      </c>
+      <c r="F93" s="61" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E2_v2_clean_20260323_054101/features_seleccionadas_h4.csv</t>
+        </is>
+      </c>
+      <c r="G93" s="61" t="inlineStr">
+        <is>
+          <t>Resumen de combinaciones de features seleccionadas por fold externo. El filtro se calcula solo con el train de cada fold externo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="15" customHeight="1" s="27">
+      <c r="A94" s="61" t="inlineStr">
+        <is>
+          <t>2026-03-23 06:10:23</t>
+        </is>
+      </c>
+      <c r="B94" s="61" t="inlineStr">
+        <is>
+          <t>E2_v2_clean</t>
+        </is>
+      </c>
+      <c r="C94" s="61" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="D94" s="61" t="inlineStr">
+        <is>
+          <t>predicciones</t>
+        </is>
+      </c>
+      <c r="E94" s="61" t="inlineStr">
+        <is>
+          <t>predicciones_h1.csv</t>
+        </is>
+      </c>
+      <c r="F94" s="61" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E2_v2_clean_20260323_054101/predicciones_h1.csv</t>
+        </is>
+      </c>
+      <c r="G94" s="61" t="inlineStr">
+        <is>
+          <t>Predicciones walk-forward para horizonte 1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="15" customHeight="1" s="27">
+      <c r="A95" s="61" t="inlineStr">
+        <is>
+          <t>2026-03-23 06:10:23</t>
+        </is>
+      </c>
+      <c r="B95" s="61" t="inlineStr">
+        <is>
+          <t>E2_v2_clean</t>
+        </is>
+      </c>
+      <c r="C95" s="61" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="D95" s="61" t="inlineStr">
+        <is>
+          <t>predicciones</t>
+        </is>
+      </c>
+      <c r="E95" s="61" t="inlineStr">
+        <is>
+          <t>predicciones_h2.csv</t>
+        </is>
+      </c>
+      <c r="F95" s="61" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E2_v2_clean_20260323_054101/predicciones_h2.csv</t>
+        </is>
+      </c>
+      <c r="G95" s="61" t="inlineStr">
+        <is>
+          <t>Predicciones walk-forward para horizonte 2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="15" customHeight="1" s="27">
+      <c r="A96" s="61" t="inlineStr">
+        <is>
+          <t>2026-03-23 06:10:23</t>
+        </is>
+      </c>
+      <c r="B96" s="61" t="inlineStr">
+        <is>
+          <t>E2_v2_clean</t>
+        </is>
+      </c>
+      <c r="C96" s="61" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="D96" s="61" t="inlineStr">
+        <is>
+          <t>predicciones</t>
+        </is>
+      </c>
+      <c r="E96" s="61" t="inlineStr">
+        <is>
+          <t>predicciones_h3.csv</t>
+        </is>
+      </c>
+      <c r="F96" s="61" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E2_v2_clean_20260323_054101/predicciones_h3.csv</t>
+        </is>
+      </c>
+      <c r="G96" s="61" t="inlineStr">
+        <is>
+          <t>Predicciones walk-forward para horizonte 3.</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="15" customHeight="1" s="27">
+      <c r="A97" s="61" t="inlineStr">
+        <is>
+          <t>2026-03-23 06:10:23</t>
+        </is>
+      </c>
+      <c r="B97" s="61" t="inlineStr">
+        <is>
+          <t>E2_v2_clean</t>
+        </is>
+      </c>
+      <c r="C97" s="61" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="D97" s="61" t="inlineStr">
+        <is>
+          <t>predicciones</t>
+        </is>
+      </c>
+      <c r="E97" s="61" t="inlineStr">
+        <is>
+          <t>predicciones_h4.csv</t>
+        </is>
+      </c>
+      <c r="F97" s="61" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E2_v2_clean_20260323_054101/predicciones_h4.csv</t>
+        </is>
+      </c>
+      <c r="G97" s="61" t="inlineStr">
+        <is>
+          <t>Predicciones walk-forward para horizonte 4.</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="15" customHeight="1" s="27">
+      <c r="A98" s="61" t="inlineStr">
+        <is>
+          <t>2026-03-23 06:10:23</t>
+        </is>
+      </c>
+      <c r="B98" s="61" t="inlineStr">
+        <is>
+          <t>E2_v2_clean</t>
+        </is>
+      </c>
+      <c r="C98" s="61" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="D98" s="61" t="inlineStr">
+        <is>
+          <t>resumen</t>
+        </is>
+      </c>
+      <c r="E98" s="61" t="inlineStr">
+        <is>
+          <t>resumen_modeling_horizontes.json</t>
+        </is>
+      </c>
+      <c r="F98" s="61" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E2_v2_clean_20260323_054101/resumen_modeling_horizontes.json</t>
+        </is>
+      </c>
+      <c r="G98" s="61" t="inlineStr">
+        <is>
+          <t>Resumen de tamanos y seleccion de features por horizonte.</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="15" customHeight="1" s="27">
+      <c r="A99" s="61" t="inlineStr">
+        <is>
+          <t>2026-03-23 06:10:23</t>
+        </is>
+      </c>
+      <c r="B99" s="61" t="inlineStr">
+        <is>
+          <t>E2_v2_clean</t>
+        </is>
+      </c>
+      <c r="C99" s="61" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="D99" s="61" t="inlineStr">
+        <is>
+          <t>tuning</t>
+        </is>
+      </c>
+      <c r="E99" s="61" t="inlineStr">
+        <is>
+          <t>huber_tuning_horizontes.json</t>
+        </is>
+      </c>
+      <c r="F99" s="61" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E2_v2_clean_20260323_054101/huber_tuning_horizontes.json</t>
+        </is>
+      </c>
+      <c r="G99" s="61" t="inlineStr">
+        <is>
+          <t>Mejores hiperparametros Huber por fold externo y resumen por horizonte.</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="15" customHeight="1" s="27">
+      <c r="A100" s="61" t="inlineStr">
+        <is>
+          <t>2026-03-23 06:10:23</t>
+        </is>
+      </c>
+      <c r="B100" s="61" t="inlineStr">
+        <is>
+          <t>E2_v2_clean</t>
+        </is>
+      </c>
+      <c r="C100" s="61" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="D100" s="61" t="inlineStr">
+        <is>
+          <t>comparacion</t>
+        </is>
+      </c>
+      <c r="E100" s="61" t="inlineStr">
+        <is>
+          <t>comparacion_vs_E1_v5_clean.json</t>
+        </is>
+      </c>
+      <c r="F100" s="61" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E2_v2_clean_20260323_054101/comparacion_vs_E1_v5_clean.json</t>
+        </is>
+      </c>
+      <c r="G100" s="61" t="inlineStr">
+        <is>
+          <t>Comparacion de la corrida clean contra E1_v5_clean.</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="15" customHeight="1" s="27">
+      <c r="A101" s="61" t="inlineStr">
+        <is>
+          <t>2026-03-23 06:10:23</t>
+        </is>
+      </c>
+      <c r="B101" s="61" t="inlineStr">
+        <is>
+          <t>E2_v2_clean</t>
+        </is>
+      </c>
+      <c r="C101" s="61" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="D101" s="61" t="inlineStr">
+        <is>
+          <t>comparacion</t>
+        </is>
+      </c>
+      <c r="E101" s="61" t="inlineStr">
+        <is>
+          <t>comparacion_vs_E2_v1_clean.json</t>
+        </is>
+      </c>
+      <c r="F101" s="61" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E2_v2_clean_20260323_054101/comparacion_vs_E2_v1_clean.json</t>
+        </is>
+      </c>
+      <c r="G101" s="61" t="inlineStr">
+        <is>
+          <t>Comparacion de la corrida clean contra E2_v1_clean.</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="15" customHeight="1" s="27">
+      <c r="A102" s="61" t="inlineStr">
+        <is>
+          <t>2026-03-23 06:10:23</t>
+        </is>
+      </c>
+      <c r="B102" s="61" t="inlineStr">
+        <is>
+          <t>E2_v2_clean</t>
+        </is>
+      </c>
+      <c r="C102" s="61" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="D102" s="61" t="inlineStr">
+        <is>
+          <t>metricas</t>
+        </is>
+      </c>
+      <c r="E102" s="61" t="inlineStr">
+        <is>
+          <t>metricas_horizonte.json</t>
+        </is>
+      </c>
+      <c r="F102" s="61" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E2_v2_clean_20260323_054101/metricas_horizonte.json</t>
+        </is>
+      </c>
+      <c r="G102" s="61" t="inlineStr">
+        <is>
+          <t>Resumen estructurado por horizonte.</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="15" customHeight="1" s="27">
+      <c r="A103" s="61" t="inlineStr">
+        <is>
+          <t>2026-03-23 06:10:23</t>
+        </is>
+      </c>
+      <c r="B103" s="61" t="inlineStr">
+        <is>
+          <t>E2_v2_clean</t>
+        </is>
+      </c>
+      <c r="C103" s="61" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="D103" s="61" t="inlineStr">
+        <is>
+          <t>metadata</t>
+        </is>
+      </c>
+      <c r="E103" s="61" t="inlineStr">
+        <is>
+          <t>metadata_run.json</t>
+        </is>
+      </c>
+      <c r="F103" s="61" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E2_v2_clean_20260323_054101/metadata_run.json</t>
+        </is>
+      </c>
+      <c r="G103" s="61" t="inlineStr">
+        <is>
+          <t>Metadata base del run.</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="15" customHeight="1" s="27">
+      <c r="A104" s="61" t="inlineStr">
+        <is>
+          <t>2026-03-23 06:22:49</t>
+        </is>
+      </c>
+      <c r="B104" s="61" t="inlineStr">
+        <is>
+          <t>E2_v3_clean</t>
+        </is>
+      </c>
+      <c r="C104" s="61" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="D104" s="61" t="inlineStr">
+        <is>
+          <t>script_snapshot</t>
+        </is>
+      </c>
+      <c r="E104" s="61" t="inlineStr">
+        <is>
+          <t>run_e2_huber_clean.py</t>
+        </is>
+      </c>
+      <c r="F104" s="61" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E2_v3_clean_20260323_061213/scripts/run_e2_huber_clean.py</t>
+        </is>
+      </c>
+      <c r="G104" s="61" t="inlineStr">
+        <is>
+          <t>Copia del script ejecutado para reproducibilidad.</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="15" customHeight="1" s="27">
+      <c r="A105" s="61" t="inlineStr">
+        <is>
+          <t>2026-03-23 06:22:49</t>
+        </is>
+      </c>
+      <c r="B105" s="61" t="inlineStr">
+        <is>
+          <t>E2_v3_clean</t>
+        </is>
+      </c>
+      <c r="C105" s="61" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="D105" s="61" t="inlineStr">
+        <is>
+          <t>parametros</t>
+        </is>
+      </c>
+      <c r="E105" s="61" t="inlineStr">
+        <is>
+          <t>parametros_run.json</t>
+        </is>
+      </c>
+      <c r="F105" s="61" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E2_v3_clean_20260323_061213/parametros_run.json</t>
+        </is>
+      </c>
+      <c r="G105" s="61" t="inlineStr">
+        <is>
+          <t>Parametros del experimento.</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="15" customHeight="1" s="27">
+      <c r="A106" s="61" t="inlineStr">
+        <is>
+          <t>2026-03-23 06:22:49</t>
+        </is>
+      </c>
+      <c r="B106" s="61" t="inlineStr">
+        <is>
+          <t>E2_v3_clean</t>
+        </is>
+      </c>
+      <c r="C106" s="61" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="D106" s="61" t="inlineStr">
+        <is>
+          <t>seleccion_features</t>
+        </is>
+      </c>
+      <c r="E106" s="61" t="inlineStr">
+        <is>
+          <t>features_seleccionadas_h1.csv</t>
+        </is>
+      </c>
+      <c r="F106" s="61" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E2_v3_clean_20260323_061213/features_seleccionadas_h1.csv</t>
+        </is>
+      </c>
+      <c r="G106" s="61" t="inlineStr">
+        <is>
+          <t>Resumen de combinaciones de features seleccionadas por fold externo. El filtro se calcula solo con el train de cada fold externo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="15" customHeight="1" s="27">
+      <c r="A107" s="61" t="inlineStr">
+        <is>
+          <t>2026-03-23 06:22:49</t>
+        </is>
+      </c>
+      <c r="B107" s="61" t="inlineStr">
+        <is>
+          <t>E2_v3_clean</t>
+        </is>
+      </c>
+      <c r="C107" s="61" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="D107" s="61" t="inlineStr">
+        <is>
+          <t>seleccion_features</t>
+        </is>
+      </c>
+      <c r="E107" s="61" t="inlineStr">
+        <is>
+          <t>features_seleccionadas_h2.csv</t>
+        </is>
+      </c>
+      <c r="F107" s="61" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E2_v3_clean_20260323_061213/features_seleccionadas_h2.csv</t>
+        </is>
+      </c>
+      <c r="G107" s="61" t="inlineStr">
+        <is>
+          <t>Resumen de combinaciones de features seleccionadas por fold externo. El filtro se calcula solo con el train de cada fold externo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="15" customHeight="1" s="27">
+      <c r="A108" s="61" t="inlineStr">
+        <is>
+          <t>2026-03-23 06:22:49</t>
+        </is>
+      </c>
+      <c r="B108" s="61" t="inlineStr">
+        <is>
+          <t>E2_v3_clean</t>
+        </is>
+      </c>
+      <c r="C108" s="61" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="D108" s="61" t="inlineStr">
+        <is>
+          <t>seleccion_features</t>
+        </is>
+      </c>
+      <c r="E108" s="61" t="inlineStr">
+        <is>
+          <t>features_seleccionadas_h3.csv</t>
+        </is>
+      </c>
+      <c r="F108" s="61" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E2_v3_clean_20260323_061213/features_seleccionadas_h3.csv</t>
+        </is>
+      </c>
+      <c r="G108" s="61" t="inlineStr">
+        <is>
+          <t>Resumen de combinaciones de features seleccionadas por fold externo. El filtro se calcula solo con el train de cada fold externo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="15" customHeight="1" s="27">
+      <c r="A109" s="61" t="inlineStr">
+        <is>
+          <t>2026-03-23 06:22:49</t>
+        </is>
+      </c>
+      <c r="B109" s="61" t="inlineStr">
+        <is>
+          <t>E2_v3_clean</t>
+        </is>
+      </c>
+      <c r="C109" s="61" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="D109" s="61" t="inlineStr">
+        <is>
+          <t>seleccion_features</t>
+        </is>
+      </c>
+      <c r="E109" s="61" t="inlineStr">
+        <is>
+          <t>features_seleccionadas_h4.csv</t>
+        </is>
+      </c>
+      <c r="F109" s="61" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E2_v3_clean_20260323_061213/features_seleccionadas_h4.csv</t>
+        </is>
+      </c>
+      <c r="G109" s="61" t="inlineStr">
+        <is>
+          <t>Resumen de combinaciones de features seleccionadas por fold externo. El filtro se calcula solo con el train de cada fold externo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="15" customHeight="1" s="27">
+      <c r="A110" s="61" t="inlineStr">
+        <is>
+          <t>2026-03-23 06:22:49</t>
+        </is>
+      </c>
+      <c r="B110" s="61" t="inlineStr">
+        <is>
+          <t>E2_v3_clean</t>
+        </is>
+      </c>
+      <c r="C110" s="61" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="D110" s="61" t="inlineStr">
+        <is>
+          <t>predicciones</t>
+        </is>
+      </c>
+      <c r="E110" s="61" t="inlineStr">
+        <is>
+          <t>predicciones_h1.csv</t>
+        </is>
+      </c>
+      <c r="F110" s="61" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E2_v3_clean_20260323_061213/predicciones_h1.csv</t>
+        </is>
+      </c>
+      <c r="G110" s="61" t="inlineStr">
+        <is>
+          <t>Predicciones walk-forward para horizonte 1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="15" customHeight="1" s="27">
+      <c r="A111" s="61" t="inlineStr">
+        <is>
+          <t>2026-03-23 06:22:49</t>
+        </is>
+      </c>
+      <c r="B111" s="61" t="inlineStr">
+        <is>
+          <t>E2_v3_clean</t>
+        </is>
+      </c>
+      <c r="C111" s="61" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="D111" s="61" t="inlineStr">
+        <is>
+          <t>predicciones</t>
+        </is>
+      </c>
+      <c r="E111" s="61" t="inlineStr">
+        <is>
+          <t>predicciones_h2.csv</t>
+        </is>
+      </c>
+      <c r="F111" s="61" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E2_v3_clean_20260323_061213/predicciones_h2.csv</t>
+        </is>
+      </c>
+      <c r="G111" s="61" t="inlineStr">
+        <is>
+          <t>Predicciones walk-forward para horizonte 2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="15" customHeight="1" s="27">
+      <c r="A112" s="61" t="inlineStr">
+        <is>
+          <t>2026-03-23 06:22:49</t>
+        </is>
+      </c>
+      <c r="B112" s="61" t="inlineStr">
+        <is>
+          <t>E2_v3_clean</t>
+        </is>
+      </c>
+      <c r="C112" s="61" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="D112" s="61" t="inlineStr">
+        <is>
+          <t>predicciones</t>
+        </is>
+      </c>
+      <c r="E112" s="61" t="inlineStr">
+        <is>
+          <t>predicciones_h3.csv</t>
+        </is>
+      </c>
+      <c r="F112" s="61" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E2_v3_clean_20260323_061213/predicciones_h3.csv</t>
+        </is>
+      </c>
+      <c r="G112" s="61" t="inlineStr">
+        <is>
+          <t>Predicciones walk-forward para horizonte 3.</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" ht="15" customHeight="1" s="27">
+      <c r="A113" s="61" t="inlineStr">
+        <is>
+          <t>2026-03-23 06:22:49</t>
+        </is>
+      </c>
+      <c r="B113" s="61" t="inlineStr">
+        <is>
+          <t>E2_v3_clean</t>
+        </is>
+      </c>
+      <c r="C113" s="61" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="D113" s="61" t="inlineStr">
+        <is>
+          <t>predicciones</t>
+        </is>
+      </c>
+      <c r="E113" s="61" t="inlineStr">
+        <is>
+          <t>predicciones_h4.csv</t>
+        </is>
+      </c>
+      <c r="F113" s="61" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E2_v3_clean_20260323_061213/predicciones_h4.csv</t>
+        </is>
+      </c>
+      <c r="G113" s="61" t="inlineStr">
+        <is>
+          <t>Predicciones walk-forward para horizonte 4.</t>
+        </is>
+      </c>
+    </row>
+    <row r="114" ht="15" customHeight="1" s="27">
+      <c r="A114" s="61" t="inlineStr">
+        <is>
+          <t>2026-03-23 06:22:49</t>
+        </is>
+      </c>
+      <c r="B114" s="61" t="inlineStr">
+        <is>
+          <t>E2_v3_clean</t>
+        </is>
+      </c>
+      <c r="C114" s="61" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="D114" s="61" t="inlineStr">
+        <is>
+          <t>resumen</t>
+        </is>
+      </c>
+      <c r="E114" s="61" t="inlineStr">
+        <is>
+          <t>resumen_modeling_horizontes.json</t>
+        </is>
+      </c>
+      <c r="F114" s="61" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E2_v3_clean_20260323_061213/resumen_modeling_horizontes.json</t>
+        </is>
+      </c>
+      <c r="G114" s="61" t="inlineStr">
+        <is>
+          <t>Resumen de tamanos y seleccion de features por horizonte.</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" ht="15" customHeight="1" s="27">
+      <c r="A115" s="61" t="inlineStr">
+        <is>
+          <t>2026-03-23 06:22:49</t>
+        </is>
+      </c>
+      <c r="B115" s="61" t="inlineStr">
+        <is>
+          <t>E2_v3_clean</t>
+        </is>
+      </c>
+      <c r="C115" s="61" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="D115" s="61" t="inlineStr">
+        <is>
+          <t>tuning</t>
+        </is>
+      </c>
+      <c r="E115" s="61" t="inlineStr">
+        <is>
+          <t>huber_tuning_horizontes.json</t>
+        </is>
+      </c>
+      <c r="F115" s="61" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E2_v3_clean_20260323_061213/huber_tuning_horizontes.json</t>
+        </is>
+      </c>
+      <c r="G115" s="61" t="inlineStr">
+        <is>
+          <t>Mejores hiperparametros Huber por fold externo y resumen por horizonte.</t>
+        </is>
+      </c>
+    </row>
+    <row r="116" ht="15" customHeight="1" s="27">
+      <c r="A116" s="61" t="inlineStr">
+        <is>
+          <t>2026-03-23 06:22:49</t>
+        </is>
+      </c>
+      <c r="B116" s="61" t="inlineStr">
+        <is>
+          <t>E2_v3_clean</t>
+        </is>
+      </c>
+      <c r="C116" s="61" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="D116" s="61" t="inlineStr">
+        <is>
+          <t>comparacion</t>
+        </is>
+      </c>
+      <c r="E116" s="61" t="inlineStr">
+        <is>
+          <t>comparacion_vs_E1_v5_clean.json</t>
+        </is>
+      </c>
+      <c r="F116" s="61" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E2_v3_clean_20260323_061213/comparacion_vs_E1_v5_clean.json</t>
+        </is>
+      </c>
+      <c r="G116" s="61" t="inlineStr">
+        <is>
+          <t>Comparacion de la corrida clean contra E1_v5_clean.</t>
+        </is>
+      </c>
+    </row>
+    <row r="117" ht="15" customHeight="1" s="27">
+      <c r="A117" s="61" t="inlineStr">
+        <is>
+          <t>2026-03-23 06:22:49</t>
+        </is>
+      </c>
+      <c r="B117" s="61" t="inlineStr">
+        <is>
+          <t>E2_v3_clean</t>
+        </is>
+      </c>
+      <c r="C117" s="61" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="D117" s="61" t="inlineStr">
+        <is>
+          <t>comparacion</t>
+        </is>
+      </c>
+      <c r="E117" s="61" t="inlineStr">
+        <is>
+          <t>comparacion_vs_E2_v1_clean.json</t>
+        </is>
+      </c>
+      <c r="F117" s="61" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E2_v3_clean_20260323_061213/comparacion_vs_E2_v1_clean.json</t>
+        </is>
+      </c>
+      <c r="G117" s="61" t="inlineStr">
+        <is>
+          <t>Comparacion de la corrida clean contra E2_v1_clean.</t>
+        </is>
+      </c>
+    </row>
+    <row r="118" ht="15" customHeight="1" s="27">
+      <c r="A118" s="61" t="inlineStr">
+        <is>
+          <t>2026-03-23 06:22:49</t>
+        </is>
+      </c>
+      <c r="B118" s="61" t="inlineStr">
+        <is>
+          <t>E2_v3_clean</t>
+        </is>
+      </c>
+      <c r="C118" s="61" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="D118" s="61" t="inlineStr">
+        <is>
+          <t>metricas</t>
+        </is>
+      </c>
+      <c r="E118" s="61" t="inlineStr">
+        <is>
+          <t>metricas_horizonte.json</t>
+        </is>
+      </c>
+      <c r="F118" s="61" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E2_v3_clean_20260323_061213/metricas_horizonte.json</t>
+        </is>
+      </c>
+      <c r="G118" s="61" t="inlineStr">
+        <is>
+          <t>Resumen estructurado por horizonte.</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" ht="15" customHeight="1" s="27">
+      <c r="A119" s="61" t="inlineStr">
+        <is>
+          <t>2026-03-23 06:22:49</t>
+        </is>
+      </c>
+      <c r="B119" s="61" t="inlineStr">
+        <is>
+          <t>E2_v3_clean</t>
+        </is>
+      </c>
+      <c r="C119" s="61" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="D119" s="61" t="inlineStr">
+        <is>
+          <t>metadata</t>
+        </is>
+      </c>
+      <c r="E119" s="61" t="inlineStr">
+        <is>
+          <t>metadata_run.json</t>
+        </is>
+      </c>
+      <c r="F119" s="61" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E2_v3_clean_20260323_061213/metadata_run.json</t>
+        </is>
+      </c>
+      <c r="G119" s="61" t="inlineStr">
+        <is>
+          <t>Metadata base del run.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>

--- a/Experimentos/grid_experimentos_radar.xlsx
+++ b/Experimentos/grid_experimentos_radar.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="3" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CONFIG_REFERENCIA" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CATALOGO_EXPERIMENTOS" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RESULTADOS_GRID" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RUN_SUMMARY" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RUN_ARTEFACTOS" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="CONFIG_REFERENCIA" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="CATALOGO_EXPERIMENTOS" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="RESULTADOS_GRID" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="RUN_SUMMARY" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="RUN_ARTEFACTOS" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" calcMode="auto" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.001" forceFullCalc="1"/>
@@ -746,7 +746,7 @@
       </c>
     </row>
     <row r="16" ht="19.5" customHeight="1" s="27">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="26" t="inlineStr">
         <is>
           <t>9) Siguiente prioridad operativa: E3 Random Forest con el mismo marco temporal limpio; E4 XGBoost y E5 CatBoost quedan como continuidad.</t>
         </is>
@@ -1580,7 +1580,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:AK173"/>
+  <dimension ref="A1:AK197"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.54296875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12" customWidth="1" style="26" min="1" max="1"/>
@@ -16707,6 +16707,3774 @@
       <c r="AK173" s="49" t="inlineStr">
         <is>
           <t>2026-03-23 06:12:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="174" ht="15" customHeight="1" s="27">
+      <c r="A174" s="49" t="inlineStr">
+        <is>
+          <t>2026-03-23 07:31:44</t>
+        </is>
+      </c>
+      <c r="B174" s="49" t="inlineStr">
+        <is>
+          <t>E3_v1_clean</t>
+        </is>
+      </c>
+      <c r="C174" s="50" t="inlineStr">
+        <is>
+          <t>E3</t>
+        </is>
+      </c>
+      <c r="D174" s="50" t="inlineStr">
+        <is>
+          <t>arboles_boosting</t>
+        </is>
+      </c>
+      <c r="E174" s="50" t="inlineStr">
+        <is>
+          <t>random_forest_regressor</t>
+        </is>
+      </c>
+      <c r="F174" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="G174" s="49" t="inlineStr">
+        <is>
+          <t>nivel</t>
+        </is>
+      </c>
+      <c r="H174" s="50" t="inlineStr">
+        <is>
+          <t>y_t + lags [1, 2, 3, 4, 5, 6]</t>
+        </is>
+      </c>
+      <c r="I174" s="50" t="inlineStr">
+        <is>
+          <t>sentimiento_medios, v5_agua_neto, v5_alumbrado_neto, v5_americo_neto, v5_basura_neto, v5_corrupcion_neto, v5_delitos_neto, v5_morena_neto, v5_obras_neto, v5_prevencion_neto, v5_vialidad_neto</t>
+        </is>
+      </c>
+      <c r="J174" s="50" t="inlineStr">
+        <is>
+          <t>sin_escalar</t>
+        </is>
+      </c>
+      <c r="K174" s="50" t="inlineStr">
+        <is>
+          <t>corr</t>
+        </is>
+      </c>
+      <c r="L174" s="50" t="inlineStr">
+        <is>
+          <t>walk-forward_expanding</t>
+        </is>
+      </c>
+      <c r="M174" s="49" t="inlineStr">
+        <is>
+          <t>2024-10-14 a 2026-03-02</t>
+        </is>
+      </c>
+      <c r="N174" s="49" t="inlineStr">
+        <is>
+          <t>{"feature_candidates": 83, "feature_mode": "corr", "horizon": 1, "initial_train_size": 40, "lags": [1, 2, 3, 4, 5, 6], "model": "random_forest_regressor", "model_params": {"bootstrap": true, "max_depth": 6, "max_features": "sqrt", "min_samples_leaf": 2, "min_samples_split": 4, "n_estimators": 400, "random_state": 42, "uses_scaling": false}, "rows_eval": 26, "rows_modeling": 66, "selected_feature_count_avg": 30.0, "target_mode": "nivel", "transform_mode": ""}</t>
+        </is>
+      </c>
+      <c r="O174" s="51" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="P174" s="51" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="Q174" s="51" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="R174" s="51" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="S174" s="52" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="T174" s="53" t="n">
+        <v>0.1725014827223296</v>
+      </c>
+      <c r="U174" s="53" t="n">
+        <v>0.2692307692307693</v>
+      </c>
+      <c r="V174" s="53" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="W174" s="53" t="n">
+        <v>0.7692307692307693</v>
+      </c>
+      <c r="X174" s="54" t="n">
+        <v>0.08013188645507538</v>
+      </c>
+      <c r="Y174" s="53" t="n">
+        <v>0.1061374139453869</v>
+      </c>
+      <c r="Z174" s="53" t="n">
+        <v>0.1328844909113693</v>
+      </c>
+      <c r="AA174" s="55" t="n">
+        <v>0.7307692307692307</v>
+      </c>
+      <c r="AB174" s="55" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AC174" s="49" t="inlineStr">
+        <is>
+          <t>corrido</t>
+        </is>
+      </c>
+      <c r="AD174" s="49" t="inlineStr">
+        <is>
+          <t>Random Forest limpio con walk-forward temporal | hipotesis=baseline_no_lineal_corr_memoria_larga | sin escalado por naturaleza basada en arboles</t>
+        </is>
+      </c>
+      <c r="AE174" s="49" t="inlineStr">
+        <is>
+          <t>run_e3_random_forest.py</t>
+        </is>
+      </c>
+      <c r="AF174" s="49" t="inlineStr">
+        <is>
+          <t>Scripts/Modeling/run_e3_random_forest.py</t>
+        </is>
+      </c>
+      <c r="AG174" s="49" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E3_v1_clean_20260323_073144</t>
+        </is>
+      </c>
+      <c r="AH174" s="49" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E3_v1_clean_20260323_073144/scripts/run_e3_random_forest.py</t>
+        </is>
+      </c>
+      <c r="AI174" s="49" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E3_v1_clean_20260323_073144/parametros_run.json</t>
+        </is>
+      </c>
+      <c r="AJ174" s="49" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E3_v1_clean_20260323_073144/metricas_horizonte.json</t>
+        </is>
+      </c>
+      <c r="AK174" s="49" t="inlineStr">
+        <is>
+          <t>2026-03-23 07:31:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="175" ht="15" customHeight="1" s="27">
+      <c r="A175" s="49" t="inlineStr">
+        <is>
+          <t>2026-03-23 07:31:44</t>
+        </is>
+      </c>
+      <c r="B175" s="49" t="inlineStr">
+        <is>
+          <t>E3_v1_clean</t>
+        </is>
+      </c>
+      <c r="C175" s="50" t="inlineStr">
+        <is>
+          <t>E3</t>
+        </is>
+      </c>
+      <c r="D175" s="50" t="inlineStr">
+        <is>
+          <t>arboles_boosting</t>
+        </is>
+      </c>
+      <c r="E175" s="50" t="inlineStr">
+        <is>
+          <t>random_forest_regressor</t>
+        </is>
+      </c>
+      <c r="F175" s="50" t="n">
+        <v>2</v>
+      </c>
+      <c r="G175" s="49" t="inlineStr">
+        <is>
+          <t>nivel</t>
+        </is>
+      </c>
+      <c r="H175" s="50" t="inlineStr">
+        <is>
+          <t>y_t + lags [1, 2, 3, 4, 5, 6]</t>
+        </is>
+      </c>
+      <c r="I175" s="50" t="inlineStr">
+        <is>
+          <t>sentimiento_medios, v5_agua_neto, v5_alumbrado_neto, v5_americo_neto, v5_basura_neto, v5_corrupcion_neto, v5_delitos_neto, v5_morena_neto, v5_obras_neto, v5_prevencion_neto, v5_vialidad_neto</t>
+        </is>
+      </c>
+      <c r="J175" s="50" t="inlineStr">
+        <is>
+          <t>sin_escalar</t>
+        </is>
+      </c>
+      <c r="K175" s="50" t="inlineStr">
+        <is>
+          <t>corr</t>
+        </is>
+      </c>
+      <c r="L175" s="50" t="inlineStr">
+        <is>
+          <t>walk-forward_expanding</t>
+        </is>
+      </c>
+      <c r="M175" s="49" t="inlineStr">
+        <is>
+          <t>2024-10-14 a 2026-03-02</t>
+        </is>
+      </c>
+      <c r="N175" s="49" t="inlineStr">
+        <is>
+          <t>{"feature_candidates": 83, "feature_mode": "corr", "horizon": 2, "initial_train_size": 40, "lags": [1, 2, 3, 4, 5, 6], "model": "random_forest_regressor", "model_params": {"bootstrap": true, "max_depth": 6, "max_features": "sqrt", "min_samples_leaf": 2, "min_samples_split": 4, "n_estimators": 400, "random_state": 42, "uses_scaling": false}, "rows_eval": 25, "rows_modeling": 65, "selected_feature_count_avg": 30.0, "target_mode": "nivel", "transform_mode": ""}</t>
+        </is>
+      </c>
+      <c r="O175" s="51" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="P175" s="51" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="Q175" s="51" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="R175" s="51" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="S175" s="52" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="T175" s="53" t="n">
+        <v>0.1740295415812016</v>
+      </c>
+      <c r="U175" s="53" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="V175" s="53" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="W175" s="53" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="X175" s="54" t="n">
+        <v>0.08422758488835515</v>
+      </c>
+      <c r="Y175" s="53" t="n">
+        <v>0.1070776042155081</v>
+      </c>
+      <c r="Z175" s="53" t="n">
+        <v>0.1342516027711331</v>
+      </c>
+      <c r="AA175" s="55" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AB175" s="55" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AC175" s="49" t="inlineStr">
+        <is>
+          <t>corrido</t>
+        </is>
+      </c>
+      <c r="AD175" s="49" t="inlineStr">
+        <is>
+          <t>Random Forest limpio con walk-forward temporal | hipotesis=baseline_no_lineal_corr_memoria_larga | sin escalado por naturaleza basada en arboles</t>
+        </is>
+      </c>
+      <c r="AE175" s="49" t="inlineStr">
+        <is>
+          <t>run_e3_random_forest.py</t>
+        </is>
+      </c>
+      <c r="AF175" s="49" t="inlineStr">
+        <is>
+          <t>Scripts/Modeling/run_e3_random_forest.py</t>
+        </is>
+      </c>
+      <c r="AG175" s="49" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E3_v1_clean_20260323_073144</t>
+        </is>
+      </c>
+      <c r="AH175" s="49" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E3_v1_clean_20260323_073144/scripts/run_e3_random_forest.py</t>
+        </is>
+      </c>
+      <c r="AI175" s="49" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E3_v1_clean_20260323_073144/parametros_run.json</t>
+        </is>
+      </c>
+      <c r="AJ175" s="49" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E3_v1_clean_20260323_073144/metricas_horizonte.json</t>
+        </is>
+      </c>
+      <c r="AK175" s="49" t="inlineStr">
+        <is>
+          <t>2026-03-23 07:31:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="176" ht="15" customHeight="1" s="27">
+      <c r="A176" s="49" t="inlineStr">
+        <is>
+          <t>2026-03-23 07:31:44</t>
+        </is>
+      </c>
+      <c r="B176" s="49" t="inlineStr">
+        <is>
+          <t>E3_v1_clean</t>
+        </is>
+      </c>
+      <c r="C176" s="50" t="inlineStr">
+        <is>
+          <t>E3</t>
+        </is>
+      </c>
+      <c r="D176" s="50" t="inlineStr">
+        <is>
+          <t>arboles_boosting</t>
+        </is>
+      </c>
+      <c r="E176" s="50" t="inlineStr">
+        <is>
+          <t>random_forest_regressor</t>
+        </is>
+      </c>
+      <c r="F176" s="50" t="n">
+        <v>3</v>
+      </c>
+      <c r="G176" s="49" t="inlineStr">
+        <is>
+          <t>nivel</t>
+        </is>
+      </c>
+      <c r="H176" s="50" t="inlineStr">
+        <is>
+          <t>y_t + lags [1, 2, 3, 4, 5, 6]</t>
+        </is>
+      </c>
+      <c r="I176" s="50" t="inlineStr">
+        <is>
+          <t>sentimiento_medios, v5_agua_neto, v5_alumbrado_neto, v5_americo_neto, v5_basura_neto, v5_corrupcion_neto, v5_delitos_neto, v5_morena_neto, v5_obras_neto, v5_prevencion_neto, v5_vialidad_neto</t>
+        </is>
+      </c>
+      <c r="J176" s="50" t="inlineStr">
+        <is>
+          <t>sin_escalar</t>
+        </is>
+      </c>
+      <c r="K176" s="50" t="inlineStr">
+        <is>
+          <t>corr</t>
+        </is>
+      </c>
+      <c r="L176" s="50" t="inlineStr">
+        <is>
+          <t>walk-forward_expanding</t>
+        </is>
+      </c>
+      <c r="M176" s="49" t="inlineStr">
+        <is>
+          <t>2024-10-14 a 2026-03-02</t>
+        </is>
+      </c>
+      <c r="N176" s="49" t="inlineStr">
+        <is>
+          <t>{"feature_candidates": 83, "feature_mode": "corr", "horizon": 3, "initial_train_size": 40, "lags": [1, 2, 3, 4, 5, 6], "model": "random_forest_regressor", "model_params": {"bootstrap": true, "max_depth": 6, "max_features": "sqrt", "min_samples_leaf": 2, "min_samples_split": 4, "n_estimators": 400, "random_state": 42, "uses_scaling": false}, "rows_eval": 24, "rows_modeling": 64, "selected_feature_count_avg": 30.0, "target_mode": "nivel", "transform_mode": ""}</t>
+        </is>
+      </c>
+      <c r="O176" s="51" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="P176" s="51" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="Q176" s="51" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="R176" s="51" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="S176" s="52" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="T176" s="53" t="n">
+        <v>0.1753743579276128</v>
+      </c>
+      <c r="U176" s="53" t="n">
+        <v>0.1666666666666666</v>
+      </c>
+      <c r="V176" s="53" t="n">
+        <v>0.1818181818181818</v>
+      </c>
+      <c r="W176" s="53" t="n">
+        <v>0.7916666666666666</v>
+      </c>
+      <c r="X176" s="54" t="n">
+        <v>0.06830067121876297</v>
+      </c>
+      <c r="Y176" s="53" t="n">
+        <v>0.1079050482872169</v>
+      </c>
+      <c r="Z176" s="53" t="n">
+        <v>0.1365551368707545</v>
+      </c>
+      <c r="AA176" s="55" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="AB176" s="55" t="n">
+        <v>0.8181818181818182</v>
+      </c>
+      <c r="AC176" s="49" t="inlineStr">
+        <is>
+          <t>corrido</t>
+        </is>
+      </c>
+      <c r="AD176" s="49" t="inlineStr">
+        <is>
+          <t>Random Forest limpio con walk-forward temporal | hipotesis=baseline_no_lineal_corr_memoria_larga | sin escalado por naturaleza basada en arboles</t>
+        </is>
+      </c>
+      <c r="AE176" s="49" t="inlineStr">
+        <is>
+          <t>run_e3_random_forest.py</t>
+        </is>
+      </c>
+      <c r="AF176" s="49" t="inlineStr">
+        <is>
+          <t>Scripts/Modeling/run_e3_random_forest.py</t>
+        </is>
+      </c>
+      <c r="AG176" s="49" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E3_v1_clean_20260323_073144</t>
+        </is>
+      </c>
+      <c r="AH176" s="49" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E3_v1_clean_20260323_073144/scripts/run_e3_random_forest.py</t>
+        </is>
+      </c>
+      <c r="AI176" s="49" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E3_v1_clean_20260323_073144/parametros_run.json</t>
+        </is>
+      </c>
+      <c r="AJ176" s="49" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E3_v1_clean_20260323_073144/metricas_horizonte.json</t>
+        </is>
+      </c>
+      <c r="AK176" s="49" t="inlineStr">
+        <is>
+          <t>2026-03-23 07:31:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="177" ht="15" customHeight="1" s="27">
+      <c r="A177" s="49" t="inlineStr">
+        <is>
+          <t>2026-03-23 07:31:44</t>
+        </is>
+      </c>
+      <c r="B177" s="49" t="inlineStr">
+        <is>
+          <t>E3_v1_clean</t>
+        </is>
+      </c>
+      <c r="C177" s="50" t="inlineStr">
+        <is>
+          <t>E3</t>
+        </is>
+      </c>
+      <c r="D177" s="50" t="inlineStr">
+        <is>
+          <t>arboles_boosting</t>
+        </is>
+      </c>
+      <c r="E177" s="50" t="inlineStr">
+        <is>
+          <t>random_forest_regressor</t>
+        </is>
+      </c>
+      <c r="F177" s="50" t="n">
+        <v>4</v>
+      </c>
+      <c r="G177" s="49" t="inlineStr">
+        <is>
+          <t>nivel</t>
+        </is>
+      </c>
+      <c r="H177" s="50" t="inlineStr">
+        <is>
+          <t>y_t + lags [1, 2, 3, 4, 5, 6]</t>
+        </is>
+      </c>
+      <c r="I177" s="50" t="inlineStr">
+        <is>
+          <t>sentimiento_medios, v5_agua_neto, v5_alumbrado_neto, v5_americo_neto, v5_basura_neto, v5_corrupcion_neto, v5_delitos_neto, v5_morena_neto, v5_obras_neto, v5_prevencion_neto, v5_vialidad_neto</t>
+        </is>
+      </c>
+      <c r="J177" s="50" t="inlineStr">
+        <is>
+          <t>sin_escalar</t>
+        </is>
+      </c>
+      <c r="K177" s="50" t="inlineStr">
+        <is>
+          <t>corr</t>
+        </is>
+      </c>
+      <c r="L177" s="50" t="inlineStr">
+        <is>
+          <t>walk-forward_expanding</t>
+        </is>
+      </c>
+      <c r="M177" s="49" t="inlineStr">
+        <is>
+          <t>2024-10-14 a 2026-03-02</t>
+        </is>
+      </c>
+      <c r="N177" s="49" t="inlineStr">
+        <is>
+          <t>{"feature_candidates": 83, "feature_mode": "corr", "horizon": 4, "initial_train_size": 40, "lags": [1, 2, 3, 4, 5, 6], "model": "random_forest_regressor", "model_params": {"bootstrap": true, "max_depth": 6, "max_features": "sqrt", "min_samples_leaf": 2, "min_samples_split": 4, "n_estimators": 400, "random_state": 42, "uses_scaling": false}, "rows_eval": 23, "rows_modeling": 63, "selected_feature_count_avg": 30.0, "target_mode": "nivel", "transform_mode": ""}</t>
+        </is>
+      </c>
+      <c r="O177" s="51" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="P177" s="51" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="Q177" s="51" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="R177" s="51" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="S177" s="52" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="T177" s="53" t="n">
+        <v>0.1664652377469872</v>
+      </c>
+      <c r="U177" s="53" t="n">
+        <v>0.3478260869565217</v>
+      </c>
+      <c r="V177" s="53" t="n">
+        <v>0.4444444444444444</v>
+      </c>
+      <c r="W177" s="53" t="n">
+        <v>0.6521739130434783</v>
+      </c>
+      <c r="X177" s="54" t="n">
+        <v>0.04823217860490524</v>
+      </c>
+      <c r="Y177" s="53" t="n">
+        <v>0.1024234085843145</v>
+      </c>
+      <c r="Z177" s="53" t="n">
+        <v>0.1426623715507875</v>
+      </c>
+      <c r="AA177" s="55" t="n">
+        <v>0.6521739130434783</v>
+      </c>
+      <c r="AB177" s="55" t="n">
+        <v>0.5555555555555556</v>
+      </c>
+      <c r="AC177" s="49" t="inlineStr">
+        <is>
+          <t>corrido</t>
+        </is>
+      </c>
+      <c r="AD177" s="49" t="inlineStr">
+        <is>
+          <t>Random Forest limpio con walk-forward temporal | hipotesis=baseline_no_lineal_corr_memoria_larga | sin escalado por naturaleza basada en arboles</t>
+        </is>
+      </c>
+      <c r="AE177" s="49" t="inlineStr">
+        <is>
+          <t>run_e3_random_forest.py</t>
+        </is>
+      </c>
+      <c r="AF177" s="49" t="inlineStr">
+        <is>
+          <t>Scripts/Modeling/run_e3_random_forest.py</t>
+        </is>
+      </c>
+      <c r="AG177" s="49" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E3_v1_clean_20260323_073144</t>
+        </is>
+      </c>
+      <c r="AH177" s="49" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E3_v1_clean_20260323_073144/scripts/run_e3_random_forest.py</t>
+        </is>
+      </c>
+      <c r="AI177" s="49" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E3_v1_clean_20260323_073144/parametros_run.json</t>
+        </is>
+      </c>
+      <c r="AJ177" s="49" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E3_v1_clean_20260323_073144/metricas_horizonte.json</t>
+        </is>
+      </c>
+      <c r="AK177" s="49" t="inlineStr">
+        <is>
+          <t>2026-03-23 07:31:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="178" ht="15" customHeight="1" s="27">
+      <c r="A178" s="49" t="inlineStr">
+        <is>
+          <t>2026-03-23 08:01:10</t>
+        </is>
+      </c>
+      <c r="B178" s="49" t="inlineStr">
+        <is>
+          <t>E3_v3_clean</t>
+        </is>
+      </c>
+      <c r="C178" s="50" t="inlineStr">
+        <is>
+          <t>E3</t>
+        </is>
+      </c>
+      <c r="D178" s="50" t="inlineStr">
+        <is>
+          <t>arboles_boosting</t>
+        </is>
+      </c>
+      <c r="E178" s="50" t="inlineStr">
+        <is>
+          <t>extra_trees_regressor</t>
+        </is>
+      </c>
+      <c r="F178" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="G178" s="49" t="inlineStr">
+        <is>
+          <t>nivel</t>
+        </is>
+      </c>
+      <c r="H178" s="50" t="inlineStr">
+        <is>
+          <t>y_t + lags [1, 2, 3, 4, 5, 6]</t>
+        </is>
+      </c>
+      <c r="I178" s="50" t="inlineStr">
+        <is>
+          <t>sentimiento_medios, v5_agua_neto, v5_alumbrado_neto, v5_americo_neto, v5_basura_neto, v5_corrupcion_neto, v5_delitos_neto, v5_morena_neto, v5_obras_neto, v5_prevencion_neto, v5_vialidad_neto</t>
+        </is>
+      </c>
+      <c r="J178" s="50" t="inlineStr">
+        <is>
+          <t>sin_escalar</t>
+        </is>
+      </c>
+      <c r="K178" s="50" t="inlineStr">
+        <is>
+          <t>corr</t>
+        </is>
+      </c>
+      <c r="L178" s="50" t="inlineStr">
+        <is>
+          <t>walk-forward_expanding</t>
+        </is>
+      </c>
+      <c r="M178" s="49" t="inlineStr">
+        <is>
+          <t>2024-10-14 a 2026-03-02</t>
+        </is>
+      </c>
+      <c r="N178" s="49" t="inlineStr">
+        <is>
+          <t>{"feature_candidates": 83, "feature_mode": "corr", "horizon": 1, "initial_train_size": 40, "lags": [1, 2, 3, 4, 5, 6], "model": "extra_trees_regressor", "model_params": {"bootstrap": false, "max_depth": null, "max_features": "sqrt", "min_samples_leaf": 1, "min_samples_split": 2, "n_estimators": 600, "random_state": 42, "tree_model": "extra_trees", "uses_scaling": false}, "rows_eval": 26, "rows_modeling": 66, "selected_feature_count_avg": 30.0, "target_mode": "nivel", "transform_mode": ""}</t>
+        </is>
+      </c>
+      <c r="O178" s="51" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="P178" s="51" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="Q178" s="51" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="R178" s="51" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="S178" s="52" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="T178" s="53" t="n">
+        <v>0.1794634415432397</v>
+      </c>
+      <c r="U178" s="53" t="n">
+        <v>0.1923076923076923</v>
+      </c>
+      <c r="V178" s="53" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="W178" s="53" t="n">
+        <v>0.8076923076923077</v>
+      </c>
+      <c r="X178" s="54" t="n">
+        <v>0.07624750751588631</v>
+      </c>
+      <c r="Y178" s="53" t="n">
+        <v>0.1104209962867346</v>
+      </c>
+      <c r="Z178" s="53" t="n">
+        <v>0.1373978872462336</v>
+      </c>
+      <c r="AA178" s="55" t="n">
+        <v>0.8076923076923077</v>
+      </c>
+      <c r="AB178" s="55" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AC178" s="49" t="inlineStr">
+        <is>
+          <t>corrido</t>
+        </is>
+      </c>
+      <c r="AD178" s="49" t="inlineStr">
+        <is>
+          <t>ExtraTrees limpio con walk-forward temporal | hipotesis=extratrees_mas_aleatorio_h3_h4 | sin escalado por naturaleza basada en arboles</t>
+        </is>
+      </c>
+      <c r="AE178" s="49" t="inlineStr">
+        <is>
+          <t>run_e3_random_forest.py</t>
+        </is>
+      </c>
+      <c r="AF178" s="49" t="inlineStr">
+        <is>
+          <t>Scripts/Modeling/run_e3_random_forest.py</t>
+        </is>
+      </c>
+      <c r="AG178" s="49" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E3_v3_clean_20260323_080110</t>
+        </is>
+      </c>
+      <c r="AH178" s="49" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E3_v3_clean_20260323_080110/scripts/run_e3_random_forest.py</t>
+        </is>
+      </c>
+      <c r="AI178" s="49" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E3_v3_clean_20260323_080110/parametros_run.json</t>
+        </is>
+      </c>
+      <c r="AJ178" s="49" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E3_v3_clean_20260323_080110/metricas_horizonte.json</t>
+        </is>
+      </c>
+      <c r="AK178" s="49" t="inlineStr">
+        <is>
+          <t>2026-03-23 08:01:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="179" ht="15" customHeight="1" s="27">
+      <c r="A179" s="49" t="inlineStr">
+        <is>
+          <t>2026-03-23 08:01:10</t>
+        </is>
+      </c>
+      <c r="B179" s="49" t="inlineStr">
+        <is>
+          <t>E3_v3_clean</t>
+        </is>
+      </c>
+      <c r="C179" s="50" t="inlineStr">
+        <is>
+          <t>E3</t>
+        </is>
+      </c>
+      <c r="D179" s="50" t="inlineStr">
+        <is>
+          <t>arboles_boosting</t>
+        </is>
+      </c>
+      <c r="E179" s="50" t="inlineStr">
+        <is>
+          <t>extra_trees_regressor</t>
+        </is>
+      </c>
+      <c r="F179" s="50" t="n">
+        <v>2</v>
+      </c>
+      <c r="G179" s="49" t="inlineStr">
+        <is>
+          <t>nivel</t>
+        </is>
+      </c>
+      <c r="H179" s="50" t="inlineStr">
+        <is>
+          <t>y_t + lags [1, 2, 3, 4, 5, 6]</t>
+        </is>
+      </c>
+      <c r="I179" s="50" t="inlineStr">
+        <is>
+          <t>sentimiento_medios, v5_agua_neto, v5_alumbrado_neto, v5_americo_neto, v5_basura_neto, v5_corrupcion_neto, v5_delitos_neto, v5_morena_neto, v5_obras_neto, v5_prevencion_neto, v5_vialidad_neto</t>
+        </is>
+      </c>
+      <c r="J179" s="50" t="inlineStr">
+        <is>
+          <t>sin_escalar</t>
+        </is>
+      </c>
+      <c r="K179" s="50" t="inlineStr">
+        <is>
+          <t>corr</t>
+        </is>
+      </c>
+      <c r="L179" s="50" t="inlineStr">
+        <is>
+          <t>walk-forward_expanding</t>
+        </is>
+      </c>
+      <c r="M179" s="49" t="inlineStr">
+        <is>
+          <t>2024-10-14 a 2026-03-02</t>
+        </is>
+      </c>
+      <c r="N179" s="49" t="inlineStr">
+        <is>
+          <t>{"feature_candidates": 83, "feature_mode": "corr", "horizon": 2, "initial_train_size": 40, "lags": [1, 2, 3, 4, 5, 6], "model": "extra_trees_regressor", "model_params": {"bootstrap": false, "max_depth": null, "max_features": "sqrt", "min_samples_leaf": 1, "min_samples_split": 2, "n_estimators": 600, "random_state": 42, "tree_model": "extra_trees", "uses_scaling": false}, "rows_eval": 25, "rows_modeling": 65, "selected_feature_count_avg": 30.0, "target_mode": "nivel", "transform_mode": ""}</t>
+        </is>
+      </c>
+      <c r="O179" s="51" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="P179" s="51" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="Q179" s="51" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="R179" s="51" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="S179" s="52" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="T179" s="53" t="n">
+        <v>0.1804913780280977</v>
+      </c>
+      <c r="U179" s="53" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="V179" s="53" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="W179" s="53" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="X179" s="54" t="n">
+        <v>0.09104299557745855</v>
+      </c>
+      <c r="Y179" s="53" t="n">
+        <v>0.1110534692283068</v>
+      </c>
+      <c r="Z179" s="53" t="n">
+        <v>0.139706041100004</v>
+      </c>
+      <c r="AA179" s="55" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AB179" s="55" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AC179" s="49" t="inlineStr">
+        <is>
+          <t>corrido</t>
+        </is>
+      </c>
+      <c r="AD179" s="49" t="inlineStr">
+        <is>
+          <t>ExtraTrees limpio con walk-forward temporal | hipotesis=extratrees_mas_aleatorio_h3_h4 | sin escalado por naturaleza basada en arboles</t>
+        </is>
+      </c>
+      <c r="AE179" s="49" t="inlineStr">
+        <is>
+          <t>run_e3_random_forest.py</t>
+        </is>
+      </c>
+      <c r="AF179" s="49" t="inlineStr">
+        <is>
+          <t>Scripts/Modeling/run_e3_random_forest.py</t>
+        </is>
+      </c>
+      <c r="AG179" s="49" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E3_v3_clean_20260323_080110</t>
+        </is>
+      </c>
+      <c r="AH179" s="49" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E3_v3_clean_20260323_080110/scripts/run_e3_random_forest.py</t>
+        </is>
+      </c>
+      <c r="AI179" s="49" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E3_v3_clean_20260323_080110/parametros_run.json</t>
+        </is>
+      </c>
+      <c r="AJ179" s="49" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E3_v3_clean_20260323_080110/metricas_horizonte.json</t>
+        </is>
+      </c>
+      <c r="AK179" s="49" t="inlineStr">
+        <is>
+          <t>2026-03-23 08:01:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="180" ht="15" customHeight="1" s="27">
+      <c r="A180" s="49" t="inlineStr">
+        <is>
+          <t>2026-03-23 08:01:10</t>
+        </is>
+      </c>
+      <c r="B180" s="49" t="inlineStr">
+        <is>
+          <t>E3_v3_clean</t>
+        </is>
+      </c>
+      <c r="C180" s="50" t="inlineStr">
+        <is>
+          <t>E3</t>
+        </is>
+      </c>
+      <c r="D180" s="50" t="inlineStr">
+        <is>
+          <t>arboles_boosting</t>
+        </is>
+      </c>
+      <c r="E180" s="50" t="inlineStr">
+        <is>
+          <t>extra_trees_regressor</t>
+        </is>
+      </c>
+      <c r="F180" s="50" t="n">
+        <v>3</v>
+      </c>
+      <c r="G180" s="49" t="inlineStr">
+        <is>
+          <t>nivel</t>
+        </is>
+      </c>
+      <c r="H180" s="50" t="inlineStr">
+        <is>
+          <t>y_t + lags [1, 2, 3, 4, 5, 6]</t>
+        </is>
+      </c>
+      <c r="I180" s="50" t="inlineStr">
+        <is>
+          <t>sentimiento_medios, v5_agua_neto, v5_alumbrado_neto, v5_americo_neto, v5_basura_neto, v5_corrupcion_neto, v5_delitos_neto, v5_morena_neto, v5_obras_neto, v5_prevencion_neto, v5_vialidad_neto</t>
+        </is>
+      </c>
+      <c r="J180" s="50" t="inlineStr">
+        <is>
+          <t>sin_escalar</t>
+        </is>
+      </c>
+      <c r="K180" s="50" t="inlineStr">
+        <is>
+          <t>corr</t>
+        </is>
+      </c>
+      <c r="L180" s="50" t="inlineStr">
+        <is>
+          <t>walk-forward_expanding</t>
+        </is>
+      </c>
+      <c r="M180" s="49" t="inlineStr">
+        <is>
+          <t>2024-10-14 a 2026-03-02</t>
+        </is>
+      </c>
+      <c r="N180" s="49" t="inlineStr">
+        <is>
+          <t>{"feature_candidates": 83, "feature_mode": "corr", "horizon": 3, "initial_train_size": 40, "lags": [1, 2, 3, 4, 5, 6], "model": "extra_trees_regressor", "model_params": {"bootstrap": false, "max_depth": null, "max_features": "sqrt", "min_samples_leaf": 1, "min_samples_split": 2, "n_estimators": 600, "random_state": 42, "tree_model": "extra_trees", "uses_scaling": false}, "rows_eval": 24, "rows_modeling": 64, "selected_feature_count_avg": 30.0, "target_mode": "nivel", "transform_mode": ""}</t>
+        </is>
+      </c>
+      <c r="O180" s="51" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="P180" s="51" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="Q180" s="51" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="R180" s="51" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="S180" s="52" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="T180" s="53" t="n">
+        <v>0.187403115427832</v>
+      </c>
+      <c r="U180" s="53" t="n">
+        <v>0.1666666666666666</v>
+      </c>
+      <c r="V180" s="53" t="n">
+        <v>0.1818181818181818</v>
+      </c>
+      <c r="W180" s="53" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="X180" s="54" t="n">
+        <v>0.07081369075628599</v>
+      </c>
+      <c r="Y180" s="53" t="n">
+        <v>0.115306151129356</v>
+      </c>
+      <c r="Z180" s="53" t="n">
+        <v>0.142039525563487</v>
+      </c>
+      <c r="AA180" s="55" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="AB180" s="55" t="n">
+        <v>0.8181818181818182</v>
+      </c>
+      <c r="AC180" s="49" t="inlineStr">
+        <is>
+          <t>corrido</t>
+        </is>
+      </c>
+      <c r="AD180" s="49" t="inlineStr">
+        <is>
+          <t>ExtraTrees limpio con walk-forward temporal | hipotesis=extratrees_mas_aleatorio_h3_h4 | sin escalado por naturaleza basada en arboles</t>
+        </is>
+      </c>
+      <c r="AE180" s="49" t="inlineStr">
+        <is>
+          <t>run_e3_random_forest.py</t>
+        </is>
+      </c>
+      <c r="AF180" s="49" t="inlineStr">
+        <is>
+          <t>Scripts/Modeling/run_e3_random_forest.py</t>
+        </is>
+      </c>
+      <c r="AG180" s="49" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E3_v3_clean_20260323_080110</t>
+        </is>
+      </c>
+      <c r="AH180" s="49" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E3_v3_clean_20260323_080110/scripts/run_e3_random_forest.py</t>
+        </is>
+      </c>
+      <c r="AI180" s="49" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E3_v3_clean_20260323_080110/parametros_run.json</t>
+        </is>
+      </c>
+      <c r="AJ180" s="49" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E3_v3_clean_20260323_080110/metricas_horizonte.json</t>
+        </is>
+      </c>
+      <c r="AK180" s="49" t="inlineStr">
+        <is>
+          <t>2026-03-23 08:01:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="181" ht="15" customHeight="1" s="27">
+      <c r="A181" s="49" t="inlineStr">
+        <is>
+          <t>2026-03-23 08:01:10</t>
+        </is>
+      </c>
+      <c r="B181" s="49" t="inlineStr">
+        <is>
+          <t>E3_v3_clean</t>
+        </is>
+      </c>
+      <c r="C181" s="50" t="inlineStr">
+        <is>
+          <t>E3</t>
+        </is>
+      </c>
+      <c r="D181" s="50" t="inlineStr">
+        <is>
+          <t>arboles_boosting</t>
+        </is>
+      </c>
+      <c r="E181" s="50" t="inlineStr">
+        <is>
+          <t>extra_trees_regressor</t>
+        </is>
+      </c>
+      <c r="F181" s="50" t="n">
+        <v>4</v>
+      </c>
+      <c r="G181" s="49" t="inlineStr">
+        <is>
+          <t>nivel</t>
+        </is>
+      </c>
+      <c r="H181" s="50" t="inlineStr">
+        <is>
+          <t>y_t + lags [1, 2, 3, 4, 5, 6]</t>
+        </is>
+      </c>
+      <c r="I181" s="50" t="inlineStr">
+        <is>
+          <t>sentimiento_medios, v5_agua_neto, v5_alumbrado_neto, v5_americo_neto, v5_basura_neto, v5_corrupcion_neto, v5_delitos_neto, v5_morena_neto, v5_obras_neto, v5_prevencion_neto, v5_vialidad_neto</t>
+        </is>
+      </c>
+      <c r="J181" s="50" t="inlineStr">
+        <is>
+          <t>sin_escalar</t>
+        </is>
+      </c>
+      <c r="K181" s="50" t="inlineStr">
+        <is>
+          <t>corr</t>
+        </is>
+      </c>
+      <c r="L181" s="50" t="inlineStr">
+        <is>
+          <t>walk-forward_expanding</t>
+        </is>
+      </c>
+      <c r="M181" s="49" t="inlineStr">
+        <is>
+          <t>2024-10-14 a 2026-03-02</t>
+        </is>
+      </c>
+      <c r="N181" s="49" t="inlineStr">
+        <is>
+          <t>{"feature_candidates": 83, "feature_mode": "corr", "horizon": 4, "initial_train_size": 40, "lags": [1, 2, 3, 4, 5, 6], "model": "extra_trees_regressor", "model_params": {"bootstrap": false, "max_depth": null, "max_features": "sqrt", "min_samples_leaf": 1, "min_samples_split": 2, "n_estimators": 600, "random_state": 42, "tree_model": "extra_trees", "uses_scaling": false}, "rows_eval": 23, "rows_modeling": 63, "selected_feature_count_avg": 30.0, "target_mode": "nivel", "transform_mode": ""}</t>
+        </is>
+      </c>
+      <c r="O181" s="51" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="P181" s="51" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="Q181" s="51" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="R181" s="51" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="S181" s="52" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="T181" s="53" t="n">
+        <v>0.1721947665007063</v>
+      </c>
+      <c r="U181" s="53" t="n">
+        <v>0.3478260869565217</v>
+      </c>
+      <c r="V181" s="53" t="n">
+        <v>0.4444444444444444</v>
+      </c>
+      <c r="W181" s="53" t="n">
+        <v>0.6956521739130435</v>
+      </c>
+      <c r="X181" s="54" t="n">
+        <v>0.04918515277751895</v>
+      </c>
+      <c r="Y181" s="53" t="n">
+        <v>0.1059486963409672</v>
+      </c>
+      <c r="Z181" s="53" t="n">
+        <v>0.146264840710321</v>
+      </c>
+      <c r="AA181" s="55" t="n">
+        <v>0.6521739130434783</v>
+      </c>
+      <c r="AB181" s="55" t="n">
+        <v>0.5555555555555556</v>
+      </c>
+      <c r="AC181" s="49" t="inlineStr">
+        <is>
+          <t>corrido</t>
+        </is>
+      </c>
+      <c r="AD181" s="49" t="inlineStr">
+        <is>
+          <t>ExtraTrees limpio con walk-forward temporal | hipotesis=extratrees_mas_aleatorio_h3_h4 | sin escalado por naturaleza basada en arboles</t>
+        </is>
+      </c>
+      <c r="AE181" s="49" t="inlineStr">
+        <is>
+          <t>run_e3_random_forest.py</t>
+        </is>
+      </c>
+      <c r="AF181" s="49" t="inlineStr">
+        <is>
+          <t>Scripts/Modeling/run_e3_random_forest.py</t>
+        </is>
+      </c>
+      <c r="AG181" s="49" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E3_v3_clean_20260323_080110</t>
+        </is>
+      </c>
+      <c r="AH181" s="49" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E3_v3_clean_20260323_080110/scripts/run_e3_random_forest.py</t>
+        </is>
+      </c>
+      <c r="AI181" s="49" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E3_v3_clean_20260323_080110/parametros_run.json</t>
+        </is>
+      </c>
+      <c r="AJ181" s="49" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E3_v3_clean_20260323_080110/metricas_horizonte.json</t>
+        </is>
+      </c>
+      <c r="AK181" s="49" t="inlineStr">
+        <is>
+          <t>2026-03-23 08:01:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="182" ht="15" customHeight="1" s="27">
+      <c r="A182" s="49" t="inlineStr">
+        <is>
+          <t>2026-03-25 04:59:18</t>
+        </is>
+      </c>
+      <c r="B182" s="49" t="inlineStr">
+        <is>
+          <t>E3_v2_clean</t>
+        </is>
+      </c>
+      <c r="C182" s="50" t="inlineStr">
+        <is>
+          <t>E3</t>
+        </is>
+      </c>
+      <c r="D182" s="50" t="inlineStr">
+        <is>
+          <t>arboles_boosting</t>
+        </is>
+      </c>
+      <c r="E182" s="50" t="inlineStr">
+        <is>
+          <t>random_forest_regressor</t>
+        </is>
+      </c>
+      <c r="F182" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="G182" s="49" t="inlineStr">
+        <is>
+          <t>nivel</t>
+        </is>
+      </c>
+      <c r="H182" s="50" t="inlineStr">
+        <is>
+          <t>y_t + lags [1, 2, 3, 4, 5, 6]</t>
+        </is>
+      </c>
+      <c r="I182" s="50" t="inlineStr">
+        <is>
+          <t>sentimiento_medios, v5_agua_neto, v5_alumbrado_neto, v5_americo_neto, v5_basura_neto, v5_corrupcion_neto, v5_delitos_neto, v5_morena_neto, v5_obras_neto, v5_prevencion_neto, v5_vialidad_neto</t>
+        </is>
+      </c>
+      <c r="J182" s="50" t="inlineStr">
+        <is>
+          <t>sin_escalar</t>
+        </is>
+      </c>
+      <c r="K182" s="50" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="L182" s="50" t="inlineStr">
+        <is>
+          <t>walk-forward_expanding</t>
+        </is>
+      </c>
+      <c r="M182" s="49" t="inlineStr">
+        <is>
+          <t>2024-10-14 a 2026-03-02</t>
+        </is>
+      </c>
+      <c r="N182" s="49" t="inlineStr">
+        <is>
+          <t>{"feature_candidates": 83, "feature_mode": "all", "horizon": 1, "initial_train_size": 40, "lags": [1, 2, 3, 4, 5, 6], "model": "random_forest_regressor", "model_params": {"bootstrap": true, "max_depth": 6, "max_features": "sqrt", "min_samples_leaf": 2, "min_samples_split": 4, "n_estimators": 400, "random_state": 42, "tree_model": "random_forest", "uses_scaling": false}, "rows_eval": 26, "rows_modeling": 66, "selected_feature_count_avg": 83.0, "target_mode": "nivel", "transform_mode": ""}</t>
+        </is>
+      </c>
+      <c r="O182" s="51" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="P182" s="51" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="Q182" s="51" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="R182" s="51" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="S182" s="52" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="T182" s="53" t="n">
+        <v>0.1675782427314824</v>
+      </c>
+      <c r="U182" s="53" t="n">
+        <v>0.1923076923076923</v>
+      </c>
+      <c r="V182" s="53" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="W182" s="53" t="n">
+        <v>0.7307692307692307</v>
+      </c>
+      <c r="X182" s="54" t="n">
+        <v>0.0726918693329595</v>
+      </c>
+      <c r="Y182" s="53" t="n">
+        <v>0.1031082228183625</v>
+      </c>
+      <c r="Z182" s="53" t="n">
+        <v>0.1285747794616388</v>
+      </c>
+      <c r="AA182" s="55" t="n">
+        <v>0.8076923076923077</v>
+      </c>
+      <c r="AB182" s="55" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AC182" s="49" t="inlineStr">
+        <is>
+          <t>corrido</t>
+        </is>
+      </c>
+      <c r="AD182" s="49" t="inlineStr">
+        <is>
+          <t>Random Forest limpio con walk-forward temporal | hipotesis=random_forest_base_amplia | sin escalado por naturaleza basada en arboles</t>
+        </is>
+      </c>
+      <c r="AE182" s="49" t="inlineStr">
+        <is>
+          <t>run_e3_random_forest.py</t>
+        </is>
+      </c>
+      <c r="AF182" s="49" t="inlineStr">
+        <is>
+          <t>Scripts/Modeling/run_e3_random_forest.py</t>
+        </is>
+      </c>
+      <c r="AG182" s="49" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E3_v2_clean_20260325_045918</t>
+        </is>
+      </c>
+      <c r="AH182" s="49" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E3_v2_clean_20260325_045918/scripts/run_e3_random_forest.py</t>
+        </is>
+      </c>
+      <c r="AI182" s="49" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E3_v2_clean_20260325_045918/parametros_run.json</t>
+        </is>
+      </c>
+      <c r="AJ182" s="49" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E3_v2_clean_20260325_045918/metricas_horizonte.json</t>
+        </is>
+      </c>
+      <c r="AK182" s="49" t="inlineStr">
+        <is>
+          <t>2026-03-25 04:59:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="183" ht="15" customHeight="1" s="27">
+      <c r="A183" s="49" t="inlineStr">
+        <is>
+          <t>2026-03-25 04:59:18</t>
+        </is>
+      </c>
+      <c r="B183" s="49" t="inlineStr">
+        <is>
+          <t>E3_v2_clean</t>
+        </is>
+      </c>
+      <c r="C183" s="50" t="inlineStr">
+        <is>
+          <t>E3</t>
+        </is>
+      </c>
+      <c r="D183" s="50" t="inlineStr">
+        <is>
+          <t>arboles_boosting</t>
+        </is>
+      </c>
+      <c r="E183" s="50" t="inlineStr">
+        <is>
+          <t>random_forest_regressor</t>
+        </is>
+      </c>
+      <c r="F183" s="50" t="n">
+        <v>2</v>
+      </c>
+      <c r="G183" s="49" t="inlineStr">
+        <is>
+          <t>nivel</t>
+        </is>
+      </c>
+      <c r="H183" s="50" t="inlineStr">
+        <is>
+          <t>y_t + lags [1, 2, 3, 4, 5, 6]</t>
+        </is>
+      </c>
+      <c r="I183" s="50" t="inlineStr">
+        <is>
+          <t>sentimiento_medios, v5_agua_neto, v5_alumbrado_neto, v5_americo_neto, v5_basura_neto, v5_corrupcion_neto, v5_delitos_neto, v5_morena_neto, v5_obras_neto, v5_prevencion_neto, v5_vialidad_neto</t>
+        </is>
+      </c>
+      <c r="J183" s="50" t="inlineStr">
+        <is>
+          <t>sin_escalar</t>
+        </is>
+      </c>
+      <c r="K183" s="50" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="L183" s="50" t="inlineStr">
+        <is>
+          <t>walk-forward_expanding</t>
+        </is>
+      </c>
+      <c r="M183" s="49" t="inlineStr">
+        <is>
+          <t>2024-10-14 a 2026-03-02</t>
+        </is>
+      </c>
+      <c r="N183" s="49" t="inlineStr">
+        <is>
+          <t>{"feature_candidates": 83, "feature_mode": "all", "horizon": 2, "initial_train_size": 40, "lags": [1, 2, 3, 4, 5, 6], "model": "random_forest_regressor", "model_params": {"bootstrap": true, "max_depth": 6, "max_features": "sqrt", "min_samples_leaf": 2, "min_samples_split": 4, "n_estimators": 400, "random_state": 42, "tree_model": "random_forest", "uses_scaling": false}, "rows_eval": 25, "rows_modeling": 65, "selected_feature_count_avg": 83.0, "target_mode": "nivel", "transform_mode": ""}</t>
+        </is>
+      </c>
+      <c r="O183" s="51" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="P183" s="51" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="Q183" s="51" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="R183" s="51" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="S183" s="52" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="T183" s="53" t="n">
+        <v>0.1713405254856186</v>
+      </c>
+      <c r="U183" s="53" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="V183" s="53" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="W183" s="53" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="X183" s="54" t="n">
+        <v>0.08249229597999164</v>
+      </c>
+      <c r="Y183" s="53" t="n">
+        <v>0.105423095454548</v>
+      </c>
+      <c r="Z183" s="53" t="n">
+        <v>0.1318483561897889</v>
+      </c>
+      <c r="AA183" s="55" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="AB183" s="55" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AC183" s="49" t="inlineStr">
+        <is>
+          <t>corrido</t>
+        </is>
+      </c>
+      <c r="AD183" s="49" t="inlineStr">
+        <is>
+          <t>Random Forest limpio con walk-forward temporal | hipotesis=random_forest_base_amplia | sin escalado por naturaleza basada en arboles</t>
+        </is>
+      </c>
+      <c r="AE183" s="49" t="inlineStr">
+        <is>
+          <t>run_e3_random_forest.py</t>
+        </is>
+      </c>
+      <c r="AF183" s="49" t="inlineStr">
+        <is>
+          <t>Scripts/Modeling/run_e3_random_forest.py</t>
+        </is>
+      </c>
+      <c r="AG183" s="49" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E3_v2_clean_20260325_045918</t>
+        </is>
+      </c>
+      <c r="AH183" s="49" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E3_v2_clean_20260325_045918/scripts/run_e3_random_forest.py</t>
+        </is>
+      </c>
+      <c r="AI183" s="49" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E3_v2_clean_20260325_045918/parametros_run.json</t>
+        </is>
+      </c>
+      <c r="AJ183" s="49" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E3_v2_clean_20260325_045918/metricas_horizonte.json</t>
+        </is>
+      </c>
+      <c r="AK183" s="49" t="inlineStr">
+        <is>
+          <t>2026-03-25 04:59:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="184" ht="15" customHeight="1" s="27">
+      <c r="A184" s="49" t="inlineStr">
+        <is>
+          <t>2026-03-25 04:59:18</t>
+        </is>
+      </c>
+      <c r="B184" s="49" t="inlineStr">
+        <is>
+          <t>E3_v2_clean</t>
+        </is>
+      </c>
+      <c r="C184" s="50" t="inlineStr">
+        <is>
+          <t>E3</t>
+        </is>
+      </c>
+      <c r="D184" s="50" t="inlineStr">
+        <is>
+          <t>arboles_boosting</t>
+        </is>
+      </c>
+      <c r="E184" s="50" t="inlineStr">
+        <is>
+          <t>random_forest_regressor</t>
+        </is>
+      </c>
+      <c r="F184" s="50" t="n">
+        <v>3</v>
+      </c>
+      <c r="G184" s="49" t="inlineStr">
+        <is>
+          <t>nivel</t>
+        </is>
+      </c>
+      <c r="H184" s="50" t="inlineStr">
+        <is>
+          <t>y_t + lags [1, 2, 3, 4, 5, 6]</t>
+        </is>
+      </c>
+      <c r="I184" s="50" t="inlineStr">
+        <is>
+          <t>sentimiento_medios, v5_agua_neto, v5_alumbrado_neto, v5_americo_neto, v5_basura_neto, v5_corrupcion_neto, v5_delitos_neto, v5_morena_neto, v5_obras_neto, v5_prevencion_neto, v5_vialidad_neto</t>
+        </is>
+      </c>
+      <c r="J184" s="50" t="inlineStr">
+        <is>
+          <t>sin_escalar</t>
+        </is>
+      </c>
+      <c r="K184" s="50" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="L184" s="50" t="inlineStr">
+        <is>
+          <t>walk-forward_expanding</t>
+        </is>
+      </c>
+      <c r="M184" s="49" t="inlineStr">
+        <is>
+          <t>2024-10-14 a 2026-03-02</t>
+        </is>
+      </c>
+      <c r="N184" s="49" t="inlineStr">
+        <is>
+          <t>{"feature_candidates": 83, "feature_mode": "all", "horizon": 3, "initial_train_size": 40, "lags": [1, 2, 3, 4, 5, 6], "model": "random_forest_regressor", "model_params": {"bootstrap": true, "max_depth": 6, "max_features": "sqrt", "min_samples_leaf": 2, "min_samples_split": 4, "n_estimators": 400, "random_state": 42, "tree_model": "random_forest", "uses_scaling": false}, "rows_eval": 24, "rows_modeling": 64, "selected_feature_count_avg": 83.0, "target_mode": "nivel", "transform_mode": ""}</t>
+        </is>
+      </c>
+      <c r="O184" s="51" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="P184" s="51" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="Q184" s="51" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="R184" s="51" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="S184" s="52" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="T184" s="53" t="n">
+        <v>0.1755955670167976</v>
+      </c>
+      <c r="U184" s="53" t="n">
+        <v>0.2083333333333334</v>
+      </c>
+      <c r="V184" s="53" t="n">
+        <v>0.1818181818181818</v>
+      </c>
+      <c r="W184" s="53" t="n">
+        <v>0.7083333333333334</v>
+      </c>
+      <c r="X184" s="54" t="n">
+        <v>0.0689488981731274</v>
+      </c>
+      <c r="Y184" s="53" t="n">
+        <v>0.1080411547153864</v>
+      </c>
+      <c r="Z184" s="53" t="n">
+        <v>0.1374566791526148</v>
+      </c>
+      <c r="AA184" s="55" t="n">
+        <v>0.7916666666666666</v>
+      </c>
+      <c r="AB184" s="55" t="n">
+        <v>0.8181818181818182</v>
+      </c>
+      <c r="AC184" s="49" t="inlineStr">
+        <is>
+          <t>corrido</t>
+        </is>
+      </c>
+      <c r="AD184" s="49" t="inlineStr">
+        <is>
+          <t>Random Forest limpio con walk-forward temporal | hipotesis=random_forest_base_amplia | sin escalado por naturaleza basada en arboles</t>
+        </is>
+      </c>
+      <c r="AE184" s="49" t="inlineStr">
+        <is>
+          <t>run_e3_random_forest.py</t>
+        </is>
+      </c>
+      <c r="AF184" s="49" t="inlineStr">
+        <is>
+          <t>Scripts/Modeling/run_e3_random_forest.py</t>
+        </is>
+      </c>
+      <c r="AG184" s="49" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E3_v2_clean_20260325_045918</t>
+        </is>
+      </c>
+      <c r="AH184" s="49" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E3_v2_clean_20260325_045918/scripts/run_e3_random_forest.py</t>
+        </is>
+      </c>
+      <c r="AI184" s="49" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E3_v2_clean_20260325_045918/parametros_run.json</t>
+        </is>
+      </c>
+      <c r="AJ184" s="49" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E3_v2_clean_20260325_045918/metricas_horizonte.json</t>
+        </is>
+      </c>
+      <c r="AK184" s="49" t="inlineStr">
+        <is>
+          <t>2026-03-25 04:59:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="185" ht="15" customHeight="1" s="27">
+      <c r="A185" s="49" t="inlineStr">
+        <is>
+          <t>2026-03-25 04:59:18</t>
+        </is>
+      </c>
+      <c r="B185" s="49" t="inlineStr">
+        <is>
+          <t>E3_v2_clean</t>
+        </is>
+      </c>
+      <c r="C185" s="50" t="inlineStr">
+        <is>
+          <t>E3</t>
+        </is>
+      </c>
+      <c r="D185" s="50" t="inlineStr">
+        <is>
+          <t>arboles_boosting</t>
+        </is>
+      </c>
+      <c r="E185" s="50" t="inlineStr">
+        <is>
+          <t>random_forest_regressor</t>
+        </is>
+      </c>
+      <c r="F185" s="50" t="n">
+        <v>4</v>
+      </c>
+      <c r="G185" s="49" t="inlineStr">
+        <is>
+          <t>nivel</t>
+        </is>
+      </c>
+      <c r="H185" s="50" t="inlineStr">
+        <is>
+          <t>y_t + lags [1, 2, 3, 4, 5, 6]</t>
+        </is>
+      </c>
+      <c r="I185" s="50" t="inlineStr">
+        <is>
+          <t>sentimiento_medios, v5_agua_neto, v5_alumbrado_neto, v5_americo_neto, v5_basura_neto, v5_corrupcion_neto, v5_delitos_neto, v5_morena_neto, v5_obras_neto, v5_prevencion_neto, v5_vialidad_neto</t>
+        </is>
+      </c>
+      <c r="J185" s="50" t="inlineStr">
+        <is>
+          <t>sin_escalar</t>
+        </is>
+      </c>
+      <c r="K185" s="50" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="L185" s="50" t="inlineStr">
+        <is>
+          <t>walk-forward_expanding</t>
+        </is>
+      </c>
+      <c r="M185" s="49" t="inlineStr">
+        <is>
+          <t>2024-10-14 a 2026-03-02</t>
+        </is>
+      </c>
+      <c r="N185" s="49" t="inlineStr">
+        <is>
+          <t>{"feature_candidates": 83, "feature_mode": "all", "horizon": 4, "initial_train_size": 40, "lags": [1, 2, 3, 4, 5, 6], "model": "random_forest_regressor", "model_params": {"bootstrap": true, "max_depth": 6, "max_features": "sqrt", "min_samples_leaf": 2, "min_samples_split": 4, "n_estimators": 400, "random_state": 42, "tree_model": "random_forest", "uses_scaling": false}, "rows_eval": 23, "rows_modeling": 63, "selected_feature_count_avg": 83.0, "target_mode": "nivel", "transform_mode": ""}</t>
+        </is>
+      </c>
+      <c r="O185" s="51" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="P185" s="51" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="Q185" s="51" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="R185" s="51" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="S185" s="52" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="T185" s="53" t="n">
+        <v>0.1630091888460166</v>
+      </c>
+      <c r="U185" s="53" t="n">
+        <v>0.3043478260869565</v>
+      </c>
+      <c r="V185" s="53" t="n">
+        <v>0.3333333333333334</v>
+      </c>
+      <c r="W185" s="53" t="n">
+        <v>0.6521739130434783</v>
+      </c>
+      <c r="X185" s="54" t="n">
+        <v>0.04225363458832891</v>
+      </c>
+      <c r="Y185" s="53" t="n">
+        <v>0.1002969567589219</v>
+      </c>
+      <c r="Z185" s="53" t="n">
+        <v>0.1407502345248033</v>
+      </c>
+      <c r="AA185" s="55" t="n">
+        <v>0.6956521739130435</v>
+      </c>
+      <c r="AB185" s="55" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="AC185" s="49" t="inlineStr">
+        <is>
+          <t>corrido</t>
+        </is>
+      </c>
+      <c r="AD185" s="49" t="inlineStr">
+        <is>
+          <t>Random Forest limpio con walk-forward temporal | hipotesis=random_forest_base_amplia | sin escalado por naturaleza basada en arboles</t>
+        </is>
+      </c>
+      <c r="AE185" s="49" t="inlineStr">
+        <is>
+          <t>run_e3_random_forest.py</t>
+        </is>
+      </c>
+      <c r="AF185" s="49" t="inlineStr">
+        <is>
+          <t>Scripts/Modeling/run_e3_random_forest.py</t>
+        </is>
+      </c>
+      <c r="AG185" s="49" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E3_v2_clean_20260325_045918</t>
+        </is>
+      </c>
+      <c r="AH185" s="49" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E3_v2_clean_20260325_045918/scripts/run_e3_random_forest.py</t>
+        </is>
+      </c>
+      <c r="AI185" s="49" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E3_v2_clean_20260325_045918/parametros_run.json</t>
+        </is>
+      </c>
+      <c r="AJ185" s="49" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E3_v2_clean_20260325_045918/metricas_horizonte.json</t>
+        </is>
+      </c>
+      <c r="AK185" s="49" t="inlineStr">
+        <is>
+          <t>2026-03-25 04:59:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="186" ht="15" customHeight="1" s="27">
+      <c r="A186" s="49" t="inlineStr">
+        <is>
+          <t>2026-03-25 05:20:51</t>
+        </is>
+      </c>
+      <c r="B186" s="49" t="inlineStr">
+        <is>
+          <t>E4_v1_clean</t>
+        </is>
+      </c>
+      <c r="C186" s="50" t="inlineStr">
+        <is>
+          <t>E4</t>
+        </is>
+      </c>
+      <c r="D186" s="50" t="inlineStr">
+        <is>
+          <t>arboles_boosting</t>
+        </is>
+      </c>
+      <c r="E186" s="50" t="inlineStr">
+        <is>
+          <t>xgboost_regressor</t>
+        </is>
+      </c>
+      <c r="F186" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="G186" s="49" t="inlineStr">
+        <is>
+          <t>nivel</t>
+        </is>
+      </c>
+      <c r="H186" s="50" t="inlineStr">
+        <is>
+          <t>y_t + lags [1, 2, 3, 4, 5, 6]</t>
+        </is>
+      </c>
+      <c r="I186" s="50" t="inlineStr">
+        <is>
+          <t>sentimiento_medios, v5_agua_neto, v5_alumbrado_neto, v5_americo_neto, v5_basura_neto, v5_corrupcion_neto, v5_delitos_neto, v5_morena_neto, v5_obras_neto, v5_prevencion_neto, v5_vialidad_neto</t>
+        </is>
+      </c>
+      <c r="J186" s="50" t="inlineStr">
+        <is>
+          <t>sin_escalar</t>
+        </is>
+      </c>
+      <c r="K186" s="50" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="L186" s="50" t="inlineStr">
+        <is>
+          <t>walk-forward_expanding</t>
+        </is>
+      </c>
+      <c r="M186" s="49" t="inlineStr">
+        <is>
+          <t>2024-10-14 a 2026-03-02</t>
+        </is>
+      </c>
+      <c r="N186" s="49" t="inlineStr">
+        <is>
+          <t>{"feature_candidates": 83, "feature_mode": "all", "horizon": 1, "initial_train_size": 40, "lags": [1, 2, 3, 4, 5, 6], "model": "xgboost_regressor", "model_params": {"colsample_bytree": 0.8, "learning_rate": 0.05, "max_depth": 3, "min_child_weight": 3.0, "n_estimators": 300, "random_state": 42, "reg_alpha": 0.0, "reg_lambda": 1.0, "subsample": 0.8, "tuning_strategy": "baseline_fijo_sin_tuning_interno", "uses_scaling": false}, "rows_eval": 26, "rows_modeling": 66, "selected_feature_count_avg": 83.0, "target_mode": "nivel", "transform_mode": ""}</t>
+        </is>
+      </c>
+      <c r="O186" s="51" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="P186" s="51" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="Q186" s="51" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="R186" s="51" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="S186" s="52" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="T186" s="53" t="n">
+        <v>0.1780240685740992</v>
+      </c>
+      <c r="U186" s="53" t="n">
+        <v>0.2307692307692307</v>
+      </c>
+      <c r="V186" s="53" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="W186" s="53" t="n">
+        <v>0.7692307692307693</v>
+      </c>
+      <c r="X186" s="54" t="n">
+        <v>0.07782714258489579</v>
+      </c>
+      <c r="Y186" s="53" t="n">
+        <v>0.1095353730315805</v>
+      </c>
+      <c r="Z186" s="53" t="n">
+        <v>0.1306657841806134</v>
+      </c>
+      <c r="AA186" s="55" t="n">
+        <v>0.7692307692307693</v>
+      </c>
+      <c r="AB186" s="55" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AC186" s="49" t="inlineStr">
+        <is>
+          <t>corrido</t>
+        </is>
+      </c>
+      <c r="AD186" s="49" t="inlineStr">
+        <is>
+          <t>XGBoost limpio con walk-forward temporal | hipotesis=boosting_base_conservador | baseline fijo sin tuning interno | sin escalado por naturaleza basada en arboles</t>
+        </is>
+      </c>
+      <c r="AE186" s="49" t="inlineStr">
+        <is>
+          <t>run_e4_xgboost.py</t>
+        </is>
+      </c>
+      <c r="AF186" s="49" t="inlineStr">
+        <is>
+          <t>Scripts/Modeling/run_e4_xgboost.py</t>
+        </is>
+      </c>
+      <c r="AG186" s="49" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E4_v1_clean_20260325_052051</t>
+        </is>
+      </c>
+      <c r="AH186" s="49" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E4_v1_clean_20260325_052051/scripts/run_e4_xgboost.py</t>
+        </is>
+      </c>
+      <c r="AI186" s="49" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E4_v1_clean_20260325_052051/parametros_run.json</t>
+        </is>
+      </c>
+      <c r="AJ186" s="49" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E4_v1_clean_20260325_052051/metricas_horizonte.json</t>
+        </is>
+      </c>
+      <c r="AK186" s="49" t="inlineStr">
+        <is>
+          <t>2026-03-25 05:20:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="187" ht="15" customHeight="1" s="27">
+      <c r="A187" s="49" t="inlineStr">
+        <is>
+          <t>2026-03-25 05:20:51</t>
+        </is>
+      </c>
+      <c r="B187" s="49" t="inlineStr">
+        <is>
+          <t>E4_v1_clean</t>
+        </is>
+      </c>
+      <c r="C187" s="50" t="inlineStr">
+        <is>
+          <t>E4</t>
+        </is>
+      </c>
+      <c r="D187" s="50" t="inlineStr">
+        <is>
+          <t>arboles_boosting</t>
+        </is>
+      </c>
+      <c r="E187" s="50" t="inlineStr">
+        <is>
+          <t>xgboost_regressor</t>
+        </is>
+      </c>
+      <c r="F187" s="50" t="n">
+        <v>2</v>
+      </c>
+      <c r="G187" s="49" t="inlineStr">
+        <is>
+          <t>nivel</t>
+        </is>
+      </c>
+      <c r="H187" s="50" t="inlineStr">
+        <is>
+          <t>y_t + lags [1, 2, 3, 4, 5, 6]</t>
+        </is>
+      </c>
+      <c r="I187" s="50" t="inlineStr">
+        <is>
+          <t>sentimiento_medios, v5_agua_neto, v5_alumbrado_neto, v5_americo_neto, v5_basura_neto, v5_corrupcion_neto, v5_delitos_neto, v5_morena_neto, v5_obras_neto, v5_prevencion_neto, v5_vialidad_neto</t>
+        </is>
+      </c>
+      <c r="J187" s="50" t="inlineStr">
+        <is>
+          <t>sin_escalar</t>
+        </is>
+      </c>
+      <c r="K187" s="50" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="L187" s="50" t="inlineStr">
+        <is>
+          <t>walk-forward_expanding</t>
+        </is>
+      </c>
+      <c r="M187" s="49" t="inlineStr">
+        <is>
+          <t>2024-10-14 a 2026-03-02</t>
+        </is>
+      </c>
+      <c r="N187" s="49" t="inlineStr">
+        <is>
+          <t>{"feature_candidates": 83, "feature_mode": "all", "horizon": 2, "initial_train_size": 40, "lags": [1, 2, 3, 4, 5, 6], "model": "xgboost_regressor", "model_params": {"colsample_bytree": 0.8, "learning_rate": 0.05, "max_depth": 3, "min_child_weight": 3.0, "n_estimators": 300, "random_state": 42, "reg_alpha": 0.0, "reg_lambda": 1.0, "subsample": 0.8, "tuning_strategy": "baseline_fijo_sin_tuning_interno", "uses_scaling": false}, "rows_eval": 25, "rows_modeling": 65, "selected_feature_count_avg": 83.0, "target_mode": "nivel", "transform_mode": ""}</t>
+        </is>
+      </c>
+      <c r="O187" s="51" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="P187" s="51" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="Q187" s="51" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="R187" s="51" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="S187" s="52" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="T187" s="53" t="n">
+        <v>0.1821822415983659</v>
+      </c>
+      <c r="U187" s="53" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="V187" s="53" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="W187" s="53" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="X187" s="54" t="n">
+        <v>0.08294094613985702</v>
+      </c>
+      <c r="Y187" s="53" t="n">
+        <v>0.1120938306434698</v>
+      </c>
+      <c r="Z187" s="53" t="n">
+        <v>0.1368427314806668</v>
+      </c>
+      <c r="AA187" s="55" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AB187" s="55" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AC187" s="49" t="inlineStr">
+        <is>
+          <t>corrido</t>
+        </is>
+      </c>
+      <c r="AD187" s="49" t="inlineStr">
+        <is>
+          <t>XGBoost limpio con walk-forward temporal | hipotesis=boosting_base_conservador | baseline fijo sin tuning interno | sin escalado por naturaleza basada en arboles</t>
+        </is>
+      </c>
+      <c r="AE187" s="49" t="inlineStr">
+        <is>
+          <t>run_e4_xgboost.py</t>
+        </is>
+      </c>
+      <c r="AF187" s="49" t="inlineStr">
+        <is>
+          <t>Scripts/Modeling/run_e4_xgboost.py</t>
+        </is>
+      </c>
+      <c r="AG187" s="49" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E4_v1_clean_20260325_052051</t>
+        </is>
+      </c>
+      <c r="AH187" s="49" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E4_v1_clean_20260325_052051/scripts/run_e4_xgboost.py</t>
+        </is>
+      </c>
+      <c r="AI187" s="49" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E4_v1_clean_20260325_052051/parametros_run.json</t>
+        </is>
+      </c>
+      <c r="AJ187" s="49" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E4_v1_clean_20260325_052051/metricas_horizonte.json</t>
+        </is>
+      </c>
+      <c r="AK187" s="49" t="inlineStr">
+        <is>
+          <t>2026-03-25 05:20:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="188" ht="15" customHeight="1" s="27">
+      <c r="A188" s="49" t="inlineStr">
+        <is>
+          <t>2026-03-25 05:20:51</t>
+        </is>
+      </c>
+      <c r="B188" s="49" t="inlineStr">
+        <is>
+          <t>E4_v1_clean</t>
+        </is>
+      </c>
+      <c r="C188" s="50" t="inlineStr">
+        <is>
+          <t>E4</t>
+        </is>
+      </c>
+      <c r="D188" s="50" t="inlineStr">
+        <is>
+          <t>arboles_boosting</t>
+        </is>
+      </c>
+      <c r="E188" s="50" t="inlineStr">
+        <is>
+          <t>xgboost_regressor</t>
+        </is>
+      </c>
+      <c r="F188" s="50" t="n">
+        <v>3</v>
+      </c>
+      <c r="G188" s="49" t="inlineStr">
+        <is>
+          <t>nivel</t>
+        </is>
+      </c>
+      <c r="H188" s="50" t="inlineStr">
+        <is>
+          <t>y_t + lags [1, 2, 3, 4, 5, 6]</t>
+        </is>
+      </c>
+      <c r="I188" s="50" t="inlineStr">
+        <is>
+          <t>sentimiento_medios, v5_agua_neto, v5_alumbrado_neto, v5_americo_neto, v5_basura_neto, v5_corrupcion_neto, v5_delitos_neto, v5_morena_neto, v5_obras_neto, v5_prevencion_neto, v5_vialidad_neto</t>
+        </is>
+      </c>
+      <c r="J188" s="50" t="inlineStr">
+        <is>
+          <t>sin_escalar</t>
+        </is>
+      </c>
+      <c r="K188" s="50" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="L188" s="50" t="inlineStr">
+        <is>
+          <t>walk-forward_expanding</t>
+        </is>
+      </c>
+      <c r="M188" s="49" t="inlineStr">
+        <is>
+          <t>2024-10-14 a 2026-03-02</t>
+        </is>
+      </c>
+      <c r="N188" s="49" t="inlineStr">
+        <is>
+          <t>{"feature_candidates": 83, "feature_mode": "all", "horizon": 3, "initial_train_size": 40, "lags": [1, 2, 3, 4, 5, 6], "model": "xgboost_regressor", "model_params": {"colsample_bytree": 0.8, "learning_rate": 0.05, "max_depth": 3, "min_child_weight": 3.0, "n_estimators": 300, "random_state": 42, "reg_alpha": 0.0, "reg_lambda": 1.0, "subsample": 0.8, "tuning_strategy": "baseline_fijo_sin_tuning_interno", "uses_scaling": false}, "rows_eval": 24, "rows_modeling": 64, "selected_feature_count_avg": 83.0, "target_mode": "nivel", "transform_mode": ""}</t>
+        </is>
+      </c>
+      <c r="O188" s="51" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="P188" s="51" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="Q188" s="51" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="R188" s="51" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="S188" s="52" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="T188" s="53" t="n">
+        <v>0.1935230964875823</v>
+      </c>
+      <c r="U188" s="53" t="n">
+        <v>0.3333333333333334</v>
+      </c>
+      <c r="V188" s="53" t="n">
+        <v>0.1818181818181818</v>
+      </c>
+      <c r="W188" s="53" t="n">
+        <v>0.7083333333333334</v>
+      </c>
+      <c r="X188" s="54" t="n">
+        <v>0.08020628876755978</v>
+      </c>
+      <c r="Y188" s="53" t="n">
+        <v>0.1190716779690425</v>
+      </c>
+      <c r="Z188" s="53" t="n">
+        <v>0.1473403870715595</v>
+      </c>
+      <c r="AA188" s="55" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="AB188" s="55" t="n">
+        <v>0.8181818181818182</v>
+      </c>
+      <c r="AC188" s="49" t="inlineStr">
+        <is>
+          <t>corrido</t>
+        </is>
+      </c>
+      <c r="AD188" s="49" t="inlineStr">
+        <is>
+          <t>XGBoost limpio con walk-forward temporal | hipotesis=boosting_base_conservador | baseline fijo sin tuning interno | sin escalado por naturaleza basada en arboles</t>
+        </is>
+      </c>
+      <c r="AE188" s="49" t="inlineStr">
+        <is>
+          <t>run_e4_xgboost.py</t>
+        </is>
+      </c>
+      <c r="AF188" s="49" t="inlineStr">
+        <is>
+          <t>Scripts/Modeling/run_e4_xgboost.py</t>
+        </is>
+      </c>
+      <c r="AG188" s="49" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E4_v1_clean_20260325_052051</t>
+        </is>
+      </c>
+      <c r="AH188" s="49" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E4_v1_clean_20260325_052051/scripts/run_e4_xgboost.py</t>
+        </is>
+      </c>
+      <c r="AI188" s="49" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E4_v1_clean_20260325_052051/parametros_run.json</t>
+        </is>
+      </c>
+      <c r="AJ188" s="49" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E4_v1_clean_20260325_052051/metricas_horizonte.json</t>
+        </is>
+      </c>
+      <c r="AK188" s="49" t="inlineStr">
+        <is>
+          <t>2026-03-25 05:20:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="189" ht="15" customHeight="1" s="27">
+      <c r="A189" s="49" t="inlineStr">
+        <is>
+          <t>2026-03-25 05:20:51</t>
+        </is>
+      </c>
+      <c r="B189" s="49" t="inlineStr">
+        <is>
+          <t>E4_v1_clean</t>
+        </is>
+      </c>
+      <c r="C189" s="50" t="inlineStr">
+        <is>
+          <t>E4</t>
+        </is>
+      </c>
+      <c r="D189" s="50" t="inlineStr">
+        <is>
+          <t>arboles_boosting</t>
+        </is>
+      </c>
+      <c r="E189" s="50" t="inlineStr">
+        <is>
+          <t>xgboost_regressor</t>
+        </is>
+      </c>
+      <c r="F189" s="50" t="n">
+        <v>4</v>
+      </c>
+      <c r="G189" s="49" t="inlineStr">
+        <is>
+          <t>nivel</t>
+        </is>
+      </c>
+      <c r="H189" s="50" t="inlineStr">
+        <is>
+          <t>y_t + lags [1, 2, 3, 4, 5, 6]</t>
+        </is>
+      </c>
+      <c r="I189" s="50" t="inlineStr">
+        <is>
+          <t>sentimiento_medios, v5_agua_neto, v5_alumbrado_neto, v5_americo_neto, v5_basura_neto, v5_corrupcion_neto, v5_delitos_neto, v5_morena_neto, v5_obras_neto, v5_prevencion_neto, v5_vialidad_neto</t>
+        </is>
+      </c>
+      <c r="J189" s="50" t="inlineStr">
+        <is>
+          <t>sin_escalar</t>
+        </is>
+      </c>
+      <c r="K189" s="50" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="L189" s="50" t="inlineStr">
+        <is>
+          <t>walk-forward_expanding</t>
+        </is>
+      </c>
+      <c r="M189" s="49" t="inlineStr">
+        <is>
+          <t>2024-10-14 a 2026-03-02</t>
+        </is>
+      </c>
+      <c r="N189" s="49" t="inlineStr">
+        <is>
+          <t>{"feature_candidates": 83, "feature_mode": "all", "horizon": 4, "initial_train_size": 40, "lags": [1, 2, 3, 4, 5, 6], "model": "xgboost_regressor", "model_params": {"colsample_bytree": 0.8, "learning_rate": 0.05, "max_depth": 3, "min_child_weight": 3.0, "n_estimators": 300, "random_state": 42, "reg_alpha": 0.0, "reg_lambda": 1.0, "subsample": 0.8, "tuning_strategy": "baseline_fijo_sin_tuning_interno", "uses_scaling": false}, "rows_eval": 23, "rows_modeling": 63, "selected_feature_count_avg": 83.0, "target_mode": "nivel", "transform_mode": ""}</t>
+        </is>
+      </c>
+      <c r="O189" s="51" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="P189" s="51" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="Q189" s="51" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="R189" s="51" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="S189" s="52" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="T189" s="53" t="n">
+        <v>0.182669878414076</v>
+      </c>
+      <c r="U189" s="53" t="n">
+        <v>0.2608695652173914</v>
+      </c>
+      <c r="V189" s="53" t="n">
+        <v>0.3333333333333334</v>
+      </c>
+      <c r="W189" s="53" t="n">
+        <v>0.7391304347826086</v>
+      </c>
+      <c r="X189" s="54" t="n">
+        <v>0.04295973383413029</v>
+      </c>
+      <c r="Y189" s="53" t="n">
+        <v>0.1123938658069202</v>
+      </c>
+      <c r="Z189" s="53" t="n">
+        <v>0.1540985033542736</v>
+      </c>
+      <c r="AA189" s="55" t="n">
+        <v>0.7391304347826086</v>
+      </c>
+      <c r="AB189" s="55" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="AC189" s="49" t="inlineStr">
+        <is>
+          <t>corrido</t>
+        </is>
+      </c>
+      <c r="AD189" s="49" t="inlineStr">
+        <is>
+          <t>XGBoost limpio con walk-forward temporal | hipotesis=boosting_base_conservador | baseline fijo sin tuning interno | sin escalado por naturaleza basada en arboles</t>
+        </is>
+      </c>
+      <c r="AE189" s="49" t="inlineStr">
+        <is>
+          <t>run_e4_xgboost.py</t>
+        </is>
+      </c>
+      <c r="AF189" s="49" t="inlineStr">
+        <is>
+          <t>Scripts/Modeling/run_e4_xgboost.py</t>
+        </is>
+      </c>
+      <c r="AG189" s="49" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E4_v1_clean_20260325_052051</t>
+        </is>
+      </c>
+      <c r="AH189" s="49" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E4_v1_clean_20260325_052051/scripts/run_e4_xgboost.py</t>
+        </is>
+      </c>
+      <c r="AI189" s="49" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E4_v1_clean_20260325_052051/parametros_run.json</t>
+        </is>
+      </c>
+      <c r="AJ189" s="49" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E4_v1_clean_20260325_052051/metricas_horizonte.json</t>
+        </is>
+      </c>
+      <c r="AK189" s="49" t="inlineStr">
+        <is>
+          <t>2026-03-25 05:20:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="190" ht="15" customHeight="1" s="27">
+      <c r="A190" s="49" t="inlineStr">
+        <is>
+          <t>2026-03-25 05:51:17</t>
+        </is>
+      </c>
+      <c r="B190" s="49" t="inlineStr">
+        <is>
+          <t>E4_v2_clean</t>
+        </is>
+      </c>
+      <c r="C190" s="50" t="inlineStr">
+        <is>
+          <t>E4</t>
+        </is>
+      </c>
+      <c r="D190" s="50" t="inlineStr">
+        <is>
+          <t>arboles_boosting</t>
+        </is>
+      </c>
+      <c r="E190" s="50" t="inlineStr">
+        <is>
+          <t>xgboost_regressor</t>
+        </is>
+      </c>
+      <c r="F190" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="G190" s="49" t="inlineStr">
+        <is>
+          <t>nivel</t>
+        </is>
+      </c>
+      <c r="H190" s="50" t="inlineStr">
+        <is>
+          <t>y_t + lags [1, 2, 3, 4, 5, 6]</t>
+        </is>
+      </c>
+      <c r="I190" s="50" t="inlineStr">
+        <is>
+          <t>sentimiento_medios, v5_agua_neto, v5_alumbrado_neto, v5_americo_neto, v5_basura_neto, v5_corrupcion_neto, v5_delitos_neto, v5_morena_neto, v5_obras_neto, v5_prevencion_neto, v5_vialidad_neto</t>
+        </is>
+      </c>
+      <c r="J190" s="50" t="inlineStr">
+        <is>
+          <t>sin_escalar</t>
+        </is>
+      </c>
+      <c r="K190" s="50" t="inlineStr">
+        <is>
+          <t>corr</t>
+        </is>
+      </c>
+      <c r="L190" s="50" t="inlineStr">
+        <is>
+          <t>walk-forward_expanding</t>
+        </is>
+      </c>
+      <c r="M190" s="49" t="inlineStr">
+        <is>
+          <t>2024-10-14 a 2026-03-02</t>
+        </is>
+      </c>
+      <c r="N190" s="49" t="inlineStr">
+        <is>
+          <t>{"feature_candidates": 83, "feature_mode": "corr", "horizon": 1, "initial_train_size": 40, "lags": [1, 2, 3, 4, 5, 6], "model": "xgboost_regressor", "model_params": {"colsample_bytree": 0.8, "learning_rate": 0.05, "max_depth": 3, "min_child_weight": 3.0, "n_estimators": 300, "random_state": 42, "reg_alpha": 0.0, "reg_lambda": 1.0, "subsample": 0.8, "tuning_strategy": "baseline_fijo_sin_tuning_interno", "uses_scaling": false}, "rows_eval": 26, "rows_modeling": 66, "selected_feature_count_avg": 30.0, "target_mode": "nivel", "transform_mode": ""}</t>
+        </is>
+      </c>
+      <c r="O190" s="51" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="P190" s="51" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="Q190" s="51" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="R190" s="51" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="S190" s="52" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="T190" s="53" t="n">
+        <v>0.1719230044637626</v>
+      </c>
+      <c r="U190" s="53" t="n">
+        <v>0.2307692307692307</v>
+      </c>
+      <c r="V190" s="53" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="W190" s="53" t="n">
+        <v>0.7692307692307693</v>
+      </c>
+      <c r="X190" s="54" t="n">
+        <v>0.07718653085331044</v>
+      </c>
+      <c r="Y190" s="53" t="n">
+        <v>0.1057814854894746</v>
+      </c>
+      <c r="Z190" s="53" t="n">
+        <v>0.1327916626772419</v>
+      </c>
+      <c r="AA190" s="55" t="n">
+        <v>0.7692307692307693</v>
+      </c>
+      <c r="AB190" s="55" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AC190" s="49" t="inlineStr">
+        <is>
+          <t>corrido</t>
+        </is>
+      </c>
+      <c r="AD190" s="49" t="inlineStr">
+        <is>
+          <t>XGBoost limpio con walk-forward temporal | hipotesis=boosting_corr_vs_all | baseline fijo sin tuning interno | sin escalado por naturaleza basada en arboles</t>
+        </is>
+      </c>
+      <c r="AE190" s="49" t="inlineStr">
+        <is>
+          <t>run_e4_xgboost.py</t>
+        </is>
+      </c>
+      <c r="AF190" s="49" t="inlineStr">
+        <is>
+          <t>Scripts/Modeling/run_e4_xgboost.py</t>
+        </is>
+      </c>
+      <c r="AG190" s="49" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E4_v2_clean_20260325_055117</t>
+        </is>
+      </c>
+      <c r="AH190" s="49" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E4_v2_clean_20260325_055117/scripts/run_e4_xgboost.py</t>
+        </is>
+      </c>
+      <c r="AI190" s="49" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E4_v2_clean_20260325_055117/parametros_run.json</t>
+        </is>
+      </c>
+      <c r="AJ190" s="49" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E4_v2_clean_20260325_055117/metricas_horizonte.json</t>
+        </is>
+      </c>
+      <c r="AK190" s="49" t="inlineStr">
+        <is>
+          <t>2026-03-25 05:51:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="191" ht="15" customHeight="1" s="27">
+      <c r="A191" s="49" t="inlineStr">
+        <is>
+          <t>2026-03-25 05:51:17</t>
+        </is>
+      </c>
+      <c r="B191" s="49" t="inlineStr">
+        <is>
+          <t>E4_v2_clean</t>
+        </is>
+      </c>
+      <c r="C191" s="50" t="inlineStr">
+        <is>
+          <t>E4</t>
+        </is>
+      </c>
+      <c r="D191" s="50" t="inlineStr">
+        <is>
+          <t>arboles_boosting</t>
+        </is>
+      </c>
+      <c r="E191" s="50" t="inlineStr">
+        <is>
+          <t>xgboost_regressor</t>
+        </is>
+      </c>
+      <c r="F191" s="50" t="n">
+        <v>2</v>
+      </c>
+      <c r="G191" s="49" t="inlineStr">
+        <is>
+          <t>nivel</t>
+        </is>
+      </c>
+      <c r="H191" s="50" t="inlineStr">
+        <is>
+          <t>y_t + lags [1, 2, 3, 4, 5, 6]</t>
+        </is>
+      </c>
+      <c r="I191" s="50" t="inlineStr">
+        <is>
+          <t>sentimiento_medios, v5_agua_neto, v5_alumbrado_neto, v5_americo_neto, v5_basura_neto, v5_corrupcion_neto, v5_delitos_neto, v5_morena_neto, v5_obras_neto, v5_prevencion_neto, v5_vialidad_neto</t>
+        </is>
+      </c>
+      <c r="J191" s="50" t="inlineStr">
+        <is>
+          <t>sin_escalar</t>
+        </is>
+      </c>
+      <c r="K191" s="50" t="inlineStr">
+        <is>
+          <t>corr</t>
+        </is>
+      </c>
+      <c r="L191" s="50" t="inlineStr">
+        <is>
+          <t>walk-forward_expanding</t>
+        </is>
+      </c>
+      <c r="M191" s="49" t="inlineStr">
+        <is>
+          <t>2024-10-14 a 2026-03-02</t>
+        </is>
+      </c>
+      <c r="N191" s="49" t="inlineStr">
+        <is>
+          <t>{"feature_candidates": 83, "feature_mode": "corr", "horizon": 2, "initial_train_size": 40, "lags": [1, 2, 3, 4, 5, 6], "model": "xgboost_regressor", "model_params": {"colsample_bytree": 0.8, "learning_rate": 0.05, "max_depth": 3, "min_child_weight": 3.0, "n_estimators": 300, "random_state": 42, "reg_alpha": 0.0, "reg_lambda": 1.0, "subsample": 0.8, "tuning_strategy": "baseline_fijo_sin_tuning_interno", "uses_scaling": false}, "rows_eval": 25, "rows_modeling": 65, "selected_feature_count_avg": 30.0, "target_mode": "nivel", "transform_mode": ""}</t>
+        </is>
+      </c>
+      <c r="O191" s="51" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="P191" s="51" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="Q191" s="51" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="R191" s="51" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="S191" s="52" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="T191" s="53" t="n">
+        <v>0.1792346703223226</v>
+      </c>
+      <c r="U191" s="53" t="n">
+        <v>0.4399999999999999</v>
+      </c>
+      <c r="V191" s="53" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="W191" s="53" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="X191" s="54" t="n">
+        <v>0.09343303365320323</v>
+      </c>
+      <c r="Y191" s="53" t="n">
+        <v>0.1102802369993936</v>
+      </c>
+      <c r="Z191" s="53" t="n">
+        <v>0.1294353604420072</v>
+      </c>
+      <c r="AA191" s="55" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="AB191" s="55" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AC191" s="49" t="inlineStr">
+        <is>
+          <t>corrido</t>
+        </is>
+      </c>
+      <c r="AD191" s="49" t="inlineStr">
+        <is>
+          <t>XGBoost limpio con walk-forward temporal | hipotesis=boosting_corr_vs_all | baseline fijo sin tuning interno | sin escalado por naturaleza basada en arboles</t>
+        </is>
+      </c>
+      <c r="AE191" s="49" t="inlineStr">
+        <is>
+          <t>run_e4_xgboost.py</t>
+        </is>
+      </c>
+      <c r="AF191" s="49" t="inlineStr">
+        <is>
+          <t>Scripts/Modeling/run_e4_xgboost.py</t>
+        </is>
+      </c>
+      <c r="AG191" s="49" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E4_v2_clean_20260325_055117</t>
+        </is>
+      </c>
+      <c r="AH191" s="49" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E4_v2_clean_20260325_055117/scripts/run_e4_xgboost.py</t>
+        </is>
+      </c>
+      <c r="AI191" s="49" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E4_v2_clean_20260325_055117/parametros_run.json</t>
+        </is>
+      </c>
+      <c r="AJ191" s="49" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E4_v2_clean_20260325_055117/metricas_horizonte.json</t>
+        </is>
+      </c>
+      <c r="AK191" s="49" t="inlineStr">
+        <is>
+          <t>2026-03-25 05:51:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="192" ht="15" customHeight="1" s="27">
+      <c r="A192" s="49" t="inlineStr">
+        <is>
+          <t>2026-03-25 05:51:17</t>
+        </is>
+      </c>
+      <c r="B192" s="49" t="inlineStr">
+        <is>
+          <t>E4_v2_clean</t>
+        </is>
+      </c>
+      <c r="C192" s="50" t="inlineStr">
+        <is>
+          <t>E4</t>
+        </is>
+      </c>
+      <c r="D192" s="50" t="inlineStr">
+        <is>
+          <t>arboles_boosting</t>
+        </is>
+      </c>
+      <c r="E192" s="50" t="inlineStr">
+        <is>
+          <t>xgboost_regressor</t>
+        </is>
+      </c>
+      <c r="F192" s="50" t="n">
+        <v>3</v>
+      </c>
+      <c r="G192" s="49" t="inlineStr">
+        <is>
+          <t>nivel</t>
+        </is>
+      </c>
+      <c r="H192" s="50" t="inlineStr">
+        <is>
+          <t>y_t + lags [1, 2, 3, 4, 5, 6]</t>
+        </is>
+      </c>
+      <c r="I192" s="50" t="inlineStr">
+        <is>
+          <t>sentimiento_medios, v5_agua_neto, v5_alumbrado_neto, v5_americo_neto, v5_basura_neto, v5_corrupcion_neto, v5_delitos_neto, v5_morena_neto, v5_obras_neto, v5_prevencion_neto, v5_vialidad_neto</t>
+        </is>
+      </c>
+      <c r="J192" s="50" t="inlineStr">
+        <is>
+          <t>sin_escalar</t>
+        </is>
+      </c>
+      <c r="K192" s="50" t="inlineStr">
+        <is>
+          <t>corr</t>
+        </is>
+      </c>
+      <c r="L192" s="50" t="inlineStr">
+        <is>
+          <t>walk-forward_expanding</t>
+        </is>
+      </c>
+      <c r="M192" s="49" t="inlineStr">
+        <is>
+          <t>2024-10-14 a 2026-03-02</t>
+        </is>
+      </c>
+      <c r="N192" s="49" t="inlineStr">
+        <is>
+          <t>{"feature_candidates": 83, "feature_mode": "corr", "horizon": 3, "initial_train_size": 40, "lags": [1, 2, 3, 4, 5, 6], "model": "xgboost_regressor", "model_params": {"colsample_bytree": 0.8, "learning_rate": 0.05, "max_depth": 3, "min_child_weight": 3.0, "n_estimators": 300, "random_state": 42, "reg_alpha": 0.0, "reg_lambda": 1.0, "subsample": 0.8, "tuning_strategy": "baseline_fijo_sin_tuning_interno", "uses_scaling": false}, "rows_eval": 24, "rows_modeling": 64, "selected_feature_count_avg": 30.0, "target_mode": "nivel", "transform_mode": ""}</t>
+        </is>
+      </c>
+      <c r="O192" s="51" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="P192" s="51" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="Q192" s="51" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="R192" s="51" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="S192" s="52" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="T192" s="53" t="n">
+        <v>0.1804354685231082</v>
+      </c>
+      <c r="U192" s="53" t="n">
+        <v>0.2083333333333334</v>
+      </c>
+      <c r="V192" s="53" t="n">
+        <v>0.2727272727272727</v>
+      </c>
+      <c r="W192" s="53" t="n">
+        <v>0.7916666666666666</v>
+      </c>
+      <c r="X192" s="54" t="n">
+        <v>0.07877526964947182</v>
+      </c>
+      <c r="Y192" s="53" t="n">
+        <v>0.1110190690006629</v>
+      </c>
+      <c r="Z192" s="53" t="n">
+        <v>0.1357056504923607</v>
+      </c>
+      <c r="AA192" s="55" t="n">
+        <v>0.7916666666666666</v>
+      </c>
+      <c r="AB192" s="55" t="n">
+        <v>0.7272727272727273</v>
+      </c>
+      <c r="AC192" s="49" t="inlineStr">
+        <is>
+          <t>corrido</t>
+        </is>
+      </c>
+      <c r="AD192" s="49" t="inlineStr">
+        <is>
+          <t>XGBoost limpio con walk-forward temporal | hipotesis=boosting_corr_vs_all | baseline fijo sin tuning interno | sin escalado por naturaleza basada en arboles</t>
+        </is>
+      </c>
+      <c r="AE192" s="49" t="inlineStr">
+        <is>
+          <t>run_e4_xgboost.py</t>
+        </is>
+      </c>
+      <c r="AF192" s="49" t="inlineStr">
+        <is>
+          <t>Scripts/Modeling/run_e4_xgboost.py</t>
+        </is>
+      </c>
+      <c r="AG192" s="49" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E4_v2_clean_20260325_055117</t>
+        </is>
+      </c>
+      <c r="AH192" s="49" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E4_v2_clean_20260325_055117/scripts/run_e4_xgboost.py</t>
+        </is>
+      </c>
+      <c r="AI192" s="49" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E4_v2_clean_20260325_055117/parametros_run.json</t>
+        </is>
+      </c>
+      <c r="AJ192" s="49" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E4_v2_clean_20260325_055117/metricas_horizonte.json</t>
+        </is>
+      </c>
+      <c r="AK192" s="49" t="inlineStr">
+        <is>
+          <t>2026-03-25 05:51:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="193" ht="15" customHeight="1" s="27">
+      <c r="A193" s="49" t="inlineStr">
+        <is>
+          <t>2026-03-25 05:51:17</t>
+        </is>
+      </c>
+      <c r="B193" s="49" t="inlineStr">
+        <is>
+          <t>E4_v2_clean</t>
+        </is>
+      </c>
+      <c r="C193" s="50" t="inlineStr">
+        <is>
+          <t>E4</t>
+        </is>
+      </c>
+      <c r="D193" s="50" t="inlineStr">
+        <is>
+          <t>arboles_boosting</t>
+        </is>
+      </c>
+      <c r="E193" s="50" t="inlineStr">
+        <is>
+          <t>xgboost_regressor</t>
+        </is>
+      </c>
+      <c r="F193" s="50" t="n">
+        <v>4</v>
+      </c>
+      <c r="G193" s="49" t="inlineStr">
+        <is>
+          <t>nivel</t>
+        </is>
+      </c>
+      <c r="H193" s="50" t="inlineStr">
+        <is>
+          <t>y_t + lags [1, 2, 3, 4, 5, 6]</t>
+        </is>
+      </c>
+      <c r="I193" s="50" t="inlineStr">
+        <is>
+          <t>sentimiento_medios, v5_agua_neto, v5_alumbrado_neto, v5_americo_neto, v5_basura_neto, v5_corrupcion_neto, v5_delitos_neto, v5_morena_neto, v5_obras_neto, v5_prevencion_neto, v5_vialidad_neto</t>
+        </is>
+      </c>
+      <c r="J193" s="50" t="inlineStr">
+        <is>
+          <t>sin_escalar</t>
+        </is>
+      </c>
+      <c r="K193" s="50" t="inlineStr">
+        <is>
+          <t>corr</t>
+        </is>
+      </c>
+      <c r="L193" s="50" t="inlineStr">
+        <is>
+          <t>walk-forward_expanding</t>
+        </is>
+      </c>
+      <c r="M193" s="49" t="inlineStr">
+        <is>
+          <t>2024-10-14 a 2026-03-02</t>
+        </is>
+      </c>
+      <c r="N193" s="49" t="inlineStr">
+        <is>
+          <t>{"feature_candidates": 83, "feature_mode": "corr", "horizon": 4, "initial_train_size": 40, "lags": [1, 2, 3, 4, 5, 6], "model": "xgboost_regressor", "model_params": {"colsample_bytree": 0.8, "learning_rate": 0.05, "max_depth": 3, "min_child_weight": 3.0, "n_estimators": 300, "random_state": 42, "reg_alpha": 0.0, "reg_lambda": 1.0, "subsample": 0.8, "tuning_strategy": "baseline_fijo_sin_tuning_interno", "uses_scaling": false}, "rows_eval": 23, "rows_modeling": 63, "selected_feature_count_avg": 30.0, "target_mode": "nivel", "transform_mode": ""}</t>
+        </is>
+      </c>
+      <c r="O193" s="51" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="P193" s="51" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="Q193" s="51" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="R193" s="51" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="S193" s="52" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="T193" s="53" t="n">
+        <v>0.1907233496482671</v>
+      </c>
+      <c r="U193" s="53" t="n">
+        <v>0.3478260869565217</v>
+      </c>
+      <c r="V193" s="53" t="n">
+        <v>0.3333333333333334</v>
+      </c>
+      <c r="W193" s="53" t="n">
+        <v>0.8260869565217391</v>
+      </c>
+      <c r="X193" s="54" t="n">
+        <v>0.04794775846522967</v>
+      </c>
+      <c r="Y193" s="53" t="n">
+        <v>0.1173490383456775</v>
+      </c>
+      <c r="Z193" s="53" t="n">
+        <v>0.1570762633016385</v>
+      </c>
+      <c r="AA193" s="55" t="n">
+        <v>0.6521739130434783</v>
+      </c>
+      <c r="AB193" s="55" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="AC193" s="49" t="inlineStr">
+        <is>
+          <t>corrido</t>
+        </is>
+      </c>
+      <c r="AD193" s="49" t="inlineStr">
+        <is>
+          <t>XGBoost limpio con walk-forward temporal | hipotesis=boosting_corr_vs_all | baseline fijo sin tuning interno | sin escalado por naturaleza basada en arboles</t>
+        </is>
+      </c>
+      <c r="AE193" s="49" t="inlineStr">
+        <is>
+          <t>run_e4_xgboost.py</t>
+        </is>
+      </c>
+      <c r="AF193" s="49" t="inlineStr">
+        <is>
+          <t>Scripts/Modeling/run_e4_xgboost.py</t>
+        </is>
+      </c>
+      <c r="AG193" s="49" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E4_v2_clean_20260325_055117</t>
+        </is>
+      </c>
+      <c r="AH193" s="49" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E4_v2_clean_20260325_055117/scripts/run_e4_xgboost.py</t>
+        </is>
+      </c>
+      <c r="AI193" s="49" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E4_v2_clean_20260325_055117/parametros_run.json</t>
+        </is>
+      </c>
+      <c r="AJ193" s="49" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E4_v2_clean_20260325_055117/metricas_horizonte.json</t>
+        </is>
+      </c>
+      <c r="AK193" s="49" t="inlineStr">
+        <is>
+          <t>2026-03-25 05:51:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="194" ht="15" customHeight="1" s="27">
+      <c r="A194" s="49" t="inlineStr">
+        <is>
+          <t>2026-03-25 05:51:34</t>
+        </is>
+      </c>
+      <c r="B194" s="49" t="inlineStr">
+        <is>
+          <t>E4_v3_clean</t>
+        </is>
+      </c>
+      <c r="C194" s="50" t="inlineStr">
+        <is>
+          <t>E4</t>
+        </is>
+      </c>
+      <c r="D194" s="50" t="inlineStr">
+        <is>
+          <t>arboles_boosting</t>
+        </is>
+      </c>
+      <c r="E194" s="50" t="inlineStr">
+        <is>
+          <t>xgboost_regressor</t>
+        </is>
+      </c>
+      <c r="F194" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="G194" s="49" t="inlineStr">
+        <is>
+          <t>delta</t>
+        </is>
+      </c>
+      <c r="H194" s="50" t="inlineStr">
+        <is>
+          <t>y_t + lags [1, 2, 3, 4, 5, 6]</t>
+        </is>
+      </c>
+      <c r="I194" s="50" t="inlineStr">
+        <is>
+          <t>sentimiento_medios, v5_agua_neto, v5_alumbrado_neto, v5_americo_neto, v5_basura_neto, v5_corrupcion_neto, v5_delitos_neto, v5_morena_neto, v5_obras_neto, v5_prevencion_neto, v5_vialidad_neto</t>
+        </is>
+      </c>
+      <c r="J194" s="50" t="inlineStr">
+        <is>
+          <t>sin_escalar</t>
+        </is>
+      </c>
+      <c r="K194" s="50" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="L194" s="50" t="inlineStr">
+        <is>
+          <t>walk-forward_expanding</t>
+        </is>
+      </c>
+      <c r="M194" s="49" t="inlineStr">
+        <is>
+          <t>2024-10-14 a 2026-03-02</t>
+        </is>
+      </c>
+      <c r="N194" s="49" t="inlineStr">
+        <is>
+          <t>{"feature_candidates": 83, "feature_mode": "all", "horizon": 1, "initial_train_size": 40, "lags": [1, 2, 3, 4, 5, 6], "model": "xgboost_regressor", "model_params": {"colsample_bytree": 0.8, "learning_rate": 0.05, "max_depth": 3, "min_child_weight": 3.0, "n_estimators": 300, "random_state": 42, "reg_alpha": 0.0, "reg_lambda": 1.0, "subsample": 0.8, "tuning_strategy": "baseline_fijo_sin_tuning_interno", "uses_scaling": false}, "rows_eval": 26, "rows_modeling": 66, "selected_feature_count_avg": 83.0, "target_mode": "delta", "transform_mode": ""}</t>
+        </is>
+      </c>
+      <c r="O194" s="51" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="P194" s="51" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="Q194" s="51" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="R194" s="51" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="S194" s="52" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="T194" s="53" t="n">
+        <v>0.2779216239561862</v>
+      </c>
+      <c r="U194" s="53" t="n">
+        <v>0.6153846153846154</v>
+      </c>
+      <c r="V194" s="53" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="W194" s="53" t="n">
+        <v>0.8461538461538461</v>
+      </c>
+      <c r="X194" s="54" t="n">
+        <v>0.1569702320538611</v>
+      </c>
+      <c r="Y194" s="53" t="n">
+        <v>0.1710007472439743</v>
+      </c>
+      <c r="Z194" s="53" t="n">
+        <v>0.2011160550490227</v>
+      </c>
+      <c r="AA194" s="55" t="n">
+        <v>0.3846153846153846</v>
+      </c>
+      <c r="AB194" s="55" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AC194" s="49" t="inlineStr">
+        <is>
+          <t>corrido</t>
+        </is>
+      </c>
+      <c r="AD194" s="49" t="inlineStr">
+        <is>
+          <t>XGBoost limpio con walk-forward temporal | hipotesis=boosting_delta_vs_nivel | baseline fijo sin tuning interno | sin escalado por naturaleza basada en arboles</t>
+        </is>
+      </c>
+      <c r="AE194" s="49" t="inlineStr">
+        <is>
+          <t>run_e4_xgboost.py</t>
+        </is>
+      </c>
+      <c r="AF194" s="49" t="inlineStr">
+        <is>
+          <t>Scripts/Modeling/run_e4_xgboost.py</t>
+        </is>
+      </c>
+      <c r="AG194" s="49" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E4_v3_clean_20260325_055134</t>
+        </is>
+      </c>
+      <c r="AH194" s="49" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E4_v3_clean_20260325_055134/scripts/run_e4_xgboost.py</t>
+        </is>
+      </c>
+      <c r="AI194" s="49" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E4_v3_clean_20260325_055134/parametros_run.json</t>
+        </is>
+      </c>
+      <c r="AJ194" s="49" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E4_v3_clean_20260325_055134/metricas_horizonte.json</t>
+        </is>
+      </c>
+      <c r="AK194" s="49" t="inlineStr">
+        <is>
+          <t>2026-03-25 05:51:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="195" ht="15" customHeight="1" s="27">
+      <c r="A195" s="49" t="inlineStr">
+        <is>
+          <t>2026-03-25 05:51:34</t>
+        </is>
+      </c>
+      <c r="B195" s="49" t="inlineStr">
+        <is>
+          <t>E4_v3_clean</t>
+        </is>
+      </c>
+      <c r="C195" s="50" t="inlineStr">
+        <is>
+          <t>E4</t>
+        </is>
+      </c>
+      <c r="D195" s="50" t="inlineStr">
+        <is>
+          <t>arboles_boosting</t>
+        </is>
+      </c>
+      <c r="E195" s="50" t="inlineStr">
+        <is>
+          <t>xgboost_regressor</t>
+        </is>
+      </c>
+      <c r="F195" s="50" t="n">
+        <v>2</v>
+      </c>
+      <c r="G195" s="49" t="inlineStr">
+        <is>
+          <t>delta</t>
+        </is>
+      </c>
+      <c r="H195" s="50" t="inlineStr">
+        <is>
+          <t>y_t + lags [1, 2, 3, 4, 5, 6]</t>
+        </is>
+      </c>
+      <c r="I195" s="50" t="inlineStr">
+        <is>
+          <t>sentimiento_medios, v5_agua_neto, v5_alumbrado_neto, v5_americo_neto, v5_basura_neto, v5_corrupcion_neto, v5_delitos_neto, v5_morena_neto, v5_obras_neto, v5_prevencion_neto, v5_vialidad_neto</t>
+        </is>
+      </c>
+      <c r="J195" s="50" t="inlineStr">
+        <is>
+          <t>sin_escalar</t>
+        </is>
+      </c>
+      <c r="K195" s="50" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="L195" s="50" t="inlineStr">
+        <is>
+          <t>walk-forward_expanding</t>
+        </is>
+      </c>
+      <c r="M195" s="49" t="inlineStr">
+        <is>
+          <t>2024-10-14 a 2026-03-02</t>
+        </is>
+      </c>
+      <c r="N195" s="49" t="inlineStr">
+        <is>
+          <t>{"feature_candidates": 83, "feature_mode": "all", "horizon": 2, "initial_train_size": 40, "lags": [1, 2, 3, 4, 5, 6], "model": "xgboost_regressor", "model_params": {"colsample_bytree": 0.8, "learning_rate": 0.05, "max_depth": 3, "min_child_weight": 3.0, "n_estimators": 300, "random_state": 42, "reg_alpha": 0.0, "reg_lambda": 1.0, "subsample": 0.8, "tuning_strategy": "baseline_fijo_sin_tuning_interno", "uses_scaling": false}, "rows_eval": 25, "rows_modeling": 65, "selected_feature_count_avg": 83.0, "target_mode": "delta", "transform_mode": ""}</t>
+        </is>
+      </c>
+      <c r="O195" s="51" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="P195" s="51" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="Q195" s="51" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="R195" s="51" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="S195" s="52" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="T195" s="53" t="n">
+        <v>0.2027491306706547</v>
+      </c>
+      <c r="U195" s="53" t="n">
+        <v>0.4399999999999999</v>
+      </c>
+      <c r="V195" s="53" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="W195" s="53" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="X195" s="54" t="n">
+        <v>0.07899054893368228</v>
+      </c>
+      <c r="Y195" s="53" t="n">
+        <v>0.1247483098084295</v>
+      </c>
+      <c r="Z195" s="53" t="n">
+        <v>0.1619462114626966</v>
+      </c>
+      <c r="AA195" s="55" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="AB195" s="55" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AC195" s="49" t="inlineStr">
+        <is>
+          <t>corrido</t>
+        </is>
+      </c>
+      <c r="AD195" s="49" t="inlineStr">
+        <is>
+          <t>XGBoost limpio con walk-forward temporal | hipotesis=boosting_delta_vs_nivel | baseline fijo sin tuning interno | sin escalado por naturaleza basada en arboles</t>
+        </is>
+      </c>
+      <c r="AE195" s="49" t="inlineStr">
+        <is>
+          <t>run_e4_xgboost.py</t>
+        </is>
+      </c>
+      <c r="AF195" s="49" t="inlineStr">
+        <is>
+          <t>Scripts/Modeling/run_e4_xgboost.py</t>
+        </is>
+      </c>
+      <c r="AG195" s="49" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E4_v3_clean_20260325_055134</t>
+        </is>
+      </c>
+      <c r="AH195" s="49" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E4_v3_clean_20260325_055134/scripts/run_e4_xgboost.py</t>
+        </is>
+      </c>
+      <c r="AI195" s="49" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E4_v3_clean_20260325_055134/parametros_run.json</t>
+        </is>
+      </c>
+      <c r="AJ195" s="49" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E4_v3_clean_20260325_055134/metricas_horizonte.json</t>
+        </is>
+      </c>
+      <c r="AK195" s="49" t="inlineStr">
+        <is>
+          <t>2026-03-25 05:51:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="196" ht="15" customHeight="1" s="27">
+      <c r="A196" s="49" t="inlineStr">
+        <is>
+          <t>2026-03-25 05:51:34</t>
+        </is>
+      </c>
+      <c r="B196" s="49" t="inlineStr">
+        <is>
+          <t>E4_v3_clean</t>
+        </is>
+      </c>
+      <c r="C196" s="50" t="inlineStr">
+        <is>
+          <t>E4</t>
+        </is>
+      </c>
+      <c r="D196" s="50" t="inlineStr">
+        <is>
+          <t>arboles_boosting</t>
+        </is>
+      </c>
+      <c r="E196" s="50" t="inlineStr">
+        <is>
+          <t>xgboost_regressor</t>
+        </is>
+      </c>
+      <c r="F196" s="50" t="n">
+        <v>3</v>
+      </c>
+      <c r="G196" s="49" t="inlineStr">
+        <is>
+          <t>delta</t>
+        </is>
+      </c>
+      <c r="H196" s="50" t="inlineStr">
+        <is>
+          <t>y_t + lags [1, 2, 3, 4, 5, 6]</t>
+        </is>
+      </c>
+      <c r="I196" s="50" t="inlineStr">
+        <is>
+          <t>sentimiento_medios, v5_agua_neto, v5_alumbrado_neto, v5_americo_neto, v5_basura_neto, v5_corrupcion_neto, v5_delitos_neto, v5_morena_neto, v5_obras_neto, v5_prevencion_neto, v5_vialidad_neto</t>
+        </is>
+      </c>
+      <c r="J196" s="50" t="inlineStr">
+        <is>
+          <t>sin_escalar</t>
+        </is>
+      </c>
+      <c r="K196" s="50" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="L196" s="50" t="inlineStr">
+        <is>
+          <t>walk-forward_expanding</t>
+        </is>
+      </c>
+      <c r="M196" s="49" t="inlineStr">
+        <is>
+          <t>2024-10-14 a 2026-03-02</t>
+        </is>
+      </c>
+      <c r="N196" s="49" t="inlineStr">
+        <is>
+          <t>{"feature_candidates": 83, "feature_mode": "all", "horizon": 3, "initial_train_size": 40, "lags": [1, 2, 3, 4, 5, 6], "model": "xgboost_regressor", "model_params": {"colsample_bytree": 0.8, "learning_rate": 0.05, "max_depth": 3, "min_child_weight": 3.0, "n_estimators": 300, "random_state": 42, "reg_alpha": 0.0, "reg_lambda": 1.0, "subsample": 0.8, "tuning_strategy": "baseline_fijo_sin_tuning_interno", "uses_scaling": false}, "rows_eval": 24, "rows_modeling": 64, "selected_feature_count_avg": 83.0, "target_mode": "delta", "transform_mode": ""}</t>
+        </is>
+      </c>
+      <c r="O196" s="51" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="P196" s="51" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="Q196" s="51" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="R196" s="51" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="S196" s="52" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="T196" s="53" t="n">
+        <v>0.2960917237238554</v>
+      </c>
+      <c r="U196" s="53" t="n">
+        <v>0.5833333333333333</v>
+      </c>
+      <c r="V196" s="53" t="n">
+        <v>0.5454545454545454</v>
+      </c>
+      <c r="W196" s="53" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="X196" s="54" t="n">
+        <v>0.1419987219000957</v>
+      </c>
+      <c r="Y196" s="53" t="n">
+        <v>0.1821805201365609</v>
+      </c>
+      <c r="Z196" s="53" t="n">
+        <v>0.2172841481170919</v>
+      </c>
+      <c r="AA196" s="55" t="n">
+        <v>0.4166666666666667</v>
+      </c>
+      <c r="AB196" s="55" t="n">
+        <v>0.4545454545454545</v>
+      </c>
+      <c r="AC196" s="49" t="inlineStr">
+        <is>
+          <t>corrido</t>
+        </is>
+      </c>
+      <c r="AD196" s="49" t="inlineStr">
+        <is>
+          <t>XGBoost limpio con walk-forward temporal | hipotesis=boosting_delta_vs_nivel | baseline fijo sin tuning interno | sin escalado por naturaleza basada en arboles</t>
+        </is>
+      </c>
+      <c r="AE196" s="49" t="inlineStr">
+        <is>
+          <t>run_e4_xgboost.py</t>
+        </is>
+      </c>
+      <c r="AF196" s="49" t="inlineStr">
+        <is>
+          <t>Scripts/Modeling/run_e4_xgboost.py</t>
+        </is>
+      </c>
+      <c r="AG196" s="49" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E4_v3_clean_20260325_055134</t>
+        </is>
+      </c>
+      <c r="AH196" s="49" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E4_v3_clean_20260325_055134/scripts/run_e4_xgboost.py</t>
+        </is>
+      </c>
+      <c r="AI196" s="49" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E4_v3_clean_20260325_055134/parametros_run.json</t>
+        </is>
+      </c>
+      <c r="AJ196" s="49" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E4_v3_clean_20260325_055134/metricas_horizonte.json</t>
+        </is>
+      </c>
+      <c r="AK196" s="49" t="inlineStr">
+        <is>
+          <t>2026-03-25 05:51:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="197" ht="15" customHeight="1" s="27">
+      <c r="A197" s="49" t="inlineStr">
+        <is>
+          <t>2026-03-25 05:51:34</t>
+        </is>
+      </c>
+      <c r="B197" s="49" t="inlineStr">
+        <is>
+          <t>E4_v3_clean</t>
+        </is>
+      </c>
+      <c r="C197" s="50" t="inlineStr">
+        <is>
+          <t>E4</t>
+        </is>
+      </c>
+      <c r="D197" s="50" t="inlineStr">
+        <is>
+          <t>arboles_boosting</t>
+        </is>
+      </c>
+      <c r="E197" s="50" t="inlineStr">
+        <is>
+          <t>xgboost_regressor</t>
+        </is>
+      </c>
+      <c r="F197" s="50" t="n">
+        <v>4</v>
+      </c>
+      <c r="G197" s="49" t="inlineStr">
+        <is>
+          <t>delta</t>
+        </is>
+      </c>
+      <c r="H197" s="50" t="inlineStr">
+        <is>
+          <t>y_t + lags [1, 2, 3, 4, 5, 6]</t>
+        </is>
+      </c>
+      <c r="I197" s="50" t="inlineStr">
+        <is>
+          <t>sentimiento_medios, v5_agua_neto, v5_alumbrado_neto, v5_americo_neto, v5_basura_neto, v5_corrupcion_neto, v5_delitos_neto, v5_morena_neto, v5_obras_neto, v5_prevencion_neto, v5_vialidad_neto</t>
+        </is>
+      </c>
+      <c r="J197" s="50" t="inlineStr">
+        <is>
+          <t>sin_escalar</t>
+        </is>
+      </c>
+      <c r="K197" s="50" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="L197" s="50" t="inlineStr">
+        <is>
+          <t>walk-forward_expanding</t>
+        </is>
+      </c>
+      <c r="M197" s="49" t="inlineStr">
+        <is>
+          <t>2024-10-14 a 2026-03-02</t>
+        </is>
+      </c>
+      <c r="N197" s="49" t="inlineStr">
+        <is>
+          <t>{"feature_candidates": 83, "feature_mode": "all", "horizon": 4, "initial_train_size": 40, "lags": [1, 2, 3, 4, 5, 6], "model": "xgboost_regressor", "model_params": {"colsample_bytree": 0.8, "learning_rate": 0.05, "max_depth": 3, "min_child_weight": 3.0, "n_estimators": 300, "random_state": 42, "reg_alpha": 0.0, "reg_lambda": 1.0, "subsample": 0.8, "tuning_strategy": "baseline_fijo_sin_tuning_interno", "uses_scaling": false}, "rows_eval": 23, "rows_modeling": 63, "selected_feature_count_avg": 83.0, "target_mode": "delta", "transform_mode": ""}</t>
+        </is>
+      </c>
+      <c r="O197" s="51" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="P197" s="51" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="Q197" s="51" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="R197" s="51" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="S197" s="52" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="T197" s="53" t="n">
+        <v>0.1753545134906545</v>
+      </c>
+      <c r="U197" s="53" t="n">
+        <v>0.3913043478260869</v>
+      </c>
+      <c r="V197" s="53" t="n">
+        <v>0.3333333333333334</v>
+      </c>
+      <c r="W197" s="53" t="n">
+        <v>0.6956521739130435</v>
+      </c>
+      <c r="X197" s="54" t="n">
+        <v>0.04681480761043327</v>
+      </c>
+      <c r="Y197" s="53" t="n">
+        <v>0.1078928383213272</v>
+      </c>
+      <c r="Z197" s="53" t="n">
+        <v>0.1451686156153379</v>
+      </c>
+      <c r="AA197" s="55" t="n">
+        <v>0.6086956521739131</v>
+      </c>
+      <c r="AB197" s="55" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="AC197" s="49" t="inlineStr">
+        <is>
+          <t>corrido</t>
+        </is>
+      </c>
+      <c r="AD197" s="49" t="inlineStr">
+        <is>
+          <t>XGBoost limpio con walk-forward temporal | hipotesis=boosting_delta_vs_nivel | baseline fijo sin tuning interno | sin escalado por naturaleza basada en arboles</t>
+        </is>
+      </c>
+      <c r="AE197" s="49" t="inlineStr">
+        <is>
+          <t>run_e4_xgboost.py</t>
+        </is>
+      </c>
+      <c r="AF197" s="49" t="inlineStr">
+        <is>
+          <t>Scripts/Modeling/run_e4_xgboost.py</t>
+        </is>
+      </c>
+      <c r="AG197" s="49" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E4_v3_clean_20260325_055134</t>
+        </is>
+      </c>
+      <c r="AH197" s="49" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E4_v3_clean_20260325_055134/scripts/run_e4_xgboost.py</t>
+        </is>
+      </c>
+      <c r="AI197" s="49" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E4_v3_clean_20260325_055134/parametros_run.json</t>
+        </is>
+      </c>
+      <c r="AJ197" s="49" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E4_v3_clean_20260325_055134/metricas_horizonte.json</t>
+        </is>
+      </c>
+      <c r="AK197" s="49" t="inlineStr">
+        <is>
+          <t>2026-03-25 05:51:34</t>
         </is>
       </c>
     </row>
@@ -16775,7 +20543,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:W109"/>
+  <dimension ref="A1:W115"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.54296875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="14" customWidth="1" style="26" min="1" max="1"/>
@@ -23791,6 +27559,540 @@
       <c r="W109" s="49" t="inlineStr">
         <is>
           <t>2026-03-23 06:12:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="15" customHeight="1" s="27">
+      <c r="A110" s="49" t="inlineStr">
+        <is>
+          <t>E3_v1_clean</t>
+        </is>
+      </c>
+      <c r="B110" s="57" t="inlineStr">
+        <is>
+          <t>E3</t>
+        </is>
+      </c>
+      <c r="C110" s="57" t="inlineStr">
+        <is>
+          <t>random_forest_regressor</t>
+        </is>
+      </c>
+      <c r="D110" s="57" t="inlineStr">
+        <is>
+          <t>arboles_boosting</t>
+        </is>
+      </c>
+      <c r="E110" s="57" t="n">
+        <v>4</v>
+      </c>
+      <c r="F110" s="54" t="n">
+        <v>0.2808923211670988</v>
+      </c>
+      <c r="G110" s="53" t="n"/>
+      <c r="H110" s="58" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="I110" s="54" t="n">
+        <v>0.2808923211670988</v>
+      </c>
+      <c r="J110" s="54" t="n">
+        <v>0.1058858687581066</v>
+      </c>
+      <c r="K110" s="54" t="n">
+        <v>0.1365884005260111</v>
+      </c>
+      <c r="L110" s="51" t="n">
+        <v>0.7040691192865105</v>
+      </c>
+      <c r="M110" s="51" t="n">
+        <v>0.6809343434343436</v>
+      </c>
+      <c r="N110" s="49" t="n"/>
+      <c r="O110" s="57" t="n"/>
+      <c r="P110" s="49" t="inlineStr">
+        <is>
+          <t>Random Forest limpio con walk-forward temporal | hipotesis=baseline_no_lineal_corr_memoria_larga | sin escalado por naturaleza basada en arboles | L_total_Radar=0.280892</t>
+        </is>
+      </c>
+      <c r="Q110" s="49" t="inlineStr">
+        <is>
+          <t>run_e3_random_forest.py</t>
+        </is>
+      </c>
+      <c r="R110" s="49" t="inlineStr">
+        <is>
+          <t>Scripts/Modeling/run_e3_random_forest.py</t>
+        </is>
+      </c>
+      <c r="S110" s="49" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E3_v1_clean_20260323_073144</t>
+        </is>
+      </c>
+      <c r="T110" s="49" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E3_v1_clean_20260323_073144/scripts/run_e3_random_forest.py</t>
+        </is>
+      </c>
+      <c r="U110" s="49" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E3_v1_clean_20260323_073144/parametros_run.json</t>
+        </is>
+      </c>
+      <c r="V110" s="49" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E3_v1_clean_20260323_073144/metricas_horizonte.json</t>
+        </is>
+      </c>
+      <c r="W110" s="49" t="inlineStr">
+        <is>
+          <t>2026-03-23 07:31:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="15" customHeight="1" s="27">
+      <c r="A111" s="49" t="inlineStr">
+        <is>
+          <t>E3_v3_clean</t>
+        </is>
+      </c>
+      <c r="B111" s="57" t="inlineStr">
+        <is>
+          <t>E3</t>
+        </is>
+      </c>
+      <c r="C111" s="57" t="inlineStr">
+        <is>
+          <t>extra_trees_regressor</t>
+        </is>
+      </c>
+      <c r="D111" s="57" t="inlineStr">
+        <is>
+          <t>arboles_boosting</t>
+        </is>
+      </c>
+      <c r="E111" s="57" t="n">
+        <v>4</v>
+      </c>
+      <c r="F111" s="54" t="n">
+        <v>0.2872893466271498</v>
+      </c>
+      <c r="G111" s="53" t="n"/>
+      <c r="H111" s="58" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="I111" s="54" t="n">
+        <v>0.2872893466271498</v>
+      </c>
+      <c r="J111" s="54" t="n">
+        <v>0.1106823282463411</v>
+      </c>
+      <c r="K111" s="54" t="n">
+        <v>0.1413520736550114</v>
+      </c>
+      <c r="L111" s="51" t="n">
+        <v>0.7232998885172799</v>
+      </c>
+      <c r="M111" s="51" t="n">
+        <v>0.6559343434343434</v>
+      </c>
+      <c r="N111" s="49" t="n"/>
+      <c r="O111" s="57" t="n"/>
+      <c r="P111" s="49" t="inlineStr">
+        <is>
+          <t>ExtraTrees limpio con walk-forward temporal | hipotesis=extratrees_mas_aleatorio_h3_h4 | sin escalado por naturaleza basada en arboles | L_total_Radar=0.287289</t>
+        </is>
+      </c>
+      <c r="Q111" s="49" t="inlineStr">
+        <is>
+          <t>run_e3_random_forest.py</t>
+        </is>
+      </c>
+      <c r="R111" s="49" t="inlineStr">
+        <is>
+          <t>Scripts/Modeling/run_e3_random_forest.py</t>
+        </is>
+      </c>
+      <c r="S111" s="49" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E3_v3_clean_20260323_080110</t>
+        </is>
+      </c>
+      <c r="T111" s="49" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E3_v3_clean_20260323_080110/scripts/run_e3_random_forest.py</t>
+        </is>
+      </c>
+      <c r="U111" s="49" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E3_v3_clean_20260323_080110/parametros_run.json</t>
+        </is>
+      </c>
+      <c r="V111" s="49" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E3_v3_clean_20260323_080110/metricas_horizonte.json</t>
+        </is>
+      </c>
+      <c r="W111" s="49" t="inlineStr">
+        <is>
+          <t>2026-03-23 08:01:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="15" customHeight="1" s="27">
+      <c r="A112" s="49" t="inlineStr">
+        <is>
+          <t>E3_v2_clean</t>
+        </is>
+      </c>
+      <c r="B112" s="57" t="inlineStr">
+        <is>
+          <t>E3</t>
+        </is>
+      </c>
+      <c r="C112" s="57" t="inlineStr">
+        <is>
+          <t>random_forest_regressor</t>
+        </is>
+      </c>
+      <c r="D112" s="57" t="inlineStr">
+        <is>
+          <t>arboles_boosting</t>
+        </is>
+      </c>
+      <c r="E112" s="57" t="n">
+        <v>4</v>
+      </c>
+      <c r="F112" s="54" t="n">
+        <v>0.2663866980744075</v>
+      </c>
+      <c r="G112" s="53" t="n"/>
+      <c r="H112" s="58" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="I112" s="54" t="n">
+        <v>0.2663866980744075</v>
+      </c>
+      <c r="J112" s="54" t="n">
+        <v>0.1042173574368047</v>
+      </c>
+      <c r="K112" s="54" t="n">
+        <v>0.1346575123322115</v>
+      </c>
+      <c r="L112" s="51" t="n">
+        <v>0.7337527870680044</v>
+      </c>
+      <c r="M112" s="51" t="n">
+        <v>0.7087121212121212</v>
+      </c>
+      <c r="N112" s="49" t="n"/>
+      <c r="O112" s="57" t="n"/>
+      <c r="P112" s="49" t="inlineStr">
+        <is>
+          <t>Random Forest limpio con walk-forward temporal | hipotesis=random_forest_base_amplia | sin escalado por naturaleza basada en arboles | L_total_Radar=0.266387</t>
+        </is>
+      </c>
+      <c r="Q112" s="49" t="inlineStr">
+        <is>
+          <t>run_e3_random_forest.py</t>
+        </is>
+      </c>
+      <c r="R112" s="49" t="inlineStr">
+        <is>
+          <t>Scripts/Modeling/run_e3_random_forest.py</t>
+        </is>
+      </c>
+      <c r="S112" s="49" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E3_v2_clean_20260325_045918</t>
+        </is>
+      </c>
+      <c r="T112" s="49" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E3_v2_clean_20260325_045918/scripts/run_e3_random_forest.py</t>
+        </is>
+      </c>
+      <c r="U112" s="49" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E3_v2_clean_20260325_045918/parametros_run.json</t>
+        </is>
+      </c>
+      <c r="V112" s="49" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E3_v2_clean_20260325_045918/metricas_horizonte.json</t>
+        </is>
+      </c>
+      <c r="W112" s="49" t="inlineStr">
+        <is>
+          <t>2026-03-25 04:59:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" ht="15" customHeight="1" s="27">
+      <c r="A113" s="49" t="inlineStr">
+        <is>
+          <t>E4_v1_clean</t>
+        </is>
+      </c>
+      <c r="B113" s="57" t="inlineStr">
+        <is>
+          <t>E4</t>
+        </is>
+      </c>
+      <c r="C113" s="57" t="inlineStr">
+        <is>
+          <t>xgboost_regressor</t>
+        </is>
+      </c>
+      <c r="D113" s="57" t="inlineStr">
+        <is>
+          <t>arboles_boosting</t>
+        </is>
+      </c>
+      <c r="E113" s="57" t="n">
+        <v>4</v>
+      </c>
+      <c r="F113" s="54" t="n">
+        <v>0.2839341113264429</v>
+      </c>
+      <c r="G113" s="53" t="n"/>
+      <c r="H113" s="58" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="I113" s="54" t="n">
+        <v>0.2839341113264429</v>
+      </c>
+      <c r="J113" s="54" t="n">
+        <v>0.1132736868627532</v>
+      </c>
+      <c r="K113" s="54" t="n">
+        <v>0.1422368515217783</v>
+      </c>
+      <c r="L113" s="51" t="n">
+        <v>0.693756967670011</v>
+      </c>
+      <c r="M113" s="51" t="n">
+        <v>0.7087121212121212</v>
+      </c>
+      <c r="N113" s="49" t="n"/>
+      <c r="O113" s="57" t="n"/>
+      <c r="P113" s="49" t="inlineStr">
+        <is>
+          <t>XGBoost limpio con walk-forward temporal | hipotesis=boosting_base_conservador | baseline fijo sin tuning interno | sin escalado por naturaleza basada en arboles | L_total_Radar=0.283934</t>
+        </is>
+      </c>
+      <c r="Q113" s="49" t="inlineStr">
+        <is>
+          <t>run_e4_xgboost.py</t>
+        </is>
+      </c>
+      <c r="R113" s="49" t="inlineStr">
+        <is>
+          <t>Scripts/Modeling/run_e4_xgboost.py</t>
+        </is>
+      </c>
+      <c r="S113" s="49" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E4_v1_clean_20260325_052051</t>
+        </is>
+      </c>
+      <c r="T113" s="49" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E4_v1_clean_20260325_052051/scripts/run_e4_xgboost.py</t>
+        </is>
+      </c>
+      <c r="U113" s="49" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E4_v1_clean_20260325_052051/parametros_run.json</t>
+        </is>
+      </c>
+      <c r="V113" s="49" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E4_v1_clean_20260325_052051/metricas_horizonte.json</t>
+        </is>
+      </c>
+      <c r="W113" s="49" t="inlineStr">
+        <is>
+          <t>2026-03-25 05:20:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="114" ht="15" customHeight="1" s="27">
+      <c r="A114" s="49" t="inlineStr">
+        <is>
+          <t>E4_v2_clean</t>
+        </is>
+      </c>
+      <c r="B114" s="57" t="inlineStr">
+        <is>
+          <t>E4</t>
+        </is>
+      </c>
+      <c r="C114" s="57" t="inlineStr">
+        <is>
+          <t>xgboost_regressor</t>
+        </is>
+      </c>
+      <c r="D114" s="57" t="inlineStr">
+        <is>
+          <t>arboles_boosting</t>
+        </is>
+      </c>
+      <c r="E114" s="57" t="n">
+        <v>4</v>
+      </c>
+      <c r="F114" s="54" t="n">
+        <v>0.2973425926212152</v>
+      </c>
+      <c r="G114" s="53" t="n"/>
+      <c r="H114" s="58" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="I114" s="54" t="n">
+        <v>0.2973425926212152</v>
+      </c>
+      <c r="J114" s="54" t="n">
+        <v>0.1111074574588021</v>
+      </c>
+      <c r="K114" s="54" t="n">
+        <v>0.1387522342283121</v>
+      </c>
+      <c r="L114" s="51" t="n">
+        <v>0.6932678372352286</v>
+      </c>
+      <c r="M114" s="51" t="n">
+        <v>0.6609848484848485</v>
+      </c>
+      <c r="N114" s="49" t="n"/>
+      <c r="O114" s="57" t="n"/>
+      <c r="P114" s="49" t="inlineStr">
+        <is>
+          <t>XGBoost limpio con walk-forward temporal | hipotesis=boosting_corr_vs_all | baseline fijo sin tuning interno | sin escalado por naturaleza basada en arboles | L_total_Radar=0.297343</t>
+        </is>
+      </c>
+      <c r="Q114" s="49" t="inlineStr">
+        <is>
+          <t>run_e4_xgboost.py</t>
+        </is>
+      </c>
+      <c r="R114" s="49" t="inlineStr">
+        <is>
+          <t>Scripts/Modeling/run_e4_xgboost.py</t>
+        </is>
+      </c>
+      <c r="S114" s="49" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E4_v2_clean_20260325_055117</t>
+        </is>
+      </c>
+      <c r="T114" s="49" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E4_v2_clean_20260325_055117/scripts/run_e4_xgboost.py</t>
+        </is>
+      </c>
+      <c r="U114" s="49" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E4_v2_clean_20260325_055117/parametros_run.json</t>
+        </is>
+      </c>
+      <c r="V114" s="49" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E4_v2_clean_20260325_055117/metricas_horizonte.json</t>
+        </is>
+      </c>
+      <c r="W114" s="49" t="inlineStr">
+        <is>
+          <t>2026-03-25 05:51:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" ht="15" customHeight="1" s="27">
+      <c r="A115" s="49" t="inlineStr">
+        <is>
+          <t>E4_v3_clean</t>
+        </is>
+      </c>
+      <c r="B115" s="57" t="inlineStr">
+        <is>
+          <t>E4</t>
+        </is>
+      </c>
+      <c r="C115" s="57" t="inlineStr">
+        <is>
+          <t>xgboost_regressor</t>
+        </is>
+      </c>
+      <c r="D115" s="57" t="inlineStr">
+        <is>
+          <t>arboles_boosting</t>
+        </is>
+      </c>
+      <c r="E115" s="57" t="n">
+        <v>4</v>
+      </c>
+      <c r="F115" s="54" t="n">
+        <v>0.4247743104980723</v>
+      </c>
+      <c r="G115" s="53" t="n"/>
+      <c r="H115" s="58" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="I115" s="54" t="n">
+        <v>0.4247743104980723</v>
+      </c>
+      <c r="J115" s="54" t="n">
+        <v>0.146455603877573</v>
+      </c>
+      <c r="K115" s="54" t="n">
+        <v>0.1813787575610373</v>
+      </c>
+      <c r="L115" s="51" t="n">
+        <v>0.4924944258639911</v>
+      </c>
+      <c r="M115" s="51" t="n">
+        <v>0.5178030303030303</v>
+      </c>
+      <c r="N115" s="49" t="n"/>
+      <c r="O115" s="57" t="n"/>
+      <c r="P115" s="49" t="inlineStr">
+        <is>
+          <t>XGBoost limpio con walk-forward temporal | hipotesis=boosting_delta_vs_nivel | baseline fijo sin tuning interno | sin escalado por naturaleza basada en arboles | L_total_Radar=0.424774</t>
+        </is>
+      </c>
+      <c r="Q115" s="49" t="inlineStr">
+        <is>
+          <t>run_e4_xgboost.py</t>
+        </is>
+      </c>
+      <c r="R115" s="49" t="inlineStr">
+        <is>
+          <t>Scripts/Modeling/run_e4_xgboost.py</t>
+        </is>
+      </c>
+      <c r="S115" s="49" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E4_v3_clean_20260325_055134</t>
+        </is>
+      </c>
+      <c r="T115" s="49" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E4_v3_clean_20260325_055134/scripts/run_e4_xgboost.py</t>
+        </is>
+      </c>
+      <c r="U115" s="49" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E4_v3_clean_20260325_055134/parametros_run.json</t>
+        </is>
+      </c>
+      <c r="V115" s="49" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E4_v3_clean_20260325_055134/metricas_horizonte.json</t>
+        </is>
+      </c>
+      <c r="W115" s="49" t="inlineStr">
+        <is>
+          <t>2026-03-25 05:51:34</t>
         </is>
       </c>
     </row>
@@ -23834,7 +28136,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:G119"/>
+  <dimension ref="A1:G207"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.54296875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="26" customWidth="1" style="26" min="1" max="6"/>
@@ -28216,6 +32518,3262 @@
         </is>
       </c>
     </row>
+    <row r="120" ht="15" customHeight="1" s="27">
+      <c r="A120" s="61" t="inlineStr">
+        <is>
+          <t>2026-03-23 07:32:24</t>
+        </is>
+      </c>
+      <c r="B120" s="61" t="inlineStr">
+        <is>
+          <t>E3_v1_clean</t>
+        </is>
+      </c>
+      <c r="C120" s="61" t="inlineStr">
+        <is>
+          <t>E3</t>
+        </is>
+      </c>
+      <c r="D120" s="61" t="inlineStr">
+        <is>
+          <t>script_snapshot</t>
+        </is>
+      </c>
+      <c r="E120" s="61" t="inlineStr">
+        <is>
+          <t>run_e3_random_forest.py</t>
+        </is>
+      </c>
+      <c r="F120" s="61" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E3_v1_clean_20260323_073144/scripts/run_e3_random_forest.py</t>
+        </is>
+      </c>
+      <c r="G120" s="61" t="inlineStr">
+        <is>
+          <t>Copia del script ejecutado para reproducibilidad.</t>
+        </is>
+      </c>
+    </row>
+    <row r="121" ht="15" customHeight="1" s="27">
+      <c r="A121" s="61" t="inlineStr">
+        <is>
+          <t>2026-03-23 07:32:24</t>
+        </is>
+      </c>
+      <c r="B121" s="61" t="inlineStr">
+        <is>
+          <t>E3_v1_clean</t>
+        </is>
+      </c>
+      <c r="C121" s="61" t="inlineStr">
+        <is>
+          <t>E3</t>
+        </is>
+      </c>
+      <c r="D121" s="61" t="inlineStr">
+        <is>
+          <t>parametros</t>
+        </is>
+      </c>
+      <c r="E121" s="61" t="inlineStr">
+        <is>
+          <t>parametros_run.json</t>
+        </is>
+      </c>
+      <c r="F121" s="61" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E3_v1_clean_20260323_073144/parametros_run.json</t>
+        </is>
+      </c>
+      <c r="G121" s="61" t="inlineStr">
+        <is>
+          <t>Parametros del experimento.</t>
+        </is>
+      </c>
+    </row>
+    <row r="122" ht="15" customHeight="1" s="27">
+      <c r="A122" s="61" t="inlineStr">
+        <is>
+          <t>2026-03-23 07:32:24</t>
+        </is>
+      </c>
+      <c r="B122" s="61" t="inlineStr">
+        <is>
+          <t>E3_v1_clean</t>
+        </is>
+      </c>
+      <c r="C122" s="61" t="inlineStr">
+        <is>
+          <t>E3</t>
+        </is>
+      </c>
+      <c r="D122" s="61" t="inlineStr">
+        <is>
+          <t>seleccion_features</t>
+        </is>
+      </c>
+      <c r="E122" s="61" t="inlineStr">
+        <is>
+          <t>features_seleccionadas_h1.csv</t>
+        </is>
+      </c>
+      <c r="F122" s="61" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E3_v1_clean_20260323_073144/features_seleccionadas_h1.csv</t>
+        </is>
+      </c>
+      <c r="G122" s="61" t="inlineStr">
+        <is>
+          <t>Resumen de combinaciones de features seleccionadas por fold externo. El filtro se calcula solo con el train de cada fold externo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="123" ht="15" customHeight="1" s="27">
+      <c r="A123" s="61" t="inlineStr">
+        <is>
+          <t>2026-03-23 07:32:24</t>
+        </is>
+      </c>
+      <c r="B123" s="61" t="inlineStr">
+        <is>
+          <t>E3_v1_clean</t>
+        </is>
+      </c>
+      <c r="C123" s="61" t="inlineStr">
+        <is>
+          <t>E3</t>
+        </is>
+      </c>
+      <c r="D123" s="61" t="inlineStr">
+        <is>
+          <t>seleccion_features</t>
+        </is>
+      </c>
+      <c r="E123" s="61" t="inlineStr">
+        <is>
+          <t>features_seleccionadas_h2.csv</t>
+        </is>
+      </c>
+      <c r="F123" s="61" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E3_v1_clean_20260323_073144/features_seleccionadas_h2.csv</t>
+        </is>
+      </c>
+      <c r="G123" s="61" t="inlineStr">
+        <is>
+          <t>Resumen de combinaciones de features seleccionadas por fold externo. El filtro se calcula solo con el train de cada fold externo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="124" ht="15" customHeight="1" s="27">
+      <c r="A124" s="61" t="inlineStr">
+        <is>
+          <t>2026-03-23 07:32:24</t>
+        </is>
+      </c>
+      <c r="B124" s="61" t="inlineStr">
+        <is>
+          <t>E3_v1_clean</t>
+        </is>
+      </c>
+      <c r="C124" s="61" t="inlineStr">
+        <is>
+          <t>E3</t>
+        </is>
+      </c>
+      <c r="D124" s="61" t="inlineStr">
+        <is>
+          <t>seleccion_features</t>
+        </is>
+      </c>
+      <c r="E124" s="61" t="inlineStr">
+        <is>
+          <t>features_seleccionadas_h3.csv</t>
+        </is>
+      </c>
+      <c r="F124" s="61" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E3_v1_clean_20260323_073144/features_seleccionadas_h3.csv</t>
+        </is>
+      </c>
+      <c r="G124" s="61" t="inlineStr">
+        <is>
+          <t>Resumen de combinaciones de features seleccionadas por fold externo. El filtro se calcula solo con el train de cada fold externo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="125" ht="15" customHeight="1" s="27">
+      <c r="A125" s="61" t="inlineStr">
+        <is>
+          <t>2026-03-23 07:32:24</t>
+        </is>
+      </c>
+      <c r="B125" s="61" t="inlineStr">
+        <is>
+          <t>E3_v1_clean</t>
+        </is>
+      </c>
+      <c r="C125" s="61" t="inlineStr">
+        <is>
+          <t>E3</t>
+        </is>
+      </c>
+      <c r="D125" s="61" t="inlineStr">
+        <is>
+          <t>seleccion_features</t>
+        </is>
+      </c>
+      <c r="E125" s="61" t="inlineStr">
+        <is>
+          <t>features_seleccionadas_h4.csv</t>
+        </is>
+      </c>
+      <c r="F125" s="61" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E3_v1_clean_20260323_073144/features_seleccionadas_h4.csv</t>
+        </is>
+      </c>
+      <c r="G125" s="61" t="inlineStr">
+        <is>
+          <t>Resumen de combinaciones de features seleccionadas por fold externo. El filtro se calcula solo con el train de cada fold externo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="126" ht="15" customHeight="1" s="27">
+      <c r="A126" s="61" t="inlineStr">
+        <is>
+          <t>2026-03-23 07:32:24</t>
+        </is>
+      </c>
+      <c r="B126" s="61" t="inlineStr">
+        <is>
+          <t>E3_v1_clean</t>
+        </is>
+      </c>
+      <c r="C126" s="61" t="inlineStr">
+        <is>
+          <t>E3</t>
+        </is>
+      </c>
+      <c r="D126" s="61" t="inlineStr">
+        <is>
+          <t>predicciones</t>
+        </is>
+      </c>
+      <c r="E126" s="61" t="inlineStr">
+        <is>
+          <t>predicciones_h1.csv</t>
+        </is>
+      </c>
+      <c r="F126" s="61" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E3_v1_clean_20260323_073144/predicciones_h1.csv</t>
+        </is>
+      </c>
+      <c r="G126" s="61" t="inlineStr">
+        <is>
+          <t>Predicciones walk-forward para horizonte 1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="127" ht="15" customHeight="1" s="27">
+      <c r="A127" s="61" t="inlineStr">
+        <is>
+          <t>2026-03-23 07:32:24</t>
+        </is>
+      </c>
+      <c r="B127" s="61" t="inlineStr">
+        <is>
+          <t>E3_v1_clean</t>
+        </is>
+      </c>
+      <c r="C127" s="61" t="inlineStr">
+        <is>
+          <t>E3</t>
+        </is>
+      </c>
+      <c r="D127" s="61" t="inlineStr">
+        <is>
+          <t>predicciones</t>
+        </is>
+      </c>
+      <c r="E127" s="61" t="inlineStr">
+        <is>
+          <t>predicciones_h2.csv</t>
+        </is>
+      </c>
+      <c r="F127" s="61" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E3_v1_clean_20260323_073144/predicciones_h2.csv</t>
+        </is>
+      </c>
+      <c r="G127" s="61" t="inlineStr">
+        <is>
+          <t>Predicciones walk-forward para horizonte 2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="128" ht="15" customHeight="1" s="27">
+      <c r="A128" s="61" t="inlineStr">
+        <is>
+          <t>2026-03-23 07:32:24</t>
+        </is>
+      </c>
+      <c r="B128" s="61" t="inlineStr">
+        <is>
+          <t>E3_v1_clean</t>
+        </is>
+      </c>
+      <c r="C128" s="61" t="inlineStr">
+        <is>
+          <t>E3</t>
+        </is>
+      </c>
+      <c r="D128" s="61" t="inlineStr">
+        <is>
+          <t>predicciones</t>
+        </is>
+      </c>
+      <c r="E128" s="61" t="inlineStr">
+        <is>
+          <t>predicciones_h3.csv</t>
+        </is>
+      </c>
+      <c r="F128" s="61" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E3_v1_clean_20260323_073144/predicciones_h3.csv</t>
+        </is>
+      </c>
+      <c r="G128" s="61" t="inlineStr">
+        <is>
+          <t>Predicciones walk-forward para horizonte 3.</t>
+        </is>
+      </c>
+    </row>
+    <row r="129" ht="15" customHeight="1" s="27">
+      <c r="A129" s="61" t="inlineStr">
+        <is>
+          <t>2026-03-23 07:32:24</t>
+        </is>
+      </c>
+      <c r="B129" s="61" t="inlineStr">
+        <is>
+          <t>E3_v1_clean</t>
+        </is>
+      </c>
+      <c r="C129" s="61" t="inlineStr">
+        <is>
+          <t>E3</t>
+        </is>
+      </c>
+      <c r="D129" s="61" t="inlineStr">
+        <is>
+          <t>predicciones</t>
+        </is>
+      </c>
+      <c r="E129" s="61" t="inlineStr">
+        <is>
+          <t>predicciones_h4.csv</t>
+        </is>
+      </c>
+      <c r="F129" s="61" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E3_v1_clean_20260323_073144/predicciones_h4.csv</t>
+        </is>
+      </c>
+      <c r="G129" s="61" t="inlineStr">
+        <is>
+          <t>Predicciones walk-forward para horizonte 4.</t>
+        </is>
+      </c>
+    </row>
+    <row r="130" ht="15" customHeight="1" s="27">
+      <c r="A130" s="61" t="inlineStr">
+        <is>
+          <t>2026-03-23 07:32:24</t>
+        </is>
+      </c>
+      <c r="B130" s="61" t="inlineStr">
+        <is>
+          <t>E3_v1_clean</t>
+        </is>
+      </c>
+      <c r="C130" s="61" t="inlineStr">
+        <is>
+          <t>E3</t>
+        </is>
+      </c>
+      <c r="D130" s="61" t="inlineStr">
+        <is>
+          <t>resumen</t>
+        </is>
+      </c>
+      <c r="E130" s="61" t="inlineStr">
+        <is>
+          <t>resumen_modeling_horizontes.json</t>
+        </is>
+      </c>
+      <c r="F130" s="61" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E3_v1_clean_20260323_073144/resumen_modeling_horizontes.json</t>
+        </is>
+      </c>
+      <c r="G130" s="61" t="inlineStr">
+        <is>
+          <t>Resumen de tamanos y seleccion de features por horizonte.</t>
+        </is>
+      </c>
+    </row>
+    <row r="131" ht="15" customHeight="1" s="27">
+      <c r="A131" s="61" t="inlineStr">
+        <is>
+          <t>2026-03-23 07:32:24</t>
+        </is>
+      </c>
+      <c r="B131" s="61" t="inlineStr">
+        <is>
+          <t>E3_v1_clean</t>
+        </is>
+      </c>
+      <c r="C131" s="61" t="inlineStr">
+        <is>
+          <t>E3</t>
+        </is>
+      </c>
+      <c r="D131" s="61" t="inlineStr">
+        <is>
+          <t>comparacion</t>
+        </is>
+      </c>
+      <c r="E131" s="61" t="inlineStr">
+        <is>
+          <t>comparacion_vs_E1_v5_clean.json</t>
+        </is>
+      </c>
+      <c r="F131" s="61" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E3_v1_clean_20260323_073144/comparacion_vs_E1_v5_clean.json</t>
+        </is>
+      </c>
+      <c r="G131" s="61" t="inlineStr">
+        <is>
+          <t>Comparacion de la corrida clean contra E1_v5_clean.</t>
+        </is>
+      </c>
+    </row>
+    <row r="132" ht="15" customHeight="1" s="27">
+      <c r="A132" s="61" t="inlineStr">
+        <is>
+          <t>2026-03-23 07:32:24</t>
+        </is>
+      </c>
+      <c r="B132" s="61" t="inlineStr">
+        <is>
+          <t>E3_v1_clean</t>
+        </is>
+      </c>
+      <c r="C132" s="61" t="inlineStr">
+        <is>
+          <t>E3</t>
+        </is>
+      </c>
+      <c r="D132" s="61" t="inlineStr">
+        <is>
+          <t>comparacion</t>
+        </is>
+      </c>
+      <c r="E132" s="61" t="inlineStr">
+        <is>
+          <t>comparacion_vs_E1_v4_clean.json</t>
+        </is>
+      </c>
+      <c r="F132" s="61" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E3_v1_clean_20260323_073144/comparacion_vs_E1_v4_clean.json</t>
+        </is>
+      </c>
+      <c r="G132" s="61" t="inlineStr">
+        <is>
+          <t>Comparacion de la corrida clean contra E1_v4_clean.</t>
+        </is>
+      </c>
+    </row>
+    <row r="133" ht="15" customHeight="1" s="27">
+      <c r="A133" s="61" t="inlineStr">
+        <is>
+          <t>2026-03-23 07:32:24</t>
+        </is>
+      </c>
+      <c r="B133" s="61" t="inlineStr">
+        <is>
+          <t>E3_v1_clean</t>
+        </is>
+      </c>
+      <c r="C133" s="61" t="inlineStr">
+        <is>
+          <t>E3</t>
+        </is>
+      </c>
+      <c r="D133" s="61" t="inlineStr">
+        <is>
+          <t>comparacion</t>
+        </is>
+      </c>
+      <c r="E133" s="61" t="inlineStr">
+        <is>
+          <t>comparacion_vs_E2_v3_clean.json</t>
+        </is>
+      </c>
+      <c r="F133" s="61" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E3_v1_clean_20260323_073144/comparacion_vs_E2_v3_clean.json</t>
+        </is>
+      </c>
+      <c r="G133" s="61" t="inlineStr">
+        <is>
+          <t>Comparacion de la corrida clean contra E2_v3_clean.</t>
+        </is>
+      </c>
+    </row>
+    <row r="134" ht="15" customHeight="1" s="27">
+      <c r="A134" s="61" t="inlineStr">
+        <is>
+          <t>2026-03-23 07:32:24</t>
+        </is>
+      </c>
+      <c r="B134" s="61" t="inlineStr">
+        <is>
+          <t>E3_v1_clean</t>
+        </is>
+      </c>
+      <c r="C134" s="61" t="inlineStr">
+        <is>
+          <t>E3</t>
+        </is>
+      </c>
+      <c r="D134" s="61" t="inlineStr">
+        <is>
+          <t>metricas</t>
+        </is>
+      </c>
+      <c r="E134" s="61" t="inlineStr">
+        <is>
+          <t>metricas_horizonte.json</t>
+        </is>
+      </c>
+      <c r="F134" s="61" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E3_v1_clean_20260323_073144/metricas_horizonte.json</t>
+        </is>
+      </c>
+      <c r="G134" s="61" t="inlineStr">
+        <is>
+          <t>Resumen estructurado por horizonte.</t>
+        </is>
+      </c>
+    </row>
+    <row r="135" ht="15" customHeight="1" s="27">
+      <c r="A135" s="61" t="inlineStr">
+        <is>
+          <t>2026-03-23 07:32:24</t>
+        </is>
+      </c>
+      <c r="B135" s="61" t="inlineStr">
+        <is>
+          <t>E3_v1_clean</t>
+        </is>
+      </c>
+      <c r="C135" s="61" t="inlineStr">
+        <is>
+          <t>E3</t>
+        </is>
+      </c>
+      <c r="D135" s="61" t="inlineStr">
+        <is>
+          <t>metadata</t>
+        </is>
+      </c>
+      <c r="E135" s="61" t="inlineStr">
+        <is>
+          <t>metadata_run.json</t>
+        </is>
+      </c>
+      <c r="F135" s="61" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E3_v1_clean_20260323_073144/metadata_run.json</t>
+        </is>
+      </c>
+      <c r="G135" s="61" t="inlineStr">
+        <is>
+          <t>Metadata base del run.</t>
+        </is>
+      </c>
+    </row>
+    <row r="136" ht="15" customHeight="1" s="27">
+      <c r="A136" s="61" t="inlineStr">
+        <is>
+          <t>2026-03-23 08:01:52</t>
+        </is>
+      </c>
+      <c r="B136" s="61" t="inlineStr">
+        <is>
+          <t>E3_v3_clean</t>
+        </is>
+      </c>
+      <c r="C136" s="61" t="inlineStr">
+        <is>
+          <t>E3</t>
+        </is>
+      </c>
+      <c r="D136" s="61" t="inlineStr">
+        <is>
+          <t>script_snapshot</t>
+        </is>
+      </c>
+      <c r="E136" s="61" t="inlineStr">
+        <is>
+          <t>run_e3_random_forest.py</t>
+        </is>
+      </c>
+      <c r="F136" s="61" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E3_v3_clean_20260323_080110/scripts/run_e3_random_forest.py</t>
+        </is>
+      </c>
+      <c r="G136" s="61" t="inlineStr">
+        <is>
+          <t>Copia del script ejecutado para reproducibilidad.</t>
+        </is>
+      </c>
+    </row>
+    <row r="137" ht="15" customHeight="1" s="27">
+      <c r="A137" s="61" t="inlineStr">
+        <is>
+          <t>2026-03-23 08:01:52</t>
+        </is>
+      </c>
+      <c r="B137" s="61" t="inlineStr">
+        <is>
+          <t>E3_v3_clean</t>
+        </is>
+      </c>
+      <c r="C137" s="61" t="inlineStr">
+        <is>
+          <t>E3</t>
+        </is>
+      </c>
+      <c r="D137" s="61" t="inlineStr">
+        <is>
+          <t>parametros</t>
+        </is>
+      </c>
+      <c r="E137" s="61" t="inlineStr">
+        <is>
+          <t>parametros_run.json</t>
+        </is>
+      </c>
+      <c r="F137" s="61" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E3_v3_clean_20260323_080110/parametros_run.json</t>
+        </is>
+      </c>
+      <c r="G137" s="61" t="inlineStr">
+        <is>
+          <t>Parametros del experimento.</t>
+        </is>
+      </c>
+    </row>
+    <row r="138" ht="15" customHeight="1" s="27">
+      <c r="A138" s="61" t="inlineStr">
+        <is>
+          <t>2026-03-23 08:01:52</t>
+        </is>
+      </c>
+      <c r="B138" s="61" t="inlineStr">
+        <is>
+          <t>E3_v3_clean</t>
+        </is>
+      </c>
+      <c r="C138" s="61" t="inlineStr">
+        <is>
+          <t>E3</t>
+        </is>
+      </c>
+      <c r="D138" s="61" t="inlineStr">
+        <is>
+          <t>seleccion_features</t>
+        </is>
+      </c>
+      <c r="E138" s="61" t="inlineStr">
+        <is>
+          <t>features_seleccionadas_h1.csv</t>
+        </is>
+      </c>
+      <c r="F138" s="61" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E3_v3_clean_20260323_080110/features_seleccionadas_h1.csv</t>
+        </is>
+      </c>
+      <c r="G138" s="61" t="inlineStr">
+        <is>
+          <t>Resumen de combinaciones de features seleccionadas por fold externo. El filtro se calcula solo con el train de cada fold externo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="139" ht="15" customHeight="1" s="27">
+      <c r="A139" s="61" t="inlineStr">
+        <is>
+          <t>2026-03-23 08:01:52</t>
+        </is>
+      </c>
+      <c r="B139" s="61" t="inlineStr">
+        <is>
+          <t>E3_v3_clean</t>
+        </is>
+      </c>
+      <c r="C139" s="61" t="inlineStr">
+        <is>
+          <t>E3</t>
+        </is>
+      </c>
+      <c r="D139" s="61" t="inlineStr">
+        <is>
+          <t>seleccion_features</t>
+        </is>
+      </c>
+      <c r="E139" s="61" t="inlineStr">
+        <is>
+          <t>features_seleccionadas_h2.csv</t>
+        </is>
+      </c>
+      <c r="F139" s="61" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E3_v3_clean_20260323_080110/features_seleccionadas_h2.csv</t>
+        </is>
+      </c>
+      <c r="G139" s="61" t="inlineStr">
+        <is>
+          <t>Resumen de combinaciones de features seleccionadas por fold externo. El filtro se calcula solo con el train de cada fold externo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="140" ht="15" customHeight="1" s="27">
+      <c r="A140" s="61" t="inlineStr">
+        <is>
+          <t>2026-03-23 08:01:52</t>
+        </is>
+      </c>
+      <c r="B140" s="61" t="inlineStr">
+        <is>
+          <t>E3_v3_clean</t>
+        </is>
+      </c>
+      <c r="C140" s="61" t="inlineStr">
+        <is>
+          <t>E3</t>
+        </is>
+      </c>
+      <c r="D140" s="61" t="inlineStr">
+        <is>
+          <t>seleccion_features</t>
+        </is>
+      </c>
+      <c r="E140" s="61" t="inlineStr">
+        <is>
+          <t>features_seleccionadas_h3.csv</t>
+        </is>
+      </c>
+      <c r="F140" s="61" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E3_v3_clean_20260323_080110/features_seleccionadas_h3.csv</t>
+        </is>
+      </c>
+      <c r="G140" s="61" t="inlineStr">
+        <is>
+          <t>Resumen de combinaciones de features seleccionadas por fold externo. El filtro se calcula solo con el train de cada fold externo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="141" ht="15" customHeight="1" s="27">
+      <c r="A141" s="61" t="inlineStr">
+        <is>
+          <t>2026-03-23 08:01:52</t>
+        </is>
+      </c>
+      <c r="B141" s="61" t="inlineStr">
+        <is>
+          <t>E3_v3_clean</t>
+        </is>
+      </c>
+      <c r="C141" s="61" t="inlineStr">
+        <is>
+          <t>E3</t>
+        </is>
+      </c>
+      <c r="D141" s="61" t="inlineStr">
+        <is>
+          <t>seleccion_features</t>
+        </is>
+      </c>
+      <c r="E141" s="61" t="inlineStr">
+        <is>
+          <t>features_seleccionadas_h4.csv</t>
+        </is>
+      </c>
+      <c r="F141" s="61" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E3_v3_clean_20260323_080110/features_seleccionadas_h4.csv</t>
+        </is>
+      </c>
+      <c r="G141" s="61" t="inlineStr">
+        <is>
+          <t>Resumen de combinaciones de features seleccionadas por fold externo. El filtro se calcula solo con el train de cada fold externo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="142" ht="15" customHeight="1" s="27">
+      <c r="A142" s="61" t="inlineStr">
+        <is>
+          <t>2026-03-23 08:01:52</t>
+        </is>
+      </c>
+      <c r="B142" s="61" t="inlineStr">
+        <is>
+          <t>E3_v3_clean</t>
+        </is>
+      </c>
+      <c r="C142" s="61" t="inlineStr">
+        <is>
+          <t>E3</t>
+        </is>
+      </c>
+      <c r="D142" s="61" t="inlineStr">
+        <is>
+          <t>predicciones</t>
+        </is>
+      </c>
+      <c r="E142" s="61" t="inlineStr">
+        <is>
+          <t>predicciones_h1.csv</t>
+        </is>
+      </c>
+      <c r="F142" s="61" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E3_v3_clean_20260323_080110/predicciones_h1.csv</t>
+        </is>
+      </c>
+      <c r="G142" s="61" t="inlineStr">
+        <is>
+          <t>Predicciones walk-forward para horizonte 1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="143" ht="15" customHeight="1" s="27">
+      <c r="A143" s="61" t="inlineStr">
+        <is>
+          <t>2026-03-23 08:01:52</t>
+        </is>
+      </c>
+      <c r="B143" s="61" t="inlineStr">
+        <is>
+          <t>E3_v3_clean</t>
+        </is>
+      </c>
+      <c r="C143" s="61" t="inlineStr">
+        <is>
+          <t>E3</t>
+        </is>
+      </c>
+      <c r="D143" s="61" t="inlineStr">
+        <is>
+          <t>predicciones</t>
+        </is>
+      </c>
+      <c r="E143" s="61" t="inlineStr">
+        <is>
+          <t>predicciones_h2.csv</t>
+        </is>
+      </c>
+      <c r="F143" s="61" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E3_v3_clean_20260323_080110/predicciones_h2.csv</t>
+        </is>
+      </c>
+      <c r="G143" s="61" t="inlineStr">
+        <is>
+          <t>Predicciones walk-forward para horizonte 2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="144" ht="15" customHeight="1" s="27">
+      <c r="A144" s="61" t="inlineStr">
+        <is>
+          <t>2026-03-23 08:01:52</t>
+        </is>
+      </c>
+      <c r="B144" s="61" t="inlineStr">
+        <is>
+          <t>E3_v3_clean</t>
+        </is>
+      </c>
+      <c r="C144" s="61" t="inlineStr">
+        <is>
+          <t>E3</t>
+        </is>
+      </c>
+      <c r="D144" s="61" t="inlineStr">
+        <is>
+          <t>predicciones</t>
+        </is>
+      </c>
+      <c r="E144" s="61" t="inlineStr">
+        <is>
+          <t>predicciones_h3.csv</t>
+        </is>
+      </c>
+      <c r="F144" s="61" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E3_v3_clean_20260323_080110/predicciones_h3.csv</t>
+        </is>
+      </c>
+      <c r="G144" s="61" t="inlineStr">
+        <is>
+          <t>Predicciones walk-forward para horizonte 3.</t>
+        </is>
+      </c>
+    </row>
+    <row r="145" ht="15" customHeight="1" s="27">
+      <c r="A145" s="61" t="inlineStr">
+        <is>
+          <t>2026-03-23 08:01:52</t>
+        </is>
+      </c>
+      <c r="B145" s="61" t="inlineStr">
+        <is>
+          <t>E3_v3_clean</t>
+        </is>
+      </c>
+      <c r="C145" s="61" t="inlineStr">
+        <is>
+          <t>E3</t>
+        </is>
+      </c>
+      <c r="D145" s="61" t="inlineStr">
+        <is>
+          <t>predicciones</t>
+        </is>
+      </c>
+      <c r="E145" s="61" t="inlineStr">
+        <is>
+          <t>predicciones_h4.csv</t>
+        </is>
+      </c>
+      <c r="F145" s="61" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E3_v3_clean_20260323_080110/predicciones_h4.csv</t>
+        </is>
+      </c>
+      <c r="G145" s="61" t="inlineStr">
+        <is>
+          <t>Predicciones walk-forward para horizonte 4.</t>
+        </is>
+      </c>
+    </row>
+    <row r="146" ht="15" customHeight="1" s="27">
+      <c r="A146" s="61" t="inlineStr">
+        <is>
+          <t>2026-03-23 08:01:52</t>
+        </is>
+      </c>
+      <c r="B146" s="61" t="inlineStr">
+        <is>
+          <t>E3_v3_clean</t>
+        </is>
+      </c>
+      <c r="C146" s="61" t="inlineStr">
+        <is>
+          <t>E3</t>
+        </is>
+      </c>
+      <c r="D146" s="61" t="inlineStr">
+        <is>
+          <t>resumen</t>
+        </is>
+      </c>
+      <c r="E146" s="61" t="inlineStr">
+        <is>
+          <t>resumen_modeling_horizontes.json</t>
+        </is>
+      </c>
+      <c r="F146" s="61" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E3_v3_clean_20260323_080110/resumen_modeling_horizontes.json</t>
+        </is>
+      </c>
+      <c r="G146" s="61" t="inlineStr">
+        <is>
+          <t>Resumen de tamanos y seleccion de features por horizonte.</t>
+        </is>
+      </c>
+    </row>
+    <row r="147" ht="15" customHeight="1" s="27">
+      <c r="A147" s="61" t="inlineStr">
+        <is>
+          <t>2026-03-23 08:01:52</t>
+        </is>
+      </c>
+      <c r="B147" s="61" t="inlineStr">
+        <is>
+          <t>E3_v3_clean</t>
+        </is>
+      </c>
+      <c r="C147" s="61" t="inlineStr">
+        <is>
+          <t>E3</t>
+        </is>
+      </c>
+      <c r="D147" s="61" t="inlineStr">
+        <is>
+          <t>comparacion</t>
+        </is>
+      </c>
+      <c r="E147" s="61" t="inlineStr">
+        <is>
+          <t>comparacion_vs_E3_v1_clean.json</t>
+        </is>
+      </c>
+      <c r="F147" s="61" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E3_v3_clean_20260323_080110/comparacion_vs_E3_v1_clean.json</t>
+        </is>
+      </c>
+      <c r="G147" s="61" t="inlineStr">
+        <is>
+          <t>Comparacion de la corrida clean contra E3_v1_clean.</t>
+        </is>
+      </c>
+    </row>
+    <row r="148" ht="15" customHeight="1" s="27">
+      <c r="A148" s="61" t="inlineStr">
+        <is>
+          <t>2026-03-23 08:01:52</t>
+        </is>
+      </c>
+      <c r="B148" s="61" t="inlineStr">
+        <is>
+          <t>E3_v3_clean</t>
+        </is>
+      </c>
+      <c r="C148" s="61" t="inlineStr">
+        <is>
+          <t>E3</t>
+        </is>
+      </c>
+      <c r="D148" s="61" t="inlineStr">
+        <is>
+          <t>comparacion</t>
+        </is>
+      </c>
+      <c r="E148" s="61" t="inlineStr">
+        <is>
+          <t>comparacion_vs_E2_v3_clean.json</t>
+        </is>
+      </c>
+      <c r="F148" s="61" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E3_v3_clean_20260323_080110/comparacion_vs_E2_v3_clean.json</t>
+        </is>
+      </c>
+      <c r="G148" s="61" t="inlineStr">
+        <is>
+          <t>Comparacion de la corrida clean contra E2_v3_clean.</t>
+        </is>
+      </c>
+    </row>
+    <row r="149" ht="15" customHeight="1" s="27">
+      <c r="A149" s="61" t="inlineStr">
+        <is>
+          <t>2026-03-23 08:01:52</t>
+        </is>
+      </c>
+      <c r="B149" s="61" t="inlineStr">
+        <is>
+          <t>E3_v3_clean</t>
+        </is>
+      </c>
+      <c r="C149" s="61" t="inlineStr">
+        <is>
+          <t>E3</t>
+        </is>
+      </c>
+      <c r="D149" s="61" t="inlineStr">
+        <is>
+          <t>comparacion</t>
+        </is>
+      </c>
+      <c r="E149" s="61" t="inlineStr">
+        <is>
+          <t>comparacion_vs_E1_v4_clean.json</t>
+        </is>
+      </c>
+      <c r="F149" s="61" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E3_v3_clean_20260323_080110/comparacion_vs_E1_v4_clean.json</t>
+        </is>
+      </c>
+      <c r="G149" s="61" t="inlineStr">
+        <is>
+          <t>Comparacion de la corrida clean contra E1_v4_clean.</t>
+        </is>
+      </c>
+    </row>
+    <row r="150" ht="15" customHeight="1" s="27">
+      <c r="A150" s="61" t="inlineStr">
+        <is>
+          <t>2026-03-23 08:01:52</t>
+        </is>
+      </c>
+      <c r="B150" s="61" t="inlineStr">
+        <is>
+          <t>E3_v3_clean</t>
+        </is>
+      </c>
+      <c r="C150" s="61" t="inlineStr">
+        <is>
+          <t>E3</t>
+        </is>
+      </c>
+      <c r="D150" s="61" t="inlineStr">
+        <is>
+          <t>comparacion</t>
+        </is>
+      </c>
+      <c r="E150" s="61" t="inlineStr">
+        <is>
+          <t>comparacion_vs_E1_v5_clean.json</t>
+        </is>
+      </c>
+      <c r="F150" s="61" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E3_v3_clean_20260323_080110/comparacion_vs_E1_v5_clean.json</t>
+        </is>
+      </c>
+      <c r="G150" s="61" t="inlineStr">
+        <is>
+          <t>Comparacion de la corrida clean contra E1_v5_clean.</t>
+        </is>
+      </c>
+    </row>
+    <row r="151" ht="15" customHeight="1" s="27">
+      <c r="A151" s="61" t="inlineStr">
+        <is>
+          <t>2026-03-23 08:01:52</t>
+        </is>
+      </c>
+      <c r="B151" s="61" t="inlineStr">
+        <is>
+          <t>E3_v3_clean</t>
+        </is>
+      </c>
+      <c r="C151" s="61" t="inlineStr">
+        <is>
+          <t>E3</t>
+        </is>
+      </c>
+      <c r="D151" s="61" t="inlineStr">
+        <is>
+          <t>metricas</t>
+        </is>
+      </c>
+      <c r="E151" s="61" t="inlineStr">
+        <is>
+          <t>metricas_horizonte.json</t>
+        </is>
+      </c>
+      <c r="F151" s="61" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E3_v3_clean_20260323_080110/metricas_horizonte.json</t>
+        </is>
+      </c>
+      <c r="G151" s="61" t="inlineStr">
+        <is>
+          <t>Resumen estructurado por horizonte.</t>
+        </is>
+      </c>
+    </row>
+    <row r="152" ht="15" customHeight="1" s="27">
+      <c r="A152" s="61" t="inlineStr">
+        <is>
+          <t>2026-03-23 08:01:52</t>
+        </is>
+      </c>
+      <c r="B152" s="61" t="inlineStr">
+        <is>
+          <t>E3_v3_clean</t>
+        </is>
+      </c>
+      <c r="C152" s="61" t="inlineStr">
+        <is>
+          <t>E3</t>
+        </is>
+      </c>
+      <c r="D152" s="61" t="inlineStr">
+        <is>
+          <t>metadata</t>
+        </is>
+      </c>
+      <c r="E152" s="61" t="inlineStr">
+        <is>
+          <t>metadata_run.json</t>
+        </is>
+      </c>
+      <c r="F152" s="61" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E3_v3_clean_20260323_080110/metadata_run.json</t>
+        </is>
+      </c>
+      <c r="G152" s="61" t="inlineStr">
+        <is>
+          <t>Metadata base del run.</t>
+        </is>
+      </c>
+    </row>
+    <row r="153" ht="15" customHeight="1" s="27">
+      <c r="A153" s="61" t="inlineStr">
+        <is>
+          <t>2026-03-25 04:59:55</t>
+        </is>
+      </c>
+      <c r="B153" s="61" t="inlineStr">
+        <is>
+          <t>E3_v2_clean</t>
+        </is>
+      </c>
+      <c r="C153" s="61" t="inlineStr">
+        <is>
+          <t>E3</t>
+        </is>
+      </c>
+      <c r="D153" s="61" t="inlineStr">
+        <is>
+          <t>script_snapshot</t>
+        </is>
+      </c>
+      <c r="E153" s="61" t="inlineStr">
+        <is>
+          <t>run_e3_random_forest.py</t>
+        </is>
+      </c>
+      <c r="F153" s="61" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E3_v2_clean_20260325_045918/scripts/run_e3_random_forest.py</t>
+        </is>
+      </c>
+      <c r="G153" s="61" t="inlineStr">
+        <is>
+          <t>Copia del script ejecutado para reproducibilidad.</t>
+        </is>
+      </c>
+    </row>
+    <row r="154" ht="15" customHeight="1" s="27">
+      <c r="A154" s="61" t="inlineStr">
+        <is>
+          <t>2026-03-25 04:59:55</t>
+        </is>
+      </c>
+      <c r="B154" s="61" t="inlineStr">
+        <is>
+          <t>E3_v2_clean</t>
+        </is>
+      </c>
+      <c r="C154" s="61" t="inlineStr">
+        <is>
+          <t>E3</t>
+        </is>
+      </c>
+      <c r="D154" s="61" t="inlineStr">
+        <is>
+          <t>parametros</t>
+        </is>
+      </c>
+      <c r="E154" s="61" t="inlineStr">
+        <is>
+          <t>parametros_run.json</t>
+        </is>
+      </c>
+      <c r="F154" s="61" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E3_v2_clean_20260325_045918/parametros_run.json</t>
+        </is>
+      </c>
+      <c r="G154" s="61" t="inlineStr">
+        <is>
+          <t>Parametros del experimento.</t>
+        </is>
+      </c>
+    </row>
+    <row r="155" ht="15" customHeight="1" s="27">
+      <c r="A155" s="61" t="inlineStr">
+        <is>
+          <t>2026-03-25 04:59:55</t>
+        </is>
+      </c>
+      <c r="B155" s="61" t="inlineStr">
+        <is>
+          <t>E3_v2_clean</t>
+        </is>
+      </c>
+      <c r="C155" s="61" t="inlineStr">
+        <is>
+          <t>E3</t>
+        </is>
+      </c>
+      <c r="D155" s="61" t="inlineStr">
+        <is>
+          <t>predicciones</t>
+        </is>
+      </c>
+      <c r="E155" s="61" t="inlineStr">
+        <is>
+          <t>predicciones_h1.csv</t>
+        </is>
+      </c>
+      <c r="F155" s="61" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E3_v2_clean_20260325_045918/predicciones_h1.csv</t>
+        </is>
+      </c>
+      <c r="G155" s="61" t="inlineStr">
+        <is>
+          <t>Predicciones walk-forward para horizonte 1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="156" ht="15" customHeight="1" s="27">
+      <c r="A156" s="61" t="inlineStr">
+        <is>
+          <t>2026-03-25 04:59:55</t>
+        </is>
+      </c>
+      <c r="B156" s="61" t="inlineStr">
+        <is>
+          <t>E3_v2_clean</t>
+        </is>
+      </c>
+      <c r="C156" s="61" t="inlineStr">
+        <is>
+          <t>E3</t>
+        </is>
+      </c>
+      <c r="D156" s="61" t="inlineStr">
+        <is>
+          <t>predicciones</t>
+        </is>
+      </c>
+      <c r="E156" s="61" t="inlineStr">
+        <is>
+          <t>predicciones_h2.csv</t>
+        </is>
+      </c>
+      <c r="F156" s="61" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E3_v2_clean_20260325_045918/predicciones_h2.csv</t>
+        </is>
+      </c>
+      <c r="G156" s="61" t="inlineStr">
+        <is>
+          <t>Predicciones walk-forward para horizonte 2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="157" ht="15" customHeight="1" s="27">
+      <c r="A157" s="61" t="inlineStr">
+        <is>
+          <t>2026-03-25 04:59:55</t>
+        </is>
+      </c>
+      <c r="B157" s="61" t="inlineStr">
+        <is>
+          <t>E3_v2_clean</t>
+        </is>
+      </c>
+      <c r="C157" s="61" t="inlineStr">
+        <is>
+          <t>E3</t>
+        </is>
+      </c>
+      <c r="D157" s="61" t="inlineStr">
+        <is>
+          <t>predicciones</t>
+        </is>
+      </c>
+      <c r="E157" s="61" t="inlineStr">
+        <is>
+          <t>predicciones_h3.csv</t>
+        </is>
+      </c>
+      <c r="F157" s="61" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E3_v2_clean_20260325_045918/predicciones_h3.csv</t>
+        </is>
+      </c>
+      <c r="G157" s="61" t="inlineStr">
+        <is>
+          <t>Predicciones walk-forward para horizonte 3.</t>
+        </is>
+      </c>
+    </row>
+    <row r="158" ht="15" customHeight="1" s="27">
+      <c r="A158" s="61" t="inlineStr">
+        <is>
+          <t>2026-03-25 04:59:55</t>
+        </is>
+      </c>
+      <c r="B158" s="61" t="inlineStr">
+        <is>
+          <t>E3_v2_clean</t>
+        </is>
+      </c>
+      <c r="C158" s="61" t="inlineStr">
+        <is>
+          <t>E3</t>
+        </is>
+      </c>
+      <c r="D158" s="61" t="inlineStr">
+        <is>
+          <t>predicciones</t>
+        </is>
+      </c>
+      <c r="E158" s="61" t="inlineStr">
+        <is>
+          <t>predicciones_h4.csv</t>
+        </is>
+      </c>
+      <c r="F158" s="61" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E3_v2_clean_20260325_045918/predicciones_h4.csv</t>
+        </is>
+      </c>
+      <c r="G158" s="61" t="inlineStr">
+        <is>
+          <t>Predicciones walk-forward para horizonte 4.</t>
+        </is>
+      </c>
+    </row>
+    <row r="159" ht="15" customHeight="1" s="27">
+      <c r="A159" s="61" t="inlineStr">
+        <is>
+          <t>2026-03-25 04:59:55</t>
+        </is>
+      </c>
+      <c r="B159" s="61" t="inlineStr">
+        <is>
+          <t>E3_v2_clean</t>
+        </is>
+      </c>
+      <c r="C159" s="61" t="inlineStr">
+        <is>
+          <t>E3</t>
+        </is>
+      </c>
+      <c r="D159" s="61" t="inlineStr">
+        <is>
+          <t>resumen</t>
+        </is>
+      </c>
+      <c r="E159" s="61" t="inlineStr">
+        <is>
+          <t>resumen_modeling_horizontes.json</t>
+        </is>
+      </c>
+      <c r="F159" s="61" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E3_v2_clean_20260325_045918/resumen_modeling_horizontes.json</t>
+        </is>
+      </c>
+      <c r="G159" s="61" t="inlineStr">
+        <is>
+          <t>Resumen de tamanos y seleccion de features por horizonte.</t>
+        </is>
+      </c>
+    </row>
+    <row r="160" ht="15" customHeight="1" s="27">
+      <c r="A160" s="61" t="inlineStr">
+        <is>
+          <t>2026-03-25 04:59:55</t>
+        </is>
+      </c>
+      <c r="B160" s="61" t="inlineStr">
+        <is>
+          <t>E3_v2_clean</t>
+        </is>
+      </c>
+      <c r="C160" s="61" t="inlineStr">
+        <is>
+          <t>E3</t>
+        </is>
+      </c>
+      <c r="D160" s="61" t="inlineStr">
+        <is>
+          <t>comparacion</t>
+        </is>
+      </c>
+      <c r="E160" s="61" t="inlineStr">
+        <is>
+          <t>comparacion_vs_E1_v5_clean.json</t>
+        </is>
+      </c>
+      <c r="F160" s="61" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E3_v2_clean_20260325_045918/comparacion_vs_E1_v5_clean.json</t>
+        </is>
+      </c>
+      <c r="G160" s="61" t="inlineStr">
+        <is>
+          <t>Comparacion de la corrida clean contra E1_v5_clean.</t>
+        </is>
+      </c>
+    </row>
+    <row r="161" ht="15" customHeight="1" s="27">
+      <c r="A161" s="61" t="inlineStr">
+        <is>
+          <t>2026-03-25 04:59:55</t>
+        </is>
+      </c>
+      <c r="B161" s="61" t="inlineStr">
+        <is>
+          <t>E3_v2_clean</t>
+        </is>
+      </c>
+      <c r="C161" s="61" t="inlineStr">
+        <is>
+          <t>E3</t>
+        </is>
+      </c>
+      <c r="D161" s="61" t="inlineStr">
+        <is>
+          <t>comparacion</t>
+        </is>
+      </c>
+      <c r="E161" s="61" t="inlineStr">
+        <is>
+          <t>comparacion_vs_E1_v4_clean.json</t>
+        </is>
+      </c>
+      <c r="F161" s="61" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E3_v2_clean_20260325_045918/comparacion_vs_E1_v4_clean.json</t>
+        </is>
+      </c>
+      <c r="G161" s="61" t="inlineStr">
+        <is>
+          <t>Comparacion de la corrida clean contra E1_v4_clean.</t>
+        </is>
+      </c>
+    </row>
+    <row r="162" ht="15" customHeight="1" s="27">
+      <c r="A162" s="61" t="inlineStr">
+        <is>
+          <t>2026-03-25 04:59:55</t>
+        </is>
+      </c>
+      <c r="B162" s="61" t="inlineStr">
+        <is>
+          <t>E3_v2_clean</t>
+        </is>
+      </c>
+      <c r="C162" s="61" t="inlineStr">
+        <is>
+          <t>E3</t>
+        </is>
+      </c>
+      <c r="D162" s="61" t="inlineStr">
+        <is>
+          <t>comparacion</t>
+        </is>
+      </c>
+      <c r="E162" s="61" t="inlineStr">
+        <is>
+          <t>comparacion_vs_E2_v3_clean.json</t>
+        </is>
+      </c>
+      <c r="F162" s="61" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E3_v2_clean_20260325_045918/comparacion_vs_E2_v3_clean.json</t>
+        </is>
+      </c>
+      <c r="G162" s="61" t="inlineStr">
+        <is>
+          <t>Comparacion de la corrida clean contra E2_v3_clean.</t>
+        </is>
+      </c>
+    </row>
+    <row r="163" ht="15" customHeight="1" s="27">
+      <c r="A163" s="61" t="inlineStr">
+        <is>
+          <t>2026-03-25 04:59:55</t>
+        </is>
+      </c>
+      <c r="B163" s="61" t="inlineStr">
+        <is>
+          <t>E3_v2_clean</t>
+        </is>
+      </c>
+      <c r="C163" s="61" t="inlineStr">
+        <is>
+          <t>E3</t>
+        </is>
+      </c>
+      <c r="D163" s="61" t="inlineStr">
+        <is>
+          <t>comparacion</t>
+        </is>
+      </c>
+      <c r="E163" s="61" t="inlineStr">
+        <is>
+          <t>comparacion_vs_E3_v1_clean.json</t>
+        </is>
+      </c>
+      <c r="F163" s="61" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E3_v2_clean_20260325_045918/comparacion_vs_E3_v1_clean.json</t>
+        </is>
+      </c>
+      <c r="G163" s="61" t="inlineStr">
+        <is>
+          <t>Comparacion de la corrida clean contra E3_v1_clean.</t>
+        </is>
+      </c>
+    </row>
+    <row r="164" ht="15" customHeight="1" s="27">
+      <c r="A164" s="61" t="inlineStr">
+        <is>
+          <t>2026-03-25 04:59:55</t>
+        </is>
+      </c>
+      <c r="B164" s="61" t="inlineStr">
+        <is>
+          <t>E3_v2_clean</t>
+        </is>
+      </c>
+      <c r="C164" s="61" t="inlineStr">
+        <is>
+          <t>E3</t>
+        </is>
+      </c>
+      <c r="D164" s="61" t="inlineStr">
+        <is>
+          <t>metricas</t>
+        </is>
+      </c>
+      <c r="E164" s="61" t="inlineStr">
+        <is>
+          <t>metricas_horizonte.json</t>
+        </is>
+      </c>
+      <c r="F164" s="61" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E3_v2_clean_20260325_045918/metricas_horizonte.json</t>
+        </is>
+      </c>
+      <c r="G164" s="61" t="inlineStr">
+        <is>
+          <t>Resumen estructurado por horizonte.</t>
+        </is>
+      </c>
+    </row>
+    <row r="165" ht="15" customHeight="1" s="27">
+      <c r="A165" s="61" t="inlineStr">
+        <is>
+          <t>2026-03-25 04:59:55</t>
+        </is>
+      </c>
+      <c r="B165" s="61" t="inlineStr">
+        <is>
+          <t>E3_v2_clean</t>
+        </is>
+      </c>
+      <c r="C165" s="61" t="inlineStr">
+        <is>
+          <t>E3</t>
+        </is>
+      </c>
+      <c r="D165" s="61" t="inlineStr">
+        <is>
+          <t>metadata</t>
+        </is>
+      </c>
+      <c r="E165" s="61" t="inlineStr">
+        <is>
+          <t>metadata_run.json</t>
+        </is>
+      </c>
+      <c r="F165" s="61" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E3_v2_clean_20260325_045918/metadata_run.json</t>
+        </is>
+      </c>
+      <c r="G165" s="61" t="inlineStr">
+        <is>
+          <t>Metadata base del run.</t>
+        </is>
+      </c>
+    </row>
+    <row r="166" ht="15" customHeight="1" s="27">
+      <c r="A166" s="61" t="inlineStr">
+        <is>
+          <t>2026-03-25 05:21:02</t>
+        </is>
+      </c>
+      <c r="B166" s="61" t="inlineStr">
+        <is>
+          <t>E4_v1_clean</t>
+        </is>
+      </c>
+      <c r="C166" s="61" t="inlineStr">
+        <is>
+          <t>E4</t>
+        </is>
+      </c>
+      <c r="D166" s="61" t="inlineStr">
+        <is>
+          <t>script_snapshot</t>
+        </is>
+      </c>
+      <c r="E166" s="61" t="inlineStr">
+        <is>
+          <t>run_e4_xgboost.py</t>
+        </is>
+      </c>
+      <c r="F166" s="61" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E4_v1_clean_20260325_052051/scripts/run_e4_xgboost.py</t>
+        </is>
+      </c>
+      <c r="G166" s="61" t="inlineStr">
+        <is>
+          <t>Copia del script ejecutado para reproducibilidad.</t>
+        </is>
+      </c>
+    </row>
+    <row r="167" ht="15" customHeight="1" s="27">
+      <c r="A167" s="61" t="inlineStr">
+        <is>
+          <t>2026-03-25 05:21:02</t>
+        </is>
+      </c>
+      <c r="B167" s="61" t="inlineStr">
+        <is>
+          <t>E4_v1_clean</t>
+        </is>
+      </c>
+      <c r="C167" s="61" t="inlineStr">
+        <is>
+          <t>E4</t>
+        </is>
+      </c>
+      <c r="D167" s="61" t="inlineStr">
+        <is>
+          <t>parametros</t>
+        </is>
+      </c>
+      <c r="E167" s="61" t="inlineStr">
+        <is>
+          <t>parametros_run.json</t>
+        </is>
+      </c>
+      <c r="F167" s="61" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E4_v1_clean_20260325_052051/parametros_run.json</t>
+        </is>
+      </c>
+      <c r="G167" s="61" t="inlineStr">
+        <is>
+          <t>Parametros del experimento.</t>
+        </is>
+      </c>
+    </row>
+    <row r="168" ht="15" customHeight="1" s="27">
+      <c r="A168" s="61" t="inlineStr">
+        <is>
+          <t>2026-03-25 05:21:02</t>
+        </is>
+      </c>
+      <c r="B168" s="61" t="inlineStr">
+        <is>
+          <t>E4_v1_clean</t>
+        </is>
+      </c>
+      <c r="C168" s="61" t="inlineStr">
+        <is>
+          <t>E4</t>
+        </is>
+      </c>
+      <c r="D168" s="61" t="inlineStr">
+        <is>
+          <t>predicciones</t>
+        </is>
+      </c>
+      <c r="E168" s="61" t="inlineStr">
+        <is>
+          <t>predicciones_h1.csv</t>
+        </is>
+      </c>
+      <c r="F168" s="61" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E4_v1_clean_20260325_052051/predicciones_h1.csv</t>
+        </is>
+      </c>
+      <c r="G168" s="61" t="inlineStr">
+        <is>
+          <t>Predicciones walk-forward para horizonte 1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="169" ht="15" customHeight="1" s="27">
+      <c r="A169" s="61" t="inlineStr">
+        <is>
+          <t>2026-03-25 05:21:02</t>
+        </is>
+      </c>
+      <c r="B169" s="61" t="inlineStr">
+        <is>
+          <t>E4_v1_clean</t>
+        </is>
+      </c>
+      <c r="C169" s="61" t="inlineStr">
+        <is>
+          <t>E4</t>
+        </is>
+      </c>
+      <c r="D169" s="61" t="inlineStr">
+        <is>
+          <t>predicciones</t>
+        </is>
+      </c>
+      <c r="E169" s="61" t="inlineStr">
+        <is>
+          <t>predicciones_h2.csv</t>
+        </is>
+      </c>
+      <c r="F169" s="61" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E4_v1_clean_20260325_052051/predicciones_h2.csv</t>
+        </is>
+      </c>
+      <c r="G169" s="61" t="inlineStr">
+        <is>
+          <t>Predicciones walk-forward para horizonte 2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="170" ht="15" customHeight="1" s="27">
+      <c r="A170" s="61" t="inlineStr">
+        <is>
+          <t>2026-03-25 05:21:02</t>
+        </is>
+      </c>
+      <c r="B170" s="61" t="inlineStr">
+        <is>
+          <t>E4_v1_clean</t>
+        </is>
+      </c>
+      <c r="C170" s="61" t="inlineStr">
+        <is>
+          <t>E4</t>
+        </is>
+      </c>
+      <c r="D170" s="61" t="inlineStr">
+        <is>
+          <t>predicciones</t>
+        </is>
+      </c>
+      <c r="E170" s="61" t="inlineStr">
+        <is>
+          <t>predicciones_h3.csv</t>
+        </is>
+      </c>
+      <c r="F170" s="61" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E4_v1_clean_20260325_052051/predicciones_h3.csv</t>
+        </is>
+      </c>
+      <c r="G170" s="61" t="inlineStr">
+        <is>
+          <t>Predicciones walk-forward para horizonte 3.</t>
+        </is>
+      </c>
+    </row>
+    <row r="171" ht="15" customHeight="1" s="27">
+      <c r="A171" s="61" t="inlineStr">
+        <is>
+          <t>2026-03-25 05:21:02</t>
+        </is>
+      </c>
+      <c r="B171" s="61" t="inlineStr">
+        <is>
+          <t>E4_v1_clean</t>
+        </is>
+      </c>
+      <c r="C171" s="61" t="inlineStr">
+        <is>
+          <t>E4</t>
+        </is>
+      </c>
+      <c r="D171" s="61" t="inlineStr">
+        <is>
+          <t>predicciones</t>
+        </is>
+      </c>
+      <c r="E171" s="61" t="inlineStr">
+        <is>
+          <t>predicciones_h4.csv</t>
+        </is>
+      </c>
+      <c r="F171" s="61" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E4_v1_clean_20260325_052051/predicciones_h4.csv</t>
+        </is>
+      </c>
+      <c r="G171" s="61" t="inlineStr">
+        <is>
+          <t>Predicciones walk-forward para horizonte 4.</t>
+        </is>
+      </c>
+    </row>
+    <row r="172" ht="15" customHeight="1" s="27">
+      <c r="A172" s="61" t="inlineStr">
+        <is>
+          <t>2026-03-25 05:21:02</t>
+        </is>
+      </c>
+      <c r="B172" s="61" t="inlineStr">
+        <is>
+          <t>E4_v1_clean</t>
+        </is>
+      </c>
+      <c r="C172" s="61" t="inlineStr">
+        <is>
+          <t>E4</t>
+        </is>
+      </c>
+      <c r="D172" s="61" t="inlineStr">
+        <is>
+          <t>resumen</t>
+        </is>
+      </c>
+      <c r="E172" s="61" t="inlineStr">
+        <is>
+          <t>resumen_modeling_horizontes.json</t>
+        </is>
+      </c>
+      <c r="F172" s="61" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E4_v1_clean_20260325_052051/resumen_modeling_horizontes.json</t>
+        </is>
+      </c>
+      <c r="G172" s="61" t="inlineStr">
+        <is>
+          <t>Resumen de tamanos y seleccion de features por horizonte.</t>
+        </is>
+      </c>
+    </row>
+    <row r="173" ht="15" customHeight="1" s="27">
+      <c r="A173" s="61" t="inlineStr">
+        <is>
+          <t>2026-03-25 05:21:02</t>
+        </is>
+      </c>
+      <c r="B173" s="61" t="inlineStr">
+        <is>
+          <t>E4_v1_clean</t>
+        </is>
+      </c>
+      <c r="C173" s="61" t="inlineStr">
+        <is>
+          <t>E4</t>
+        </is>
+      </c>
+      <c r="D173" s="61" t="inlineStr">
+        <is>
+          <t>comparacion</t>
+        </is>
+      </c>
+      <c r="E173" s="61" t="inlineStr">
+        <is>
+          <t>comparacion_vs_E1_v5_clean.json</t>
+        </is>
+      </c>
+      <c r="F173" s="61" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E4_v1_clean_20260325_052051/comparacion_vs_E1_v5_clean.json</t>
+        </is>
+      </c>
+      <c r="G173" s="61" t="inlineStr">
+        <is>
+          <t>Comparacion de la corrida clean contra E1_v5_clean.</t>
+        </is>
+      </c>
+    </row>
+    <row r="174" ht="15" customHeight="1" s="27">
+      <c r="A174" s="61" t="inlineStr">
+        <is>
+          <t>2026-03-25 05:21:02</t>
+        </is>
+      </c>
+      <c r="B174" s="61" t="inlineStr">
+        <is>
+          <t>E4_v1_clean</t>
+        </is>
+      </c>
+      <c r="C174" s="61" t="inlineStr">
+        <is>
+          <t>E4</t>
+        </is>
+      </c>
+      <c r="D174" s="61" t="inlineStr">
+        <is>
+          <t>comparacion</t>
+        </is>
+      </c>
+      <c r="E174" s="61" t="inlineStr">
+        <is>
+          <t>comparacion_vs_E1_v4_clean.json</t>
+        </is>
+      </c>
+      <c r="F174" s="61" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E4_v1_clean_20260325_052051/comparacion_vs_E1_v4_clean.json</t>
+        </is>
+      </c>
+      <c r="G174" s="61" t="inlineStr">
+        <is>
+          <t>Comparacion de la corrida clean contra E1_v4_clean.</t>
+        </is>
+      </c>
+    </row>
+    <row r="175" ht="15" customHeight="1" s="27">
+      <c r="A175" s="61" t="inlineStr">
+        <is>
+          <t>2026-03-25 05:21:02</t>
+        </is>
+      </c>
+      <c r="B175" s="61" t="inlineStr">
+        <is>
+          <t>E4_v1_clean</t>
+        </is>
+      </c>
+      <c r="C175" s="61" t="inlineStr">
+        <is>
+          <t>E4</t>
+        </is>
+      </c>
+      <c r="D175" s="61" t="inlineStr">
+        <is>
+          <t>comparacion</t>
+        </is>
+      </c>
+      <c r="E175" s="61" t="inlineStr">
+        <is>
+          <t>comparacion_vs_E3_v2_clean.json</t>
+        </is>
+      </c>
+      <c r="F175" s="61" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E4_v1_clean_20260325_052051/comparacion_vs_E3_v2_clean.json</t>
+        </is>
+      </c>
+      <c r="G175" s="61" t="inlineStr">
+        <is>
+          <t>Comparacion de la corrida clean contra E3_v2_clean.</t>
+        </is>
+      </c>
+    </row>
+    <row r="176" ht="15" customHeight="1" s="27">
+      <c r="A176" s="61" t="inlineStr">
+        <is>
+          <t>2026-03-25 05:21:02</t>
+        </is>
+      </c>
+      <c r="B176" s="61" t="inlineStr">
+        <is>
+          <t>E4_v1_clean</t>
+        </is>
+      </c>
+      <c r="C176" s="61" t="inlineStr">
+        <is>
+          <t>E4</t>
+        </is>
+      </c>
+      <c r="D176" s="61" t="inlineStr">
+        <is>
+          <t>metricas</t>
+        </is>
+      </c>
+      <c r="E176" s="61" t="inlineStr">
+        <is>
+          <t>metricas_horizonte.json</t>
+        </is>
+      </c>
+      <c r="F176" s="61" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E4_v1_clean_20260325_052051/metricas_horizonte.json</t>
+        </is>
+      </c>
+      <c r="G176" s="61" t="inlineStr">
+        <is>
+          <t>Resumen estructurado por horizonte.</t>
+        </is>
+      </c>
+    </row>
+    <row r="177" ht="15" customHeight="1" s="27">
+      <c r="A177" s="61" t="inlineStr">
+        <is>
+          <t>2026-03-25 05:21:02</t>
+        </is>
+      </c>
+      <c r="B177" s="61" t="inlineStr">
+        <is>
+          <t>E4_v1_clean</t>
+        </is>
+      </c>
+      <c r="C177" s="61" t="inlineStr">
+        <is>
+          <t>E4</t>
+        </is>
+      </c>
+      <c r="D177" s="61" t="inlineStr">
+        <is>
+          <t>metadata</t>
+        </is>
+      </c>
+      <c r="E177" s="61" t="inlineStr">
+        <is>
+          <t>metadata_run.json</t>
+        </is>
+      </c>
+      <c r="F177" s="61" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E4_v1_clean_20260325_052051/metadata_run.json</t>
+        </is>
+      </c>
+      <c r="G177" s="61" t="inlineStr">
+        <is>
+          <t>Metadata base del run.</t>
+        </is>
+      </c>
+    </row>
+    <row r="178" ht="15" customHeight="1" s="27">
+      <c r="A178" s="61" t="inlineStr">
+        <is>
+          <t>2026-03-25 05:51:25</t>
+        </is>
+      </c>
+      <c r="B178" s="61" t="inlineStr">
+        <is>
+          <t>E4_v2_clean</t>
+        </is>
+      </c>
+      <c r="C178" s="61" t="inlineStr">
+        <is>
+          <t>E4</t>
+        </is>
+      </c>
+      <c r="D178" s="61" t="inlineStr">
+        <is>
+          <t>script_snapshot</t>
+        </is>
+      </c>
+      <c r="E178" s="61" t="inlineStr">
+        <is>
+          <t>run_e4_xgboost.py</t>
+        </is>
+      </c>
+      <c r="F178" s="61" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E4_v2_clean_20260325_055117/scripts/run_e4_xgboost.py</t>
+        </is>
+      </c>
+      <c r="G178" s="61" t="inlineStr">
+        <is>
+          <t>Copia del script ejecutado para reproducibilidad.</t>
+        </is>
+      </c>
+    </row>
+    <row r="179" ht="15" customHeight="1" s="27">
+      <c r="A179" s="61" t="inlineStr">
+        <is>
+          <t>2026-03-25 05:51:25</t>
+        </is>
+      </c>
+      <c r="B179" s="61" t="inlineStr">
+        <is>
+          <t>E4_v2_clean</t>
+        </is>
+      </c>
+      <c r="C179" s="61" t="inlineStr">
+        <is>
+          <t>E4</t>
+        </is>
+      </c>
+      <c r="D179" s="61" t="inlineStr">
+        <is>
+          <t>parametros</t>
+        </is>
+      </c>
+      <c r="E179" s="61" t="inlineStr">
+        <is>
+          <t>parametros_run.json</t>
+        </is>
+      </c>
+      <c r="F179" s="61" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E4_v2_clean_20260325_055117/parametros_run.json</t>
+        </is>
+      </c>
+      <c r="G179" s="61" t="inlineStr">
+        <is>
+          <t>Parametros del experimento.</t>
+        </is>
+      </c>
+    </row>
+    <row r="180" ht="15" customHeight="1" s="27">
+      <c r="A180" s="61" t="inlineStr">
+        <is>
+          <t>2026-03-25 05:51:25</t>
+        </is>
+      </c>
+      <c r="B180" s="61" t="inlineStr">
+        <is>
+          <t>E4_v2_clean</t>
+        </is>
+      </c>
+      <c r="C180" s="61" t="inlineStr">
+        <is>
+          <t>E4</t>
+        </is>
+      </c>
+      <c r="D180" s="61" t="inlineStr">
+        <is>
+          <t>seleccion_features</t>
+        </is>
+      </c>
+      <c r="E180" s="61" t="inlineStr">
+        <is>
+          <t>features_seleccionadas_h1.csv</t>
+        </is>
+      </c>
+      <c r="F180" s="61" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E4_v2_clean_20260325_055117/features_seleccionadas_h1.csv</t>
+        </is>
+      </c>
+      <c r="G180" s="61" t="inlineStr">
+        <is>
+          <t>Resumen de combinaciones de features seleccionadas por fold externo. El filtro se calcula solo con el train de cada fold externo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="181" ht="15" customHeight="1" s="27">
+      <c r="A181" s="61" t="inlineStr">
+        <is>
+          <t>2026-03-25 05:51:25</t>
+        </is>
+      </c>
+      <c r="B181" s="61" t="inlineStr">
+        <is>
+          <t>E4_v2_clean</t>
+        </is>
+      </c>
+      <c r="C181" s="61" t="inlineStr">
+        <is>
+          <t>E4</t>
+        </is>
+      </c>
+      <c r="D181" s="61" t="inlineStr">
+        <is>
+          <t>seleccion_features</t>
+        </is>
+      </c>
+      <c r="E181" s="61" t="inlineStr">
+        <is>
+          <t>features_seleccionadas_h2.csv</t>
+        </is>
+      </c>
+      <c r="F181" s="61" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E4_v2_clean_20260325_055117/features_seleccionadas_h2.csv</t>
+        </is>
+      </c>
+      <c r="G181" s="61" t="inlineStr">
+        <is>
+          <t>Resumen de combinaciones de features seleccionadas por fold externo. El filtro se calcula solo con el train de cada fold externo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="182" ht="15" customHeight="1" s="27">
+      <c r="A182" s="61" t="inlineStr">
+        <is>
+          <t>2026-03-25 05:51:25</t>
+        </is>
+      </c>
+      <c r="B182" s="61" t="inlineStr">
+        <is>
+          <t>E4_v2_clean</t>
+        </is>
+      </c>
+      <c r="C182" s="61" t="inlineStr">
+        <is>
+          <t>E4</t>
+        </is>
+      </c>
+      <c r="D182" s="61" t="inlineStr">
+        <is>
+          <t>seleccion_features</t>
+        </is>
+      </c>
+      <c r="E182" s="61" t="inlineStr">
+        <is>
+          <t>features_seleccionadas_h3.csv</t>
+        </is>
+      </c>
+      <c r="F182" s="61" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E4_v2_clean_20260325_055117/features_seleccionadas_h3.csv</t>
+        </is>
+      </c>
+      <c r="G182" s="61" t="inlineStr">
+        <is>
+          <t>Resumen de combinaciones de features seleccionadas por fold externo. El filtro se calcula solo con el train de cada fold externo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="183" ht="15" customHeight="1" s="27">
+      <c r="A183" s="61" t="inlineStr">
+        <is>
+          <t>2026-03-25 05:51:25</t>
+        </is>
+      </c>
+      <c r="B183" s="61" t="inlineStr">
+        <is>
+          <t>E4_v2_clean</t>
+        </is>
+      </c>
+      <c r="C183" s="61" t="inlineStr">
+        <is>
+          <t>E4</t>
+        </is>
+      </c>
+      <c r="D183" s="61" t="inlineStr">
+        <is>
+          <t>seleccion_features</t>
+        </is>
+      </c>
+      <c r="E183" s="61" t="inlineStr">
+        <is>
+          <t>features_seleccionadas_h4.csv</t>
+        </is>
+      </c>
+      <c r="F183" s="61" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E4_v2_clean_20260325_055117/features_seleccionadas_h4.csv</t>
+        </is>
+      </c>
+      <c r="G183" s="61" t="inlineStr">
+        <is>
+          <t>Resumen de combinaciones de features seleccionadas por fold externo. El filtro se calcula solo con el train de cada fold externo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="184" ht="15" customHeight="1" s="27">
+      <c r="A184" s="61" t="inlineStr">
+        <is>
+          <t>2026-03-25 05:51:25</t>
+        </is>
+      </c>
+      <c r="B184" s="61" t="inlineStr">
+        <is>
+          <t>E4_v2_clean</t>
+        </is>
+      </c>
+      <c r="C184" s="61" t="inlineStr">
+        <is>
+          <t>E4</t>
+        </is>
+      </c>
+      <c r="D184" s="61" t="inlineStr">
+        <is>
+          <t>predicciones</t>
+        </is>
+      </c>
+      <c r="E184" s="61" t="inlineStr">
+        <is>
+          <t>predicciones_h1.csv</t>
+        </is>
+      </c>
+      <c r="F184" s="61" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E4_v2_clean_20260325_055117/predicciones_h1.csv</t>
+        </is>
+      </c>
+      <c r="G184" s="61" t="inlineStr">
+        <is>
+          <t>Predicciones walk-forward para horizonte 1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="185" ht="15" customHeight="1" s="27">
+      <c r="A185" s="61" t="inlineStr">
+        <is>
+          <t>2026-03-25 05:51:25</t>
+        </is>
+      </c>
+      <c r="B185" s="61" t="inlineStr">
+        <is>
+          <t>E4_v2_clean</t>
+        </is>
+      </c>
+      <c r="C185" s="61" t="inlineStr">
+        <is>
+          <t>E4</t>
+        </is>
+      </c>
+      <c r="D185" s="61" t="inlineStr">
+        <is>
+          <t>predicciones</t>
+        </is>
+      </c>
+      <c r="E185" s="61" t="inlineStr">
+        <is>
+          <t>predicciones_h2.csv</t>
+        </is>
+      </c>
+      <c r="F185" s="61" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E4_v2_clean_20260325_055117/predicciones_h2.csv</t>
+        </is>
+      </c>
+      <c r="G185" s="61" t="inlineStr">
+        <is>
+          <t>Predicciones walk-forward para horizonte 2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="186" ht="15" customHeight="1" s="27">
+      <c r="A186" s="61" t="inlineStr">
+        <is>
+          <t>2026-03-25 05:51:25</t>
+        </is>
+      </c>
+      <c r="B186" s="61" t="inlineStr">
+        <is>
+          <t>E4_v2_clean</t>
+        </is>
+      </c>
+      <c r="C186" s="61" t="inlineStr">
+        <is>
+          <t>E4</t>
+        </is>
+      </c>
+      <c r="D186" s="61" t="inlineStr">
+        <is>
+          <t>predicciones</t>
+        </is>
+      </c>
+      <c r="E186" s="61" t="inlineStr">
+        <is>
+          <t>predicciones_h3.csv</t>
+        </is>
+      </c>
+      <c r="F186" s="61" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E4_v2_clean_20260325_055117/predicciones_h3.csv</t>
+        </is>
+      </c>
+      <c r="G186" s="61" t="inlineStr">
+        <is>
+          <t>Predicciones walk-forward para horizonte 3.</t>
+        </is>
+      </c>
+    </row>
+    <row r="187" ht="15" customHeight="1" s="27">
+      <c r="A187" s="61" t="inlineStr">
+        <is>
+          <t>2026-03-25 05:51:25</t>
+        </is>
+      </c>
+      <c r="B187" s="61" t="inlineStr">
+        <is>
+          <t>E4_v2_clean</t>
+        </is>
+      </c>
+      <c r="C187" s="61" t="inlineStr">
+        <is>
+          <t>E4</t>
+        </is>
+      </c>
+      <c r="D187" s="61" t="inlineStr">
+        <is>
+          <t>predicciones</t>
+        </is>
+      </c>
+      <c r="E187" s="61" t="inlineStr">
+        <is>
+          <t>predicciones_h4.csv</t>
+        </is>
+      </c>
+      <c r="F187" s="61" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E4_v2_clean_20260325_055117/predicciones_h4.csv</t>
+        </is>
+      </c>
+      <c r="G187" s="61" t="inlineStr">
+        <is>
+          <t>Predicciones walk-forward para horizonte 4.</t>
+        </is>
+      </c>
+    </row>
+    <row r="188" ht="15" customHeight="1" s="27">
+      <c r="A188" s="61" t="inlineStr">
+        <is>
+          <t>2026-03-25 05:51:25</t>
+        </is>
+      </c>
+      <c r="B188" s="61" t="inlineStr">
+        <is>
+          <t>E4_v2_clean</t>
+        </is>
+      </c>
+      <c r="C188" s="61" t="inlineStr">
+        <is>
+          <t>E4</t>
+        </is>
+      </c>
+      <c r="D188" s="61" t="inlineStr">
+        <is>
+          <t>resumen</t>
+        </is>
+      </c>
+      <c r="E188" s="61" t="inlineStr">
+        <is>
+          <t>resumen_modeling_horizontes.json</t>
+        </is>
+      </c>
+      <c r="F188" s="61" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E4_v2_clean_20260325_055117/resumen_modeling_horizontes.json</t>
+        </is>
+      </c>
+      <c r="G188" s="61" t="inlineStr">
+        <is>
+          <t>Resumen de tamanos y seleccion de features por horizonte.</t>
+        </is>
+      </c>
+    </row>
+    <row r="189" ht="15" customHeight="1" s="27">
+      <c r="A189" s="61" t="inlineStr">
+        <is>
+          <t>2026-03-25 05:51:25</t>
+        </is>
+      </c>
+      <c r="B189" s="61" t="inlineStr">
+        <is>
+          <t>E4_v2_clean</t>
+        </is>
+      </c>
+      <c r="C189" s="61" t="inlineStr">
+        <is>
+          <t>E4</t>
+        </is>
+      </c>
+      <c r="D189" s="61" t="inlineStr">
+        <is>
+          <t>comparacion</t>
+        </is>
+      </c>
+      <c r="E189" s="61" t="inlineStr">
+        <is>
+          <t>comparacion_vs_E1_v5_clean.json</t>
+        </is>
+      </c>
+      <c r="F189" s="61" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E4_v2_clean_20260325_055117/comparacion_vs_E1_v5_clean.json</t>
+        </is>
+      </c>
+      <c r="G189" s="61" t="inlineStr">
+        <is>
+          <t>Comparacion de la corrida clean contra E1_v5_clean.</t>
+        </is>
+      </c>
+    </row>
+    <row r="190" ht="15" customHeight="1" s="27">
+      <c r="A190" s="61" t="inlineStr">
+        <is>
+          <t>2026-03-25 05:51:25</t>
+        </is>
+      </c>
+      <c r="B190" s="61" t="inlineStr">
+        <is>
+          <t>E4_v2_clean</t>
+        </is>
+      </c>
+      <c r="C190" s="61" t="inlineStr">
+        <is>
+          <t>E4</t>
+        </is>
+      </c>
+      <c r="D190" s="61" t="inlineStr">
+        <is>
+          <t>comparacion</t>
+        </is>
+      </c>
+      <c r="E190" s="61" t="inlineStr">
+        <is>
+          <t>comparacion_vs_E1_v4_clean.json</t>
+        </is>
+      </c>
+      <c r="F190" s="61" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E4_v2_clean_20260325_055117/comparacion_vs_E1_v4_clean.json</t>
+        </is>
+      </c>
+      <c r="G190" s="61" t="inlineStr">
+        <is>
+          <t>Comparacion de la corrida clean contra E1_v4_clean.</t>
+        </is>
+      </c>
+    </row>
+    <row r="191" ht="15" customHeight="1" s="27">
+      <c r="A191" s="61" t="inlineStr">
+        <is>
+          <t>2026-03-25 05:51:25</t>
+        </is>
+      </c>
+      <c r="B191" s="61" t="inlineStr">
+        <is>
+          <t>E4_v2_clean</t>
+        </is>
+      </c>
+      <c r="C191" s="61" t="inlineStr">
+        <is>
+          <t>E4</t>
+        </is>
+      </c>
+      <c r="D191" s="61" t="inlineStr">
+        <is>
+          <t>comparacion</t>
+        </is>
+      </c>
+      <c r="E191" s="61" t="inlineStr">
+        <is>
+          <t>comparacion_vs_E3_v2_clean.json</t>
+        </is>
+      </c>
+      <c r="F191" s="61" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E4_v2_clean_20260325_055117/comparacion_vs_E3_v2_clean.json</t>
+        </is>
+      </c>
+      <c r="G191" s="61" t="inlineStr">
+        <is>
+          <t>Comparacion de la corrida clean contra E3_v2_clean.</t>
+        </is>
+      </c>
+    </row>
+    <row r="192" ht="15" customHeight="1" s="27">
+      <c r="A192" s="61" t="inlineStr">
+        <is>
+          <t>2026-03-25 05:51:25</t>
+        </is>
+      </c>
+      <c r="B192" s="61" t="inlineStr">
+        <is>
+          <t>E4_v2_clean</t>
+        </is>
+      </c>
+      <c r="C192" s="61" t="inlineStr">
+        <is>
+          <t>E4</t>
+        </is>
+      </c>
+      <c r="D192" s="61" t="inlineStr">
+        <is>
+          <t>comparacion</t>
+        </is>
+      </c>
+      <c r="E192" s="61" t="inlineStr">
+        <is>
+          <t>comparacion_vs_E4_v1_clean.json</t>
+        </is>
+      </c>
+      <c r="F192" s="61" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E4_v2_clean_20260325_055117/comparacion_vs_E4_v1_clean.json</t>
+        </is>
+      </c>
+      <c r="G192" s="61" t="inlineStr">
+        <is>
+          <t>Comparacion de la corrida clean contra E4_v1_clean.</t>
+        </is>
+      </c>
+    </row>
+    <row r="193" ht="15" customHeight="1" s="27">
+      <c r="A193" s="61" t="inlineStr">
+        <is>
+          <t>2026-03-25 05:51:25</t>
+        </is>
+      </c>
+      <c r="B193" s="61" t="inlineStr">
+        <is>
+          <t>E4_v2_clean</t>
+        </is>
+      </c>
+      <c r="C193" s="61" t="inlineStr">
+        <is>
+          <t>E4</t>
+        </is>
+      </c>
+      <c r="D193" s="61" t="inlineStr">
+        <is>
+          <t>metricas</t>
+        </is>
+      </c>
+      <c r="E193" s="61" t="inlineStr">
+        <is>
+          <t>metricas_horizonte.json</t>
+        </is>
+      </c>
+      <c r="F193" s="61" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E4_v2_clean_20260325_055117/metricas_horizonte.json</t>
+        </is>
+      </c>
+      <c r="G193" s="61" t="inlineStr">
+        <is>
+          <t>Resumen estructurado por horizonte.</t>
+        </is>
+      </c>
+    </row>
+    <row r="194" ht="15" customHeight="1" s="27">
+      <c r="A194" s="61" t="inlineStr">
+        <is>
+          <t>2026-03-25 05:51:25</t>
+        </is>
+      </c>
+      <c r="B194" s="61" t="inlineStr">
+        <is>
+          <t>E4_v2_clean</t>
+        </is>
+      </c>
+      <c r="C194" s="61" t="inlineStr">
+        <is>
+          <t>E4</t>
+        </is>
+      </c>
+      <c r="D194" s="61" t="inlineStr">
+        <is>
+          <t>metadata</t>
+        </is>
+      </c>
+      <c r="E194" s="61" t="inlineStr">
+        <is>
+          <t>metadata_run.json</t>
+        </is>
+      </c>
+      <c r="F194" s="61" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E4_v2_clean_20260325_055117/metadata_run.json</t>
+        </is>
+      </c>
+      <c r="G194" s="61" t="inlineStr">
+        <is>
+          <t>Metadata base del run.</t>
+        </is>
+      </c>
+    </row>
+    <row r="195" ht="15" customHeight="1" s="27">
+      <c r="A195" s="61" t="inlineStr">
+        <is>
+          <t>2026-03-25 05:51:44</t>
+        </is>
+      </c>
+      <c r="B195" s="61" t="inlineStr">
+        <is>
+          <t>E4_v3_clean</t>
+        </is>
+      </c>
+      <c r="C195" s="61" t="inlineStr">
+        <is>
+          <t>E4</t>
+        </is>
+      </c>
+      <c r="D195" s="61" t="inlineStr">
+        <is>
+          <t>script_snapshot</t>
+        </is>
+      </c>
+      <c r="E195" s="61" t="inlineStr">
+        <is>
+          <t>run_e4_xgboost.py</t>
+        </is>
+      </c>
+      <c r="F195" s="61" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E4_v3_clean_20260325_055134/scripts/run_e4_xgboost.py</t>
+        </is>
+      </c>
+      <c r="G195" s="61" t="inlineStr">
+        <is>
+          <t>Copia del script ejecutado para reproducibilidad.</t>
+        </is>
+      </c>
+    </row>
+    <row r="196" ht="15" customHeight="1" s="27">
+      <c r="A196" s="61" t="inlineStr">
+        <is>
+          <t>2026-03-25 05:51:44</t>
+        </is>
+      </c>
+      <c r="B196" s="61" t="inlineStr">
+        <is>
+          <t>E4_v3_clean</t>
+        </is>
+      </c>
+      <c r="C196" s="61" t="inlineStr">
+        <is>
+          <t>E4</t>
+        </is>
+      </c>
+      <c r="D196" s="61" t="inlineStr">
+        <is>
+          <t>parametros</t>
+        </is>
+      </c>
+      <c r="E196" s="61" t="inlineStr">
+        <is>
+          <t>parametros_run.json</t>
+        </is>
+      </c>
+      <c r="F196" s="61" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E4_v3_clean_20260325_055134/parametros_run.json</t>
+        </is>
+      </c>
+      <c r="G196" s="61" t="inlineStr">
+        <is>
+          <t>Parametros del experimento.</t>
+        </is>
+      </c>
+    </row>
+    <row r="197" ht="15" customHeight="1" s="27">
+      <c r="A197" s="61" t="inlineStr">
+        <is>
+          <t>2026-03-25 05:51:45</t>
+        </is>
+      </c>
+      <c r="B197" s="61" t="inlineStr">
+        <is>
+          <t>E4_v3_clean</t>
+        </is>
+      </c>
+      <c r="C197" s="61" t="inlineStr">
+        <is>
+          <t>E4</t>
+        </is>
+      </c>
+      <c r="D197" s="61" t="inlineStr">
+        <is>
+          <t>predicciones</t>
+        </is>
+      </c>
+      <c r="E197" s="61" t="inlineStr">
+        <is>
+          <t>predicciones_h1.csv</t>
+        </is>
+      </c>
+      <c r="F197" s="61" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E4_v3_clean_20260325_055134/predicciones_h1.csv</t>
+        </is>
+      </c>
+      <c r="G197" s="61" t="inlineStr">
+        <is>
+          <t>Predicciones walk-forward para horizonte 1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="198" ht="15" customHeight="1" s="27">
+      <c r="A198" s="61" t="inlineStr">
+        <is>
+          <t>2026-03-25 05:51:45</t>
+        </is>
+      </c>
+      <c r="B198" s="61" t="inlineStr">
+        <is>
+          <t>E4_v3_clean</t>
+        </is>
+      </c>
+      <c r="C198" s="61" t="inlineStr">
+        <is>
+          <t>E4</t>
+        </is>
+      </c>
+      <c r="D198" s="61" t="inlineStr">
+        <is>
+          <t>predicciones</t>
+        </is>
+      </c>
+      <c r="E198" s="61" t="inlineStr">
+        <is>
+          <t>predicciones_h2.csv</t>
+        </is>
+      </c>
+      <c r="F198" s="61" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E4_v3_clean_20260325_055134/predicciones_h2.csv</t>
+        </is>
+      </c>
+      <c r="G198" s="61" t="inlineStr">
+        <is>
+          <t>Predicciones walk-forward para horizonte 2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="199" ht="15" customHeight="1" s="27">
+      <c r="A199" s="61" t="inlineStr">
+        <is>
+          <t>2026-03-25 05:51:45</t>
+        </is>
+      </c>
+      <c r="B199" s="61" t="inlineStr">
+        <is>
+          <t>E4_v3_clean</t>
+        </is>
+      </c>
+      <c r="C199" s="61" t="inlineStr">
+        <is>
+          <t>E4</t>
+        </is>
+      </c>
+      <c r="D199" s="61" t="inlineStr">
+        <is>
+          <t>predicciones</t>
+        </is>
+      </c>
+      <c r="E199" s="61" t="inlineStr">
+        <is>
+          <t>predicciones_h3.csv</t>
+        </is>
+      </c>
+      <c r="F199" s="61" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E4_v3_clean_20260325_055134/predicciones_h3.csv</t>
+        </is>
+      </c>
+      <c r="G199" s="61" t="inlineStr">
+        <is>
+          <t>Predicciones walk-forward para horizonte 3.</t>
+        </is>
+      </c>
+    </row>
+    <row r="200" ht="15" customHeight="1" s="27">
+      <c r="A200" s="61" t="inlineStr">
+        <is>
+          <t>2026-03-25 05:51:45</t>
+        </is>
+      </c>
+      <c r="B200" s="61" t="inlineStr">
+        <is>
+          <t>E4_v3_clean</t>
+        </is>
+      </c>
+      <c r="C200" s="61" t="inlineStr">
+        <is>
+          <t>E4</t>
+        </is>
+      </c>
+      <c r="D200" s="61" t="inlineStr">
+        <is>
+          <t>predicciones</t>
+        </is>
+      </c>
+      <c r="E200" s="61" t="inlineStr">
+        <is>
+          <t>predicciones_h4.csv</t>
+        </is>
+      </c>
+      <c r="F200" s="61" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E4_v3_clean_20260325_055134/predicciones_h4.csv</t>
+        </is>
+      </c>
+      <c r="G200" s="61" t="inlineStr">
+        <is>
+          <t>Predicciones walk-forward para horizonte 4.</t>
+        </is>
+      </c>
+    </row>
+    <row r="201" ht="15" customHeight="1" s="27">
+      <c r="A201" s="61" t="inlineStr">
+        <is>
+          <t>2026-03-25 05:51:45</t>
+        </is>
+      </c>
+      <c r="B201" s="61" t="inlineStr">
+        <is>
+          <t>E4_v3_clean</t>
+        </is>
+      </c>
+      <c r="C201" s="61" t="inlineStr">
+        <is>
+          <t>E4</t>
+        </is>
+      </c>
+      <c r="D201" s="61" t="inlineStr">
+        <is>
+          <t>resumen</t>
+        </is>
+      </c>
+      <c r="E201" s="61" t="inlineStr">
+        <is>
+          <t>resumen_modeling_horizontes.json</t>
+        </is>
+      </c>
+      <c r="F201" s="61" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E4_v3_clean_20260325_055134/resumen_modeling_horizontes.json</t>
+        </is>
+      </c>
+      <c r="G201" s="61" t="inlineStr">
+        <is>
+          <t>Resumen de tamanos y seleccion de features por horizonte.</t>
+        </is>
+      </c>
+    </row>
+    <row r="202" ht="15" customHeight="1" s="27">
+      <c r="A202" s="61" t="inlineStr">
+        <is>
+          <t>2026-03-25 05:51:45</t>
+        </is>
+      </c>
+      <c r="B202" s="61" t="inlineStr">
+        <is>
+          <t>E4_v3_clean</t>
+        </is>
+      </c>
+      <c r="C202" s="61" t="inlineStr">
+        <is>
+          <t>E4</t>
+        </is>
+      </c>
+      <c r="D202" s="61" t="inlineStr">
+        <is>
+          <t>comparacion</t>
+        </is>
+      </c>
+      <c r="E202" s="61" t="inlineStr">
+        <is>
+          <t>comparacion_vs_E1_v5_clean.json</t>
+        </is>
+      </c>
+      <c r="F202" s="61" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E4_v3_clean_20260325_055134/comparacion_vs_E1_v5_clean.json</t>
+        </is>
+      </c>
+      <c r="G202" s="61" t="inlineStr">
+        <is>
+          <t>Comparacion de la corrida clean contra E1_v5_clean.</t>
+        </is>
+      </c>
+    </row>
+    <row r="203" ht="15" customHeight="1" s="27">
+      <c r="A203" s="61" t="inlineStr">
+        <is>
+          <t>2026-03-25 05:51:45</t>
+        </is>
+      </c>
+      <c r="B203" s="61" t="inlineStr">
+        <is>
+          <t>E4_v3_clean</t>
+        </is>
+      </c>
+      <c r="C203" s="61" t="inlineStr">
+        <is>
+          <t>E4</t>
+        </is>
+      </c>
+      <c r="D203" s="61" t="inlineStr">
+        <is>
+          <t>comparacion</t>
+        </is>
+      </c>
+      <c r="E203" s="61" t="inlineStr">
+        <is>
+          <t>comparacion_vs_E1_v4_clean.json</t>
+        </is>
+      </c>
+      <c r="F203" s="61" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E4_v3_clean_20260325_055134/comparacion_vs_E1_v4_clean.json</t>
+        </is>
+      </c>
+      <c r="G203" s="61" t="inlineStr">
+        <is>
+          <t>Comparacion de la corrida clean contra E1_v4_clean.</t>
+        </is>
+      </c>
+    </row>
+    <row r="204" ht="15" customHeight="1" s="27">
+      <c r="A204" s="61" t="inlineStr">
+        <is>
+          <t>2026-03-25 05:51:45</t>
+        </is>
+      </c>
+      <c r="B204" s="61" t="inlineStr">
+        <is>
+          <t>E4_v3_clean</t>
+        </is>
+      </c>
+      <c r="C204" s="61" t="inlineStr">
+        <is>
+          <t>E4</t>
+        </is>
+      </c>
+      <c r="D204" s="61" t="inlineStr">
+        <is>
+          <t>comparacion</t>
+        </is>
+      </c>
+      <c r="E204" s="61" t="inlineStr">
+        <is>
+          <t>comparacion_vs_E3_v2_clean.json</t>
+        </is>
+      </c>
+      <c r="F204" s="61" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E4_v3_clean_20260325_055134/comparacion_vs_E3_v2_clean.json</t>
+        </is>
+      </c>
+      <c r="G204" s="61" t="inlineStr">
+        <is>
+          <t>Comparacion de la corrida clean contra E3_v2_clean.</t>
+        </is>
+      </c>
+    </row>
+    <row r="205" ht="15" customHeight="1" s="27">
+      <c r="A205" s="61" t="inlineStr">
+        <is>
+          <t>2026-03-25 05:51:45</t>
+        </is>
+      </c>
+      <c r="B205" s="61" t="inlineStr">
+        <is>
+          <t>E4_v3_clean</t>
+        </is>
+      </c>
+      <c r="C205" s="61" t="inlineStr">
+        <is>
+          <t>E4</t>
+        </is>
+      </c>
+      <c r="D205" s="61" t="inlineStr">
+        <is>
+          <t>comparacion</t>
+        </is>
+      </c>
+      <c r="E205" s="61" t="inlineStr">
+        <is>
+          <t>comparacion_vs_E4_v1_clean.json</t>
+        </is>
+      </c>
+      <c r="F205" s="61" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E4_v3_clean_20260325_055134/comparacion_vs_E4_v1_clean.json</t>
+        </is>
+      </c>
+      <c r="G205" s="61" t="inlineStr">
+        <is>
+          <t>Comparacion de la corrida clean contra E4_v1_clean.</t>
+        </is>
+      </c>
+    </row>
+    <row r="206" ht="15" customHeight="1" s="27">
+      <c r="A206" s="61" t="inlineStr">
+        <is>
+          <t>2026-03-25 05:51:45</t>
+        </is>
+      </c>
+      <c r="B206" s="61" t="inlineStr">
+        <is>
+          <t>E4_v3_clean</t>
+        </is>
+      </c>
+      <c r="C206" s="61" t="inlineStr">
+        <is>
+          <t>E4</t>
+        </is>
+      </c>
+      <c r="D206" s="61" t="inlineStr">
+        <is>
+          <t>metricas</t>
+        </is>
+      </c>
+      <c r="E206" s="61" t="inlineStr">
+        <is>
+          <t>metricas_horizonte.json</t>
+        </is>
+      </c>
+      <c r="F206" s="61" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E4_v3_clean_20260325_055134/metricas_horizonte.json</t>
+        </is>
+      </c>
+      <c r="G206" s="61" t="inlineStr">
+        <is>
+          <t>Resumen estructurado por horizonte.</t>
+        </is>
+      </c>
+    </row>
+    <row r="207" ht="15" customHeight="1" s="27">
+      <c r="A207" s="61" t="inlineStr">
+        <is>
+          <t>2026-03-25 05:51:45</t>
+        </is>
+      </c>
+      <c r="B207" s="61" t="inlineStr">
+        <is>
+          <t>E4_v3_clean</t>
+        </is>
+      </c>
+      <c r="C207" s="61" t="inlineStr">
+        <is>
+          <t>E4</t>
+        </is>
+      </c>
+      <c r="D207" s="61" t="inlineStr">
+        <is>
+          <t>metadata</t>
+        </is>
+      </c>
+      <c r="E207" s="61" t="inlineStr">
+        <is>
+          <t>metadata_run.json</t>
+        </is>
+      </c>
+      <c r="F207" s="61" t="inlineStr">
+        <is>
+          <t>Experimentos/runs/E4_v3_clean_20260325_055134/metadata_run.json</t>
+        </is>
+      </c>
+      <c r="G207" s="61" t="inlineStr">
+        <is>
+          <t>Metadata base del run.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
